--- a/R Markdown/resultados/regionalizacao_acoes_2025.xlsx
+++ b/R Markdown/resultados/regionalizacao_acoes_2025.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F395"/>
+  <dimension ref="A1:F396"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -418,13 +418,13 @@
         <v>2025</v>
       </c>
       <c r="C3">
-        <v>8260998380.62</v>
+        <v>8261724836.03</v>
       </c>
       <c r="D3">
-        <v>7067098857.33</v>
+        <v>7067825312.74</v>
       </c>
       <c r="E3">
-        <v>0.855477574467168</v>
+        <v>0.8554902823580719</v>
       </c>
       <c r="F3">
         <v>32</v>
@@ -440,13 +440,13 @@
         <v>2025</v>
       </c>
       <c r="C4">
-        <v>7163025827.57</v>
+        <v>7164711595.23</v>
       </c>
       <c r="D4">
-        <v>6909261231.8</v>
+        <v>6910697398.82</v>
       </c>
       <c r="E4">
-        <v>0.9645729888627126</v>
+        <v>0.9645464868984939</v>
       </c>
       <c r="F4">
         <v>32</v>
@@ -506,13 +506,13 @@
         <v>2025</v>
       </c>
       <c r="C7">
-        <v>5347929013.33</v>
+        <v>5366178134.74</v>
       </c>
       <c r="D7">
-        <v>2023878602.91</v>
+        <v>2024847308.26</v>
       </c>
       <c r="E7">
-        <v>0.3784415608108062</v>
+        <v>0.3773350897823125</v>
       </c>
       <c r="F7">
         <v>32</v>
@@ -719,45 +719,45 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Programa Pode Entrar</t>
+          <t>Alimentação Escolar</t>
         </is>
       </c>
       <c r="B17">
         <v>2025</v>
       </c>
       <c r="C17">
-        <v>1161992554.54</v>
+        <v>1162285657.03</v>
       </c>
       <c r="D17">
-        <v>1161992554.54</v>
+        <v>1045629822.51</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0.8996323891511389</v>
       </c>
       <c r="F17">
-        <v>21</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Alimentação Escolar</t>
+          <t>Programa Pode Entrar</t>
         </is>
       </c>
       <c r="B18">
         <v>2025</v>
       </c>
       <c r="C18">
-        <v>1159626693.33</v>
+        <v>1162178834.16</v>
       </c>
       <c r="D18">
-        <v>1043620195.21</v>
+        <v>1162178834.16</v>
       </c>
       <c r="E18">
-        <v>0.8999622043996987</v>
+        <v>1</v>
       </c>
       <c r="F18">
-        <v>32</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -836,10 +836,10 @@
         <v>2025</v>
       </c>
       <c r="C22">
-        <v>992519202.22</v>
+        <v>995502943.62</v>
       </c>
       <c r="D22">
-        <v>992519202.22</v>
+        <v>995502943.62</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -902,10 +902,10 @@
         <v>2025</v>
       </c>
       <c r="C25">
-        <v>865763972.49</v>
+        <v>870828465.46</v>
       </c>
       <c r="D25">
-        <v>865763972.49</v>
+        <v>870828465.46</v>
       </c>
       <c r="E25">
         <v>1</v>
@@ -1122,10 +1122,10 @@
         <v>2025</v>
       </c>
       <c r="C35">
-        <v>504674645.22</v>
+        <v>505536363.2</v>
       </c>
       <c r="D35">
-        <v>504674645.22</v>
+        <v>505536363.2</v>
       </c>
       <c r="E35">
         <v>1</v>
@@ -1166,10 +1166,10 @@
         <v>2025</v>
       </c>
       <c r="C37">
-        <v>456704983.91</v>
+        <v>462226776.85</v>
       </c>
       <c r="D37">
-        <v>456704983.91</v>
+        <v>462226776.85</v>
       </c>
       <c r="E37">
         <v>1</v>
@@ -1188,10 +1188,10 @@
         <v>2025</v>
       </c>
       <c r="C38">
-        <v>447418653.37</v>
+        <v>448180450.58</v>
       </c>
       <c r="D38">
-        <v>447418653.37</v>
+        <v>448180450.58</v>
       </c>
       <c r="E38">
         <v>1</v>
@@ -1210,10 +1210,10 @@
         <v>2025</v>
       </c>
       <c r="C39">
-        <v>422715330.72</v>
+        <v>429992390.75</v>
       </c>
       <c r="D39">
-        <v>422715330.72</v>
+        <v>429992390.75</v>
       </c>
       <c r="E39">
         <v>1</v>
@@ -1232,10 +1232,10 @@
         <v>2025</v>
       </c>
       <c r="C40">
-        <v>414240376.8</v>
+        <v>414821738.89</v>
       </c>
       <c r="D40">
-        <v>414240376.8</v>
+        <v>414821738.89</v>
       </c>
       <c r="E40">
         <v>1</v>
@@ -1254,10 +1254,10 @@
         <v>2025</v>
       </c>
       <c r="C41">
-        <v>401160259.57</v>
+        <v>401175229.7</v>
       </c>
       <c r="D41">
-        <v>401160259.57</v>
+        <v>401175229.7</v>
       </c>
       <c r="E41">
         <v>1</v>
@@ -1342,13 +1342,13 @@
         <v>2025</v>
       </c>
       <c r="C45">
-        <v>374070753.03</v>
+        <v>374268404.92</v>
       </c>
       <c r="D45">
-        <v>13409170.57</v>
+        <v>13490306.1</v>
       </c>
       <c r="E45">
-        <v>0.03584661581100568</v>
+        <v>0.0360444694840954</v>
       </c>
       <c r="F45">
         <v>32</v>
@@ -1386,13 +1386,13 @@
         <v>2025</v>
       </c>
       <c r="C47">
-        <v>358570930.51</v>
+        <v>359028610.88</v>
       </c>
       <c r="D47">
-        <v>97469423.44</v>
+        <v>97927103.81</v>
       </c>
       <c r="E47">
-        <v>0.2718274548953759</v>
+        <v>0.2727557103874674</v>
       </c>
       <c r="F47">
         <v>19</v>
@@ -1430,10 +1430,10 @@
         <v>2025</v>
       </c>
       <c r="C49">
-        <v>331539229.16</v>
+        <v>339617203.45</v>
       </c>
       <c r="D49">
-        <v>331539229.16</v>
+        <v>339617203.45</v>
       </c>
       <c r="E49">
         <v>1</v>
@@ -1445,67 +1445,67 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Manutenção e Operação do Sistema Municipal de Transporte Público</t>
+          <t>Ampliação, Reforma e Requalificação de Equipamentos em Atenção Hospitalar e de Urgência e Emergência</t>
         </is>
       </c>
       <c r="B50">
         <v>2025</v>
       </c>
       <c r="C50">
-        <v>327284818.58</v>
+        <v>339270127.05</v>
       </c>
       <c r="D50">
-        <v>0</v>
+        <v>327248104.57</v>
       </c>
       <c r="E50">
-        <v>0</v>
+        <v>0.9645650426563248</v>
       </c>
       <c r="F50">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Programação de Atividades Culturais</t>
+          <t>Manutenção e Operação do Sistema Municipal de Transporte Público</t>
         </is>
       </c>
       <c r="B51">
         <v>2025</v>
       </c>
       <c r="C51">
-        <v>322719234.51</v>
+        <v>327284818.58</v>
       </c>
       <c r="D51">
-        <v>322719234.51</v>
+        <v>0</v>
       </c>
       <c r="E51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F51">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Ampliação, Reforma e Requalificação de Equipamentos em Atenção Hospitalar e de Urgência e Emergência</t>
+          <t>Programação de Atividades Culturais</t>
         </is>
       </c>
       <c r="B52">
         <v>2025</v>
       </c>
       <c r="C52">
-        <v>315146744.86</v>
+        <v>322823606.95</v>
       </c>
       <c r="D52">
-        <v>303124722.38</v>
+        <v>322823606.95</v>
       </c>
       <c r="E52">
-        <v>0.9618526204821165</v>
+        <v>1</v>
       </c>
       <c r="F52">
-        <v>22</v>
+        <v>32</v>
       </c>
     </row>
     <row r="53">
@@ -1533,45 +1533,45 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Manutenção e Operação do Programa de Estágios</t>
+          <t>Urbanização de Favelas</t>
         </is>
       </c>
       <c r="B54">
         <v>2025</v>
       </c>
       <c r="C54">
-        <v>276937453.31</v>
+        <v>277357318.52</v>
       </c>
       <c r="D54">
-        <v>1769097.52</v>
+        <v>277357318.52</v>
       </c>
       <c r="E54">
-        <v>0.006388076075862864</v>
+        <v>1</v>
       </c>
       <c r="F54">
-        <v>1</v>
+        <v>31</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Urbanização de Favelas</t>
+          <t>Manutenção e Operação do Programa de Estágios</t>
         </is>
       </c>
       <c r="B55">
         <v>2025</v>
       </c>
       <c r="C55">
-        <v>276769423.59</v>
+        <v>276937453.31</v>
       </c>
       <c r="D55">
-        <v>276769423.59</v>
+        <v>1769097.52</v>
       </c>
       <c r="E55">
-        <v>1</v>
+        <v>0.006388076075862864</v>
       </c>
       <c r="F55">
-        <v>31</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -1584,10 +1584,10 @@
         <v>2025</v>
       </c>
       <c r="C56">
-        <v>272589307.17</v>
+        <v>272596126.56</v>
       </c>
       <c r="D56">
-        <v>272589307.17</v>
+        <v>272596126.56</v>
       </c>
       <c r="E56">
         <v>1</v>
@@ -1804,10 +1804,10 @@
         <v>2025</v>
       </c>
       <c r="C66">
-        <v>187531929.15</v>
+        <v>187543337.51</v>
       </c>
       <c r="D66">
-        <v>187531929.15</v>
+        <v>187543337.51</v>
       </c>
       <c r="E66">
         <v>1</v>
@@ -1819,45 +1819,45 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Fornecimento de Material Escolar-Educação Infantil</t>
+          <t>Ampliação, Reforma e Requalificação de Equipamentos de Atenção Básica e Especialidades</t>
         </is>
       </c>
       <c r="B67">
         <v>2025</v>
       </c>
       <c r="C67">
-        <v>184272452.57</v>
+        <v>187438774.95</v>
       </c>
       <c r="D67">
-        <v>0</v>
+        <v>186913959.61</v>
       </c>
       <c r="E67">
-        <v>0</v>
+        <v>0.9972000705823008</v>
       </c>
       <c r="F67">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Ampliação, Reforma e Requalificação de Equipamentos de Atenção Básica e Especialidades</t>
+          <t>Fornecimento de Material Escolar-Educação Infantil</t>
         </is>
       </c>
       <c r="B68">
         <v>2025</v>
       </c>
       <c r="C68">
-        <v>183589741.36</v>
+        <v>184272452.57</v>
       </c>
       <c r="D68">
-        <v>183064926.02</v>
+        <v>0</v>
       </c>
       <c r="E68">
-        <v>0.9971413689233818</v>
+        <v>0</v>
       </c>
       <c r="F68">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -1870,10 +1870,10 @@
         <v>2025</v>
       </c>
       <c r="C69">
-        <v>181207214.27</v>
+        <v>181226491.55</v>
       </c>
       <c r="D69">
-        <v>181207214.27</v>
+        <v>181226491.55</v>
       </c>
       <c r="E69">
         <v>1</v>
@@ -1958,10 +1958,10 @@
         <v>2025</v>
       </c>
       <c r="C73">
-        <v>168660880.04</v>
+        <v>168720856.2</v>
       </c>
       <c r="D73">
-        <v>168660880.04</v>
+        <v>168720856.2</v>
       </c>
       <c r="E73">
         <v>1</v>
@@ -2002,10 +2002,10 @@
         <v>2025</v>
       </c>
       <c r="C75">
-        <v>165432525.7</v>
+        <v>166910635.07</v>
       </c>
       <c r="D75">
-        <v>165432525.7</v>
+        <v>166910635.07</v>
       </c>
       <c r="E75">
         <v>1</v>
@@ -2083,58 +2083,58 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Manutenção e Operação de Equipamentos Esportivos</t>
+          <t>Intervenção, Urbanização e Melhoria de Bairros - Plano de Obras das Subprefeituras</t>
         </is>
       </c>
       <c r="B79">
         <v>2025</v>
       </c>
       <c r="C79">
-        <v>154900929.52</v>
+        <v>158733785.31</v>
       </c>
       <c r="D79">
-        <v>154900929.52</v>
+        <v>158733785.31</v>
       </c>
       <c r="E79">
         <v>1</v>
       </c>
       <c r="F79">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Manutenção e Operação do Controle e Fiscalização de Tráfego</t>
+          <t>Manutenção e Operação de Equipamentos Esportivos</t>
         </is>
       </c>
       <c r="B80">
         <v>2025</v>
       </c>
       <c r="C80">
-        <v>150767148.2</v>
+        <v>154900929.52</v>
       </c>
       <c r="D80">
-        <v>0</v>
+        <v>154900929.52</v>
       </c>
       <c r="E80">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F80">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Leve-Leite</t>
+          <t>Manutenção e Operação do Controle e Fiscalização de Tráfego</t>
         </is>
       </c>
       <c r="B81">
         <v>2025</v>
       </c>
       <c r="C81">
-        <v>147955646.44</v>
+        <v>150767148.2</v>
       </c>
       <c r="D81">
         <v>0</v>
@@ -2149,23 +2149,23 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Intervenção, Urbanização e Melhoria de Bairros - Plano de Obras das Subprefeituras</t>
+          <t>Leve-Leite</t>
         </is>
       </c>
       <c r="B82">
         <v>2025</v>
       </c>
       <c r="C82">
-        <v>143183119.13</v>
+        <v>147955646.44</v>
       </c>
       <c r="D82">
-        <v>143183119.13</v>
+        <v>0</v>
       </c>
       <c r="E82">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F82">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -2222,10 +2222,10 @@
         <v>2025</v>
       </c>
       <c r="C85">
-        <v>135517672.98</v>
+        <v>135950577.37</v>
       </c>
       <c r="D85">
-        <v>135517672.98</v>
+        <v>135950577.37</v>
       </c>
       <c r="E85">
         <v>1</v>
@@ -2391,45 +2391,45 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Modernização, operação e manutenção dos canais SP156</t>
+          <t>Intervenções na Área de Mobilidade Urbana</t>
         </is>
       </c>
       <c r="B93">
         <v>2025</v>
       </c>
       <c r="C93">
-        <v>111588773.96</v>
+        <v>112920810.11</v>
       </c>
       <c r="D93">
-        <v>0</v>
+        <v>112920810.11</v>
       </c>
       <c r="E93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F93">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Intervenções na Área de Mobilidade Urbana</t>
+          <t>Modernização, operação e manutenção dos canais SP156</t>
         </is>
       </c>
       <c r="B94">
         <v>2025</v>
       </c>
       <c r="C94">
-        <v>111043151.68</v>
+        <v>111588773.96</v>
       </c>
       <c r="D94">
-        <v>111043151.68</v>
+        <v>0</v>
       </c>
       <c r="E94">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F94">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -2552,10 +2552,10 @@
         <v>2025</v>
       </c>
       <c r="C100">
-        <v>96231080.70999999</v>
+        <v>96418666.62</v>
       </c>
       <c r="D100">
-        <v>96231080.70999999</v>
+        <v>96418666.62</v>
       </c>
       <c r="E100">
         <v>1</v>
@@ -2611,111 +2611,111 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Implantação e Construção de Terminais de Ônibus</t>
+          <t>Construção e Implantação de Equipamentos de Atenção Básica e Especialidades</t>
         </is>
       </c>
       <c r="B103">
         <v>2025</v>
       </c>
       <c r="C103">
-        <v>92077776.41</v>
+        <v>93558835.55</v>
       </c>
       <c r="D103">
-        <v>92077776.41</v>
+        <v>93558835.55</v>
       </c>
       <c r="E103">
         <v>1</v>
       </c>
       <c r="F103">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Regularização Fundiária</t>
+          <t>Implantação e Construção de Terminais de Ônibus</t>
         </is>
       </c>
       <c r="B104">
         <v>2025</v>
       </c>
       <c r="C104">
-        <v>91904312.92</v>
+        <v>92522521.27</v>
       </c>
       <c r="D104">
-        <v>91904312.92</v>
+        <v>92522521.27</v>
       </c>
       <c r="E104">
         <v>1</v>
       </c>
       <c r="F104">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Programa de Incentivo Fiscal Relacionado à Arena Corinthians</t>
+          <t>Regularização Fundiária</t>
         </is>
       </c>
       <c r="B105">
         <v>2025</v>
       </c>
       <c r="C105">
-        <v>91869365</v>
+        <v>91904312.92</v>
       </c>
       <c r="D105">
-        <v>0</v>
+        <v>91904312.92</v>
       </c>
       <c r="E105">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F105">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Inspeção de Obras de Artes Especiais - OAE</t>
+          <t>Programa de Incentivo Fiscal Relacionado à Arena Corinthians</t>
         </is>
       </c>
       <c r="B106">
         <v>2025</v>
       </c>
       <c r="C106">
-        <v>88767327.64</v>
+        <v>91869365</v>
       </c>
       <c r="D106">
-        <v>88767327.64</v>
+        <v>0</v>
       </c>
       <c r="E106">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F106">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Construção e Implantação de Equipamentos de Atenção Básica e Especialidades</t>
+          <t>Inspeção de Obras de Artes Especiais - OAE</t>
         </is>
       </c>
       <c r="B107">
         <v>2025</v>
       </c>
       <c r="C107">
-        <v>85367312.78</v>
+        <v>88767327.64</v>
       </c>
       <c r="D107">
-        <v>85367312.78</v>
+        <v>88767327.64</v>
       </c>
       <c r="E107">
         <v>1</v>
       </c>
       <c r="F107">
-        <v>20</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108">
@@ -2765,45 +2765,45 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Manutenção e Operação da Guarda Civil Metropolitana</t>
+          <t>Implantação e Construção de Corredores de Ônibus</t>
         </is>
       </c>
       <c r="B110">
         <v>2025</v>
       </c>
       <c r="C110">
-        <v>81623397.22</v>
+        <v>82322186.26000001</v>
       </c>
       <c r="D110">
-        <v>81623397.22</v>
+        <v>82322186.26000001</v>
       </c>
       <c r="E110">
         <v>1</v>
       </c>
       <c r="F110">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Manutenção e Operação de Corredores de Ônibus</t>
+          <t>Manutenção e Operação da Guarda Civil Metropolitana</t>
         </is>
       </c>
       <c r="B111">
         <v>2025</v>
       </c>
       <c r="C111">
-        <v>81332054.06</v>
+        <v>81628215.27</v>
       </c>
       <c r="D111">
-        <v>81332054.06</v>
+        <v>81628215.27</v>
       </c>
       <c r="E111">
         <v>1</v>
       </c>
       <c r="F111">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="112">
@@ -2816,13 +2816,13 @@
         <v>2025</v>
       </c>
       <c r="C112">
-        <v>81231142.19</v>
+        <v>81570508.48</v>
       </c>
       <c r="D112">
         <v>14916390.43</v>
       </c>
       <c r="E112">
-        <v>0.1836289633243184</v>
+        <v>0.1828649926052294</v>
       </c>
       <c r="F112">
         <v>10</v>
@@ -2831,45 +2831,45 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Manutenção e Operação da Atenção Hospitalar da Assistência Farmacêutica</t>
+          <t>Manutenção e Operação de Corredores de Ônibus</t>
         </is>
       </c>
       <c r="B113">
         <v>2025</v>
       </c>
       <c r="C113">
-        <v>80869670.3</v>
+        <v>81332054.06</v>
       </c>
       <c r="D113">
-        <v>202925</v>
+        <v>81332054.06</v>
       </c>
       <c r="E113">
-        <v>0.002509284373822902</v>
+        <v>1</v>
       </c>
       <c r="F113">
-        <v>3</v>
+        <v>31</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Implantação e Construção de Corredores de Ônibus</t>
+          <t>Manutenção e Operação da Atenção Hospitalar da Assistência Farmacêutica</t>
         </is>
       </c>
       <c r="B114">
         <v>2025</v>
       </c>
       <c r="C114">
-        <v>78119848.7</v>
+        <v>80869670.3</v>
       </c>
       <c r="D114">
-        <v>78119848.7</v>
+        <v>202925</v>
       </c>
       <c r="E114">
-        <v>1</v>
+        <v>0.002509284373822902</v>
       </c>
       <c r="F114">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="115">
@@ -2963,45 +2963,45 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Ações de Educação Integral</t>
+          <t>Conservação e Manutenção de Unidades Educacionais - Educação Infantil</t>
         </is>
       </c>
       <c r="B119">
         <v>2025</v>
       </c>
       <c r="C119">
-        <v>66553772.75</v>
+        <v>67307983.89</v>
       </c>
       <c r="D119">
-        <v>17214932.94</v>
+        <v>67307983.89</v>
       </c>
       <c r="E119">
-        <v>0.2586620146188482</v>
+        <v>1</v>
       </c>
       <c r="F119">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Conservação e Manutenção de Unidades Educacionais - Educação Infantil</t>
+          <t>Ações de Educação Integral</t>
         </is>
       </c>
       <c r="B120">
         <v>2025</v>
       </c>
       <c r="C120">
-        <v>60184937.43</v>
+        <v>66553772.75</v>
       </c>
       <c r="D120">
-        <v>60184937.43</v>
+        <v>17214932.94</v>
       </c>
       <c r="E120">
-        <v>1</v>
+        <v>0.2586620146188482</v>
       </c>
       <c r="F120">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="121">
@@ -3095,83 +3095,83 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Suporte e Manutenção da Coordenação de Imprensa</t>
+          <t>Ampliação, Reforma e Requalificação de Centros Educacionais Unificados (CEU)</t>
         </is>
       </c>
       <c r="B125">
         <v>2025</v>
       </c>
       <c r="C125">
-        <v>54875018.52</v>
+        <v>55959202.62</v>
       </c>
       <c r="D125">
-        <v>0</v>
+        <v>55959202.62</v>
       </c>
       <c r="E125">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F125">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Manutenção e Operação das Praças Digitais</t>
+          <t>Suporte e Manutenção da Coordenação de Imprensa</t>
         </is>
       </c>
       <c r="B126">
         <v>2025</v>
       </c>
       <c r="C126">
-        <v>54264921.25</v>
+        <v>54875018.52</v>
       </c>
       <c r="D126">
-        <v>54264921.25</v>
+        <v>0</v>
       </c>
       <c r="E126">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F126">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Manutenção e Operação do Descomplica SP</t>
+          <t>Desenvolvimento de Estudos, Projetos  e Instrumentos de Políticas Urbanas</t>
         </is>
       </c>
       <c r="B127">
         <v>2025</v>
       </c>
       <c r="C127">
-        <v>53892820.59</v>
+        <v>54505414.71</v>
       </c>
       <c r="D127">
-        <v>53892820.59</v>
+        <v>14576506.04</v>
       </c>
       <c r="E127">
-        <v>1</v>
+        <v>0.2674322563649016</v>
       </c>
       <c r="F127">
-        <v>32</v>
+        <v>5</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Administração dos Conselhos Tutelares</t>
+          <t>Manutenção e Operação das Praças Digitais</t>
         </is>
       </c>
       <c r="B128">
         <v>2025</v>
       </c>
       <c r="C128">
-        <v>52932143.21</v>
+        <v>54264921.25</v>
       </c>
       <c r="D128">
-        <v>52932143.21</v>
+        <v>54264921.25</v>
       </c>
       <c r="E128">
         <v>1</v>
@@ -3183,133 +3183,133 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Desenvolvimento de Estudos, Projetos  e Instrumentos de Políticas Urbanas</t>
+          <t>Manutenção e Operação do Descomplica SP</t>
         </is>
       </c>
       <c r="B129">
         <v>2025</v>
       </c>
       <c r="C129">
-        <v>51756424.64</v>
+        <v>53892820.59</v>
       </c>
       <c r="D129">
-        <v>11827515.97</v>
+        <v>53892820.59</v>
       </c>
       <c r="E129">
-        <v>0.2285226626890895</v>
+        <v>1</v>
       </c>
       <c r="F129">
-        <v>4</v>
+        <v>32</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Capacitação, Formação e Aperfeiçoamento de Servidores</t>
+          <t>Administração dos Conselhos Tutelares</t>
         </is>
       </c>
       <c r="B130">
         <v>2025</v>
       </c>
       <c r="C130">
-        <v>51115349.4</v>
+        <v>52932143.21</v>
       </c>
       <c r="D130">
-        <v>0</v>
+        <v>52932143.21</v>
       </c>
       <c r="E130">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F130">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Manutenção e Operação de Equipamentos de Proteção Social Especial à População Idosa</t>
+          <t>Capacitação, Formação e Aperfeiçoamento de Servidores</t>
         </is>
       </c>
       <c r="B131">
         <v>2025</v>
       </c>
       <c r="C131">
-        <v>50215651.57</v>
+        <v>51119866.28</v>
       </c>
       <c r="D131">
-        <v>50215651.57</v>
+        <v>0</v>
       </c>
       <c r="E131">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F131">
-        <v>31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Manutenção e Operação de Ciclovias, Ciclofaixas e Ciclorrotas</t>
+          <t>Manutenção e Operação de Equipamentos de Proteção Social Especial à População Idosa</t>
         </is>
       </c>
       <c r="B132">
         <v>2025</v>
       </c>
       <c r="C132">
-        <v>49160838.74</v>
+        <v>50215651.57</v>
       </c>
       <c r="D132">
-        <v>49160838.74</v>
+        <v>50215651.57</v>
       </c>
       <c r="E132">
         <v>1</v>
       </c>
       <c r="F132">
-        <v>19</v>
+        <v>31</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Armazém Solidário</t>
+          <t>Manutenção e Operação de Ciclovias, Ciclofaixas e Ciclorrotas</t>
         </is>
       </c>
       <c r="B133">
         <v>2025</v>
       </c>
       <c r="C133">
-        <v>48748359.48</v>
+        <v>49160838.74</v>
       </c>
       <c r="D133">
-        <v>48748359.48</v>
+        <v>49160838.74</v>
       </c>
       <c r="E133">
         <v>1</v>
       </c>
       <c r="F133">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Ampliação, Reforma e Requalificação de Centros Educacionais Unificados (CEU)</t>
+          <t>Armazém Solidário</t>
         </is>
       </c>
       <c r="B134">
         <v>2025</v>
       </c>
       <c r="C134">
-        <v>48151172.53</v>
+        <v>48748359.48</v>
       </c>
       <c r="D134">
-        <v>48151172.53</v>
+        <v>48748359.48</v>
       </c>
       <c r="E134">
         <v>1</v>
       </c>
       <c r="F134">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="135">
@@ -3344,10 +3344,10 @@
         <v>2025</v>
       </c>
       <c r="C136">
-        <v>46819740.95</v>
+        <v>46840144.7</v>
       </c>
       <c r="D136">
-        <v>46819740.95</v>
+        <v>46840144.7</v>
       </c>
       <c r="E136">
         <v>1</v>
@@ -3410,10 +3410,10 @@
         <v>2025</v>
       </c>
       <c r="C139">
-        <v>42874741.71</v>
+        <v>43484521.34</v>
       </c>
       <c r="D139">
-        <v>42874741.71</v>
+        <v>43484521.34</v>
       </c>
       <c r="E139">
         <v>1</v>
@@ -3432,10 +3432,10 @@
         <v>2025</v>
       </c>
       <c r="C140">
-        <v>41163678.53</v>
+        <v>41188995.66</v>
       </c>
       <c r="D140">
-        <v>41163678.53</v>
+        <v>41188995.66</v>
       </c>
       <c r="E140">
         <v>1</v>
@@ -3491,17 +3491,17 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Manutenção e Operação em Serviços de Saúde Animal</t>
+          <t>Intervenções em Próprios Municipais</t>
         </is>
       </c>
       <c r="B143">
         <v>2025</v>
       </c>
       <c r="C143">
-        <v>38553092.6</v>
+        <v>39680252.57</v>
       </c>
       <c r="D143">
-        <v>38553092.6</v>
+        <v>39680252.57</v>
       </c>
       <c r="E143">
         <v>1</v>
@@ -3513,17 +3513,17 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Intervenções em Próprios Municipais</t>
+          <t>Manutenção e Operação em Serviços de Saúde Animal</t>
         </is>
       </c>
       <c r="B144">
         <v>2025</v>
       </c>
       <c r="C144">
-        <v>38444105.57</v>
+        <v>38553092.6</v>
       </c>
       <c r="D144">
-        <v>38444105.57</v>
+        <v>38553092.6</v>
       </c>
       <c r="E144">
         <v>1</v>
@@ -3535,89 +3535,89 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Manutenção e Operação de Equipamentos Públicos Voltados ao Atendimento de Mulheres</t>
+          <t>Conservação e Manutenção de Unidades Educacionais - Ensino Fundamental</t>
         </is>
       </c>
       <c r="B145">
         <v>2025</v>
       </c>
       <c r="C145">
-        <v>37278357.17</v>
+        <v>38005928.3</v>
       </c>
       <c r="D145">
-        <v>37278357.17</v>
+        <v>38005928.3</v>
       </c>
       <c r="E145">
         <v>1</v>
       </c>
       <c r="F145">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Manutenção e Operação de Ciclofaixas de Lazer</t>
+          <t>Manutenção e Operação de Equipamentos Públicos Voltados ao Atendimento de Mulheres</t>
         </is>
       </c>
       <c r="B146">
         <v>2025</v>
       </c>
       <c r="C146">
-        <v>36351026.71</v>
+        <v>37278357.17</v>
       </c>
       <c r="D146">
-        <v>36351026.71</v>
+        <v>37278357.17</v>
       </c>
       <c r="E146">
         <v>1</v>
       </c>
       <c r="F146">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Manutenção e Operação de Unidades de Conservação</t>
+          <t>Manutenção e Operação de Ciclofaixas de Lazer</t>
         </is>
       </c>
       <c r="B147">
         <v>2025</v>
       </c>
       <c r="C147">
-        <v>35751598.37</v>
+        <v>36351026.71</v>
       </c>
       <c r="D147">
-        <v>35751598.37</v>
+        <v>36351026.71</v>
       </c>
       <c r="E147">
         <v>1</v>
       </c>
       <c r="F147">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Operação e Manutenção da São Paulo Investimentos e Negócios</t>
+          <t>Manutenção e Operação de Unidades de Conservação</t>
         </is>
       </c>
       <c r="B148">
         <v>2025</v>
       </c>
       <c r="C148">
-        <v>35283200</v>
+        <v>35751598.37</v>
       </c>
       <c r="D148">
-        <v>0</v>
+        <v>35751598.37</v>
       </c>
       <c r="E148">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F148">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="149">
@@ -3630,10 +3630,10 @@
         <v>2025</v>
       </c>
       <c r="C149">
-        <v>34908139.47</v>
+        <v>35456866.39</v>
       </c>
       <c r="D149">
-        <v>34908139.47</v>
+        <v>35456866.39</v>
       </c>
       <c r="E149">
         <v>1</v>
@@ -3645,39 +3645,39 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Manutenção e Operação de Casas de Cultura</t>
+          <t>Operação e Manutenção da São Paulo Investimentos e Negócios</t>
         </is>
       </c>
       <c r="B150">
         <v>2025</v>
       </c>
       <c r="C150">
-        <v>34523635.93</v>
+        <v>35283200</v>
       </c>
       <c r="D150">
-        <v>34523635.93</v>
+        <v>0</v>
       </c>
       <c r="E150">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F150">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Conservação e Manutenção de Unidades Educacionais - Ensino Fundamental</t>
+          <t>Manutenção e Operação de Casas de Cultura</t>
         </is>
       </c>
       <c r="B151">
         <v>2025</v>
       </c>
       <c r="C151">
-        <v>33663729.53</v>
+        <v>34529029.52</v>
       </c>
       <c r="D151">
-        <v>33663729.53</v>
+        <v>34529029.52</v>
       </c>
       <c r="E151">
         <v>1</v>
@@ -3689,45 +3689,45 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Políticas de Audiovisual</t>
+          <t>Ampliação, Reforma e Requalificação da Avenida Santo Amaro</t>
         </is>
       </c>
       <c r="B152">
         <v>2025</v>
       </c>
       <c r="C152">
-        <v>32001998.39</v>
+        <v>32043919.03</v>
       </c>
       <c r="D152">
-        <v>32001998.39</v>
+        <v>32043919.03</v>
       </c>
       <c r="E152">
         <v>1</v>
       </c>
       <c r="F152">
-        <v>32</v>
+        <v>2</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Manutenção e Operação de Bilheterias e Postos de Atendimento do Bilhete Único</t>
+          <t>Políticas de Audiovisual</t>
         </is>
       </c>
       <c r="B153">
         <v>2025</v>
       </c>
       <c r="C153">
-        <v>30635126.63</v>
+        <v>32001998.39</v>
       </c>
       <c r="D153">
-        <v>30635126.63</v>
+        <v>32001998.39</v>
       </c>
       <c r="E153">
         <v>1</v>
       </c>
       <c r="F153">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="154">
@@ -3740,10 +3740,10 @@
         <v>2025</v>
       </c>
       <c r="C154">
-        <v>30099483.6</v>
+        <v>30834691.29</v>
       </c>
       <c r="D154">
-        <v>30099483.6</v>
+        <v>30834691.29</v>
       </c>
       <c r="E154">
         <v>1</v>
@@ -3755,67 +3755,67 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Projetos para Inclusão da Pessoa com Deficiência</t>
+          <t>Manutenção e Operação de Bilheterias e Postos de Atendimento do Bilhete Único</t>
         </is>
       </c>
       <c r="B155">
         <v>2025</v>
       </c>
       <c r="C155">
-        <v>29993023.82</v>
+        <v>30635126.63</v>
       </c>
       <c r="D155">
-        <v>21783547.49</v>
+        <v>30635126.63</v>
       </c>
       <c r="E155">
-        <v>0.7262871399940094</v>
+        <v>1</v>
       </c>
       <c r="F155">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Manutenção e Operação de Equipamentos de Convivência e Fortalecimento de Vínculos para a Pessoa Idosa</t>
+          <t>Projetos para Inclusão da Pessoa com Deficiência</t>
         </is>
       </c>
       <c r="B156">
         <v>2025</v>
       </c>
       <c r="C156">
-        <v>29348458.54</v>
+        <v>29993023.82</v>
       </c>
       <c r="D156">
-        <v>29348458.54</v>
+        <v>21783547.49</v>
       </c>
       <c r="E156">
-        <v>1</v>
+        <v>0.7262871399940094</v>
       </c>
       <c r="F156">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Ampliação, Reforma e Requalificação da Avenida Santo Amaro</t>
+          <t>Manutenção e Operação de Equipamentos de Convivência e Fortalecimento de Vínculos para a Pessoa Idosa</t>
         </is>
       </c>
       <c r="B157">
         <v>2025</v>
       </c>
       <c r="C157">
-        <v>28978557.33</v>
+        <v>29348458.54</v>
       </c>
       <c r="D157">
-        <v>28978557.33</v>
+        <v>29348458.54</v>
       </c>
       <c r="E157">
         <v>1</v>
       </c>
       <c r="F157">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="158">
@@ -3887,80 +3887,80 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Ações de Melhorias para Administração Fazendária</t>
+          <t>Construção de Escolas Municipais de Educação Infantil (EMEI)</t>
         </is>
       </c>
       <c r="B161">
         <v>2025</v>
       </c>
       <c r="C161">
-        <v>26262552.16</v>
+        <v>27048914.35</v>
       </c>
       <c r="D161">
-        <v>0</v>
+        <v>27048914.35</v>
       </c>
       <c r="E161">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F161">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Centro Municipal para Pessoas com Transtorno do Espectro Autista</t>
+          <t>Ações de Melhorias para Administração Fazendária</t>
         </is>
       </c>
       <c r="B162">
         <v>2025</v>
       </c>
       <c r="C162">
-        <v>25813748.57</v>
+        <v>26262552.16</v>
       </c>
       <c r="D162">
-        <v>25813748.57</v>
+        <v>0</v>
       </c>
       <c r="E162">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F162">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Ações de Desestatização</t>
+          <t>Centro Municipal para Pessoas com Transtorno do Espectro Autista</t>
         </is>
       </c>
       <c r="B163">
         <v>2025</v>
       </c>
       <c r="C163">
-        <v>25120930.7</v>
+        <v>25813748.57</v>
       </c>
       <c r="D163">
-        <v>0</v>
+        <v>25813748.57</v>
       </c>
       <c r="E163">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F163">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Compensação Financeira - Outros Fundos de Previdência</t>
+          <t>Ações de Desestatização</t>
         </is>
       </c>
       <c r="B164">
         <v>2025</v>
       </c>
       <c r="C164">
-        <v>24763727.36</v>
+        <v>25120930.7</v>
       </c>
       <c r="D164">
         <v>0</v>
@@ -3975,23 +3975,23 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Construção de Escolas Municipais de Educação Infantil (EMEI)</t>
+          <t>Compensação Financeira - Outros Fundos de Previdência</t>
         </is>
       </c>
       <c r="B165">
         <v>2025</v>
       </c>
       <c r="C165">
-        <v>24460414.78</v>
+        <v>24763727.36</v>
       </c>
       <c r="D165">
-        <v>24460414.78</v>
+        <v>0</v>
       </c>
       <c r="E165">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F165">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166">
@@ -4114,10 +4114,10 @@
         <v>2025</v>
       </c>
       <c r="C171">
-        <v>21661232.99</v>
+        <v>21662072.44</v>
       </c>
       <c r="D171">
-        <v>21661232.99</v>
+        <v>21662072.44</v>
       </c>
       <c r="E171">
         <v>1</v>
@@ -4327,419 +4327,419 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Políticas, Programas e Ações para a População em Situação de Rua</t>
+          <t>Qualificação e Transformação Urbanística - AIU-SCE - Lei 17.844/2022</t>
         </is>
       </c>
       <c r="B181">
         <v>2025</v>
       </c>
       <c r="C181">
-        <v>18975592.68</v>
+        <v>19023008.24</v>
       </c>
       <c r="D181">
-        <v>18975592.68</v>
+        <v>19023008.24</v>
       </c>
       <c r="E181">
         <v>1</v>
       </c>
       <c r="F181">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Manutenção de Unidades Habitacionais</t>
+          <t>Políticas, Programas e Ações para a População em Situação de Rua</t>
         </is>
       </c>
       <c r="B182">
         <v>2025</v>
       </c>
       <c r="C182">
-        <v>18800244.53</v>
+        <v>18975592.68</v>
       </c>
       <c r="D182">
-        <v>18800244.53</v>
+        <v>18975592.68</v>
       </c>
       <c r="E182">
         <v>1</v>
       </c>
       <c r="F182">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Manutenção e Operação do Centro Cultural São Paulo</t>
+          <t>Manutenção de Unidades Habitacionais</t>
         </is>
       </c>
       <c r="B183">
         <v>2025</v>
       </c>
       <c r="C183">
-        <v>18657797.62</v>
+        <v>18802206.94</v>
       </c>
       <c r="D183">
-        <v>18657797.62</v>
+        <v>18802206.94</v>
       </c>
       <c r="E183">
         <v>1</v>
       </c>
       <c r="F183">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Ampliação, Reforma e Requalificação de Unidades Habitacionais</t>
+          <t>Manutenção e Operação do Centro Cultural São Paulo</t>
         </is>
       </c>
       <c r="B184">
         <v>2025</v>
       </c>
       <c r="C184">
-        <v>18652479.58</v>
+        <v>18666060.12</v>
       </c>
       <c r="D184">
-        <v>18652479.58</v>
+        <v>18666060.12</v>
       </c>
       <c r="E184">
         <v>1</v>
       </c>
       <c r="F184">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Manutenção e Operação de Equipamentos do Departamento dos Museus Municipais</t>
+          <t>Ampliação, Reforma e Requalificação de Unidades Habitacionais</t>
         </is>
       </c>
       <c r="B185">
         <v>2025</v>
       </c>
       <c r="C185">
-        <v>18374330.46</v>
+        <v>18652479.58</v>
       </c>
       <c r="D185">
-        <v>18374330.46</v>
+        <v>18652479.58</v>
       </c>
       <c r="E185">
         <v>1</v>
       </c>
       <c r="F185">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Lei de Fomento ao Teatro</t>
+          <t>Apoio e Suporte Técnico para o Desenvolvimento de Ações Pertinentes à Fiscalização e Escrituração de Certificados de Potencial Adicional de Construção - CEPACs</t>
         </is>
       </c>
       <c r="B186">
         <v>2025</v>
       </c>
       <c r="C186">
-        <v>17839300.96</v>
+        <v>18636143.6</v>
       </c>
       <c r="D186">
-        <v>17839300.96</v>
+        <v>0</v>
       </c>
       <c r="E186">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F186">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Transferência de Recursos Financeiros para as Unidades Educacionais - Centro Educacional Unificado (CEU)</t>
+          <t>Lei de Fomento ao Teatro</t>
         </is>
       </c>
       <c r="B187">
         <v>2025</v>
       </c>
       <c r="C187">
-        <v>17801516</v>
+        <v>18441276.12</v>
       </c>
       <c r="D187">
-        <v>17801516</v>
+        <v>18441276.12</v>
       </c>
       <c r="E187">
         <v>1</v>
       </c>
       <c r="F187">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Desenvolvimento de Sistemas de Informação e Comunicação</t>
+          <t>Manutenção e Operação de Equipamentos do Departamento dos Museus Municipais</t>
         </is>
       </c>
       <c r="B188">
         <v>2025</v>
       </c>
       <c r="C188">
-        <v>17387407.83</v>
+        <v>18381071.38</v>
       </c>
       <c r="D188">
-        <v>0</v>
+        <v>18381071.38</v>
       </c>
       <c r="E188">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F188">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Apoio e Suporte Técnico para o Desenvolvimento de Ações Pertinentes à Fiscalização e Escrituração de Certificados de Potencial Adicional de Construção - CEPACs</t>
+          <t>Transferência de Recursos Financeiros para as Unidades Educacionais - Centro Educacional Unificado (CEU)</t>
         </is>
       </c>
       <c r="B189">
         <v>2025</v>
       </c>
       <c r="C189">
-        <v>17373687.77</v>
+        <v>17801516</v>
       </c>
       <c r="D189">
-        <v>0</v>
+        <v>17801516</v>
       </c>
       <c r="E189">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F189">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Promoção da Arborização Urbana</t>
+          <t>Desenvolvimento de Sistemas de Informação e Comunicação</t>
         </is>
       </c>
       <c r="B190">
         <v>2025</v>
       </c>
       <c r="C190">
-        <v>17074694.09</v>
+        <v>17387407.83</v>
       </c>
       <c r="D190">
-        <v>17074694.09</v>
+        <v>0</v>
       </c>
       <c r="E190">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F190">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Manutenção e Operação de Centro de Referência de Segurança Alimentar e Nutricional</t>
+          <t>Promoção da Arborização Urbana</t>
         </is>
       </c>
       <c r="B191">
         <v>2025</v>
       </c>
       <c r="C191">
-        <v>16892016.16</v>
+        <v>17074694.09</v>
       </c>
       <c r="D191">
-        <v>16892016.16</v>
+        <v>17074694.09</v>
       </c>
       <c r="E191">
         <v>1</v>
       </c>
       <c r="F191">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Manutenção e Operação dos Pólos Regionais de Esporte</t>
+          <t>Manutenção e Operação de Centro de Referência de Segurança Alimentar e Nutricional</t>
         </is>
       </c>
       <c r="B192">
         <v>2025</v>
       </c>
       <c r="C192">
-        <v>16633182</v>
+        <v>16892016.16</v>
       </c>
       <c r="D192">
-        <v>16633182</v>
+        <v>16892016.16</v>
       </c>
       <c r="E192">
         <v>1</v>
       </c>
       <c r="F192">
-        <v>4</v>
+        <v>30</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Manutenção e Operação de Praças, Canteiros Centrais e Remanescentes</t>
+          <t>Manutenção e Operação dos Pólos Regionais de Esporte</t>
         </is>
       </c>
       <c r="B193">
         <v>2025</v>
       </c>
       <c r="C193">
-        <v>16084835.87</v>
+        <v>16633182</v>
       </c>
       <c r="D193">
-        <v>16084835.87</v>
+        <v>16633182</v>
       </c>
       <c r="E193">
         <v>1</v>
       </c>
       <c r="F193">
-        <v>32</v>
+        <v>4</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Implantação de Estrutura Turística no Triângulo Histórico</t>
+          <t>Manutenção e Operação de Praças, Canteiros Centrais e Remanescentes</t>
         </is>
       </c>
       <c r="B194">
         <v>2025</v>
       </c>
       <c r="C194">
-        <v>15025888.34</v>
+        <v>16084835.87</v>
       </c>
       <c r="D194">
-        <v>15025888.34</v>
+        <v>16084835.87</v>
       </c>
       <c r="E194">
         <v>1</v>
       </c>
       <c r="F194">
-        <v>1</v>
+        <v>32</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Operação e Manutenção de Unidade da Fundação Paulistana - FPETC</t>
+          <t>Implantação de Estrutura Turística no Triângulo Histórico</t>
         </is>
       </c>
       <c r="B195">
         <v>2025</v>
       </c>
       <c r="C195">
-        <v>14963285.94</v>
+        <v>15120864.55</v>
       </c>
       <c r="D195">
-        <v>14963285.94</v>
+        <v>15120864.55</v>
       </c>
       <c r="E195">
         <v>1</v>
       </c>
       <c r="F195">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Manutenção e Operação de Equipamentos Culturais</t>
+          <t>Operação e Manutenção de Unidade da Fundação Paulistana - FPETC</t>
         </is>
       </c>
       <c r="B196">
         <v>2025</v>
       </c>
       <c r="C196">
-        <v>14870885.79</v>
+        <v>14963285.94</v>
       </c>
       <c r="D196">
-        <v>14870885.79</v>
+        <v>14963285.94</v>
       </c>
       <c r="E196">
         <v>1</v>
       </c>
       <c r="F196">
-        <v>22</v>
+        <v>4</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Programa Saúde na Escola</t>
+          <t>Manutenção e Operação de Equipamentos Culturais</t>
         </is>
       </c>
       <c r="B197">
         <v>2025</v>
       </c>
       <c r="C197">
-        <v>14568991.34</v>
+        <v>14870885.79</v>
       </c>
       <c r="D197">
-        <v>0</v>
+        <v>14870885.79</v>
       </c>
       <c r="E197">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F197">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Manutenção e Operação de Telecentros</t>
+          <t>Programa Saúde na Escola</t>
         </is>
       </c>
       <c r="B198">
         <v>2025</v>
       </c>
       <c r="C198">
-        <v>14291121.78</v>
+        <v>14568991.34</v>
       </c>
       <c r="D198">
-        <v>14291121.78</v>
+        <v>0</v>
       </c>
       <c r="E198">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F198">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Fomento à Cultura da Periferia de São Paulo</t>
+          <t>Manutenção e Operação de Telecentros</t>
         </is>
       </c>
       <c r="B199">
         <v>2025</v>
       </c>
       <c r="C199">
-        <v>13951513.62</v>
+        <v>14291121.78</v>
       </c>
       <c r="D199">
-        <v>13951513.62</v>
+        <v>14291121.78</v>
       </c>
       <c r="E199">
         <v>1</v>
       </c>
       <c r="F199">
-        <v>18</v>
+        <v>29</v>
       </c>
     </row>
     <row r="200">
@@ -4752,38 +4752,38 @@
         <v>2025</v>
       </c>
       <c r="C200">
-        <v>13931402.14</v>
+        <v>14222824.96</v>
       </c>
       <c r="D200">
-        <v>13931402.14</v>
+        <v>14222824.96</v>
       </c>
       <c r="E200">
         <v>1</v>
       </c>
       <c r="F200">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Execução do Programa para a Valorização de Iniciativas Culturais</t>
+          <t>Fomento à Cultura da Periferia de São Paulo</t>
         </is>
       </c>
       <c r="B201">
         <v>2025</v>
       </c>
       <c r="C201">
-        <v>13103647.53</v>
+        <v>13951513.62</v>
       </c>
       <c r="D201">
-        <v>13103647.53</v>
+        <v>13951513.62</v>
       </c>
       <c r="E201">
         <v>1</v>
       </c>
       <c r="F201">
-        <v>32</v>
+        <v>18</v>
       </c>
     </row>
     <row r="202">
@@ -4796,16 +4796,16 @@
         <v>2025</v>
       </c>
       <c r="C202">
-        <v>13018436.48</v>
+        <v>13881018.08</v>
       </c>
       <c r="D202">
-        <v>13018436.48</v>
+        <v>13881018.08</v>
       </c>
       <c r="E202">
         <v>1</v>
       </c>
       <c r="F202">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="203">
@@ -4818,10 +4818,10 @@
         <v>2025</v>
       </c>
       <c r="C203">
-        <v>12992648.76</v>
+        <v>13419328.9</v>
       </c>
       <c r="D203">
-        <v>12992648.76</v>
+        <v>13419328.9</v>
       </c>
       <c r="E203">
         <v>1</v>
@@ -4833,17 +4833,17 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Manutenção e Operação de Equipamentos de Proteção Jurídico Social</t>
+          <t>Execução do Programa para a Valorização de Iniciativas Culturais</t>
         </is>
       </c>
       <c r="B204">
         <v>2025</v>
       </c>
       <c r="C204">
-        <v>12674476.33</v>
+        <v>13103647.53</v>
       </c>
       <c r="D204">
-        <v>12674476.33</v>
+        <v>13103647.53</v>
       </c>
       <c r="E204">
         <v>1</v>
@@ -4855,278 +4855,278 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Manutenção e Operação de Unidades Educacionais - Escola Municipal de Educação Fundamental e Médio (EMEFM)</t>
+          <t>Manutenção e Operação de Equipamentos de Proteção Jurídico Social</t>
         </is>
       </c>
       <c r="B205">
         <v>2025</v>
       </c>
       <c r="C205">
-        <v>12652331.42</v>
+        <v>12674476.33</v>
       </c>
       <c r="D205">
-        <v>12652331.42</v>
+        <v>12674476.33</v>
       </c>
       <c r="E205">
         <v>1</v>
       </c>
       <c r="F205">
-        <v>18</v>
+        <v>32</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Manutenção e Operação da Rede Parceira - Alfabetização de Jovens e Adultos</t>
+          <t>Manutenção e Operação de Unidades Educacionais - Escola Municipal de Educação Fundamental e Médio (EMEFM)</t>
         </is>
       </c>
       <c r="B206">
         <v>2025</v>
       </c>
       <c r="C206">
-        <v>12625335.68</v>
+        <v>12661824.73</v>
       </c>
       <c r="D206">
-        <v>12625335.68</v>
+        <v>12661824.73</v>
       </c>
       <c r="E206">
         <v>1</v>
       </c>
       <c r="F206">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Manutenção de Modalidades Desportivas do Centro Olímpico de Treinamento e Pesquisa (COTP)</t>
+          <t>Manutenção e Operação da Rede Parceira - Alfabetização de Jovens e Adultos</t>
         </is>
       </c>
       <c r="B207">
         <v>2025</v>
       </c>
       <c r="C207">
-        <v>12599707</v>
+        <v>12625335.68</v>
       </c>
       <c r="D207">
-        <v>12599707</v>
+        <v>12625335.68</v>
       </c>
       <c r="E207">
         <v>1</v>
       </c>
       <c r="F207">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Compensações Ambientais</t>
+          <t>Manutenção de Modalidades Desportivas do Centro Olímpico de Treinamento e Pesquisa (COTP)</t>
         </is>
       </c>
       <c r="B208">
         <v>2025</v>
       </c>
       <c r="C208">
-        <v>12542716.23</v>
+        <v>12599707</v>
       </c>
       <c r="D208">
-        <v>12542716.23</v>
+        <v>12599707</v>
       </c>
       <c r="E208">
         <v>1</v>
       </c>
       <c r="F208">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Ações de Difusão Cultural do Theatro Municipal - Administrativos</t>
+          <t>Compensações Ambientais</t>
         </is>
       </c>
       <c r="B209">
         <v>2025</v>
       </c>
       <c r="C209">
-        <v>12337280</v>
+        <v>12542716.23</v>
       </c>
       <c r="D209">
-        <v>12337280</v>
+        <v>12542716.23</v>
       </c>
       <c r="E209">
         <v>1</v>
       </c>
       <c r="F209">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Programa Jovem Monitor Cultural</t>
+          <t>Ações de Difusão Cultural do Theatro Municipal - Administrativos</t>
         </is>
       </c>
       <c r="B210">
         <v>2025</v>
       </c>
       <c r="C210">
-        <v>12207597.05</v>
+        <v>12337280</v>
       </c>
       <c r="D210">
-        <v>12207597.05</v>
+        <v>12337280</v>
       </c>
       <c r="E210">
         <v>1</v>
       </c>
       <c r="F210">
-        <v>32</v>
+        <v>1</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Manutenção e Operação de Viveiros de Produção</t>
+          <t>Programa Jovem Monitor Cultural</t>
         </is>
       </c>
       <c r="B211">
         <v>2025</v>
       </c>
       <c r="C211">
-        <v>12081547.05</v>
+        <v>12207597.05</v>
       </c>
       <c r="D211">
-        <v>12081547.05</v>
+        <v>12207597.05</v>
       </c>
       <c r="E211">
         <v>1</v>
       </c>
       <c r="F211">
-        <v>4</v>
+        <v>32</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Operação e Manutenção dos Centros de Apoio ao Trabalho e Empreendedorismo</t>
+          <t>Manutenção e Operação de Viveiros de Produção</t>
         </is>
       </c>
       <c r="B212">
         <v>2025</v>
       </c>
       <c r="C212">
-        <v>11866192.69</v>
+        <v>12081547.05</v>
       </c>
       <c r="D212">
-        <v>11866192.69</v>
+        <v>12081547.05</v>
       </c>
       <c r="E212">
         <v>1</v>
       </c>
       <c r="F212">
-        <v>32</v>
+        <v>4</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Corredor Aricanduva - Centro de Controle Operacional - COP - 2.1</t>
+          <t>Operação e Manutenção dos Centros de Apoio ao Trabalho e Empreendedorismo</t>
         </is>
       </c>
       <c r="B213">
         <v>2025</v>
       </c>
       <c r="C213">
-        <v>11545106.24</v>
+        <v>11866192.69</v>
       </c>
       <c r="D213">
-        <v>11545106.24</v>
+        <v>11866192.69</v>
       </c>
       <c r="E213">
         <v>1</v>
       </c>
       <c r="F213">
-        <v>1</v>
+        <v>32</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Manutenção e Operação da Biblioteca Mario de Andrade</t>
+          <t>Ampliação, Reforma e Requalificação de Áreas Públicas</t>
         </is>
       </c>
       <c r="B214">
         <v>2025</v>
       </c>
       <c r="C214">
-        <v>11229426.06</v>
+        <v>11852982.06</v>
       </c>
       <c r="D214">
-        <v>11229426.06</v>
+        <v>11852982.06</v>
       </c>
       <c r="E214">
         <v>1</v>
       </c>
       <c r="F214">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Ações de Planejamento, Monitoramento e Avaliação de Políticas Públicas</t>
+          <t>Corredor Aricanduva - Centro de Controle Operacional - COP - 2.1</t>
         </is>
       </c>
       <c r="B215">
         <v>2025</v>
       </c>
       <c r="C215">
-        <v>11219880.54</v>
+        <v>11545106.24</v>
       </c>
       <c r="D215">
-        <v>0</v>
+        <v>11545106.24</v>
       </c>
       <c r="E215">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F215">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Despesas Administrativas para Execução de Ações Judiciais - Processamento de Feitos</t>
+          <t>Manutenção e Operação da Biblioteca Mario de Andrade</t>
         </is>
       </c>
       <c r="B216">
         <v>2025</v>
       </c>
       <c r="C216">
-        <v>11054261.74</v>
+        <v>11240346.51</v>
       </c>
       <c r="D216">
-        <v>0</v>
+        <v>11240346.51</v>
       </c>
       <c r="E216">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F216">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Promoção à Saúde do Servidor Municipal</t>
+          <t>Ações de Planejamento, Monitoramento e Avaliação de Políticas Públicas</t>
         </is>
       </c>
       <c r="B217">
         <v>2025</v>
       </c>
       <c r="C217">
-        <v>10965128.66</v>
+        <v>11219880.54</v>
       </c>
       <c r="D217">
         <v>0</v>
@@ -5141,234 +5141,234 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Subvenção e Contribuições a Entidades Culturais</t>
+          <t>Despesas Administrativas para Execução de Ações Judiciais - Processamento de Feitos</t>
         </is>
       </c>
       <c r="B218">
         <v>2025</v>
       </c>
       <c r="C218">
-        <v>10944338.53</v>
+        <v>11054127.57</v>
       </c>
       <c r="D218">
-        <v>10944338.53</v>
+        <v>0</v>
       </c>
       <c r="E218">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F218">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Manutenção e Operação do Programa Melhor em Casa</t>
+          <t>Obras e Serviços nas Áreas de Riscos Geológicos - Preventivas</t>
         </is>
       </c>
       <c r="B219">
         <v>2025</v>
       </c>
       <c r="C219">
-        <v>10848000</v>
+        <v>11001244.42</v>
       </c>
       <c r="D219">
-        <v>10848000</v>
+        <v>11001244.42</v>
       </c>
       <c r="E219">
         <v>1</v>
       </c>
       <c r="F219">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Manutenção e Operação da Rede Parceira - Educação Especial</t>
+          <t>Promoção à Saúde do Servidor Municipal</t>
         </is>
       </c>
       <c r="B220">
         <v>2025</v>
       </c>
       <c r="C220">
-        <v>10819458.57</v>
+        <v>10965128.66</v>
       </c>
       <c r="D220">
-        <v>10819458.57</v>
+        <v>0</v>
       </c>
       <c r="E220">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F220">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Políticas, Programas e Ações para Mulheres</t>
+          <t>Subvenção e Contribuições a Entidades Culturais</t>
         </is>
       </c>
       <c r="B221">
         <v>2025</v>
       </c>
       <c r="C221">
-        <v>10643281.77</v>
+        <v>10944338.53</v>
       </c>
       <c r="D221">
-        <v>10643281.77</v>
+        <v>10944338.53</v>
       </c>
       <c r="E221">
         <v>1</v>
       </c>
       <c r="F221">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Ampliação, Reforma e Requalificação de Áreas Públicas</t>
+          <t>Manutenção e Operação do Programa Melhor em Casa</t>
         </is>
       </c>
       <c r="B222">
         <v>2025</v>
       </c>
       <c r="C222">
-        <v>10633673.77</v>
+        <v>10848000</v>
       </c>
       <c r="D222">
-        <v>10633673.77</v>
+        <v>10848000</v>
       </c>
       <c r="E222">
         <v>1</v>
       </c>
       <c r="F222">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Ampliação, Reforma e Requalificação de Equipamentos Culturais</t>
+          <t>Manutenção e Operação da Rede Parceira - Educação Especial</t>
         </is>
       </c>
       <c r="B223">
         <v>2025</v>
       </c>
       <c r="C223">
-        <v>10477847.9</v>
+        <v>10819458.57</v>
       </c>
       <c r="D223">
-        <v>10477847.9</v>
+        <v>10819458.57</v>
       </c>
       <c r="E223">
         <v>1</v>
       </c>
       <c r="F223">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Administração do Autódromo de Interlagos</t>
+          <t>Políticas, Programas e Ações para Mulheres</t>
         </is>
       </c>
       <c r="B224">
         <v>2025</v>
       </c>
       <c r="C224">
-        <v>10439178.32</v>
+        <v>10643281.77</v>
       </c>
       <c r="D224">
-        <v>10439178.32</v>
+        <v>10643281.77</v>
       </c>
       <c r="E224">
         <v>1</v>
       </c>
       <c r="F224">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Manutenção e Operação do Serviço de Moto Verificação</t>
+          <t>Ampliação, Reforma e Requalificação de Equipamentos Culturais</t>
         </is>
       </c>
       <c r="B225">
         <v>2025</v>
       </c>
       <c r="C225">
-        <v>10429358.66</v>
+        <v>10477847.9</v>
       </c>
       <c r="D225">
-        <v>10429358.66</v>
+        <v>10477847.9</v>
       </c>
       <c r="E225">
         <v>1</v>
       </c>
       <c r="F225">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Operação e Manutenção da Infraestrutura Turística</t>
+          <t>Administração do Autódromo de Interlagos</t>
         </is>
       </c>
       <c r="B226">
         <v>2025</v>
       </c>
       <c r="C226">
-        <v>10425671.89</v>
+        <v>10439178.32</v>
       </c>
       <c r="D226">
-        <v>0</v>
+        <v>10439178.32</v>
       </c>
       <c r="E226">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F226">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Manutenção e Operação da Casa da Mulher Brasileira</t>
+          <t>Manutenção e Operação do Serviço de Moto Verificação</t>
         </is>
       </c>
       <c r="B227">
         <v>2025</v>
       </c>
       <c r="C227">
-        <v>10354999.05</v>
+        <v>10429358.66</v>
       </c>
       <c r="D227">
-        <v>10354999.05</v>
+        <v>10429358.66</v>
       </c>
       <c r="E227">
         <v>1</v>
       </c>
       <c r="F227">
-        <v>18</v>
+        <v>32</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Gratificação de Municipalização - Saúde - Lei 13.510/03</t>
+          <t>Operação e Manutenção da Infraestrutura Turística</t>
         </is>
       </c>
       <c r="B228">
         <v>2025</v>
       </c>
       <c r="C228">
-        <v>10326196.94</v>
+        <v>10425671.89</v>
       </c>
       <c r="D228">
         <v>0</v>
@@ -5383,353 +5383,353 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Construção e Implantação de Unidades de Conservação</t>
+          <t>Manutenção e Operação da Casa da Mulher Brasileira</t>
         </is>
       </c>
       <c r="B229">
         <v>2025</v>
       </c>
       <c r="C229">
-        <v>10302519.43</v>
+        <v>10354999.05</v>
       </c>
       <c r="D229">
-        <v>10302519.43</v>
+        <v>10354999.05</v>
       </c>
       <c r="E229">
         <v>1</v>
       </c>
       <c r="F229">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Locação Social</t>
+          <t>Gratificação de Municipalização - Saúde - Lei 13.510/03</t>
         </is>
       </c>
       <c r="B230">
         <v>2025</v>
       </c>
       <c r="C230">
-        <v>9862344.91</v>
+        <v>10326196.94</v>
       </c>
       <c r="D230">
-        <v>9862344.91</v>
+        <v>0</v>
       </c>
       <c r="E230">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F230">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Sistema de Avaliação Escolar dos Alunos da Rede Municipal de Ensino</t>
+          <t>Construção e Implantação de Unidades de Conservação</t>
         </is>
       </c>
       <c r="B231">
         <v>2025</v>
       </c>
       <c r="C231">
-        <v>9805367.640000001</v>
+        <v>10302519.43</v>
       </c>
       <c r="D231">
-        <v>0</v>
+        <v>10302519.43</v>
       </c>
       <c r="E231">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F231">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Estudos, Planos e Projetos Ambientais</t>
+          <t>Locação Social</t>
         </is>
       </c>
       <c r="B232">
         <v>2025</v>
       </c>
       <c r="C232">
-        <v>9780730.539999999</v>
+        <v>9862344.91</v>
       </c>
       <c r="D232">
-        <v>9319880.439999999</v>
+        <v>9862344.91</v>
       </c>
       <c r="E232">
-        <v>0.9528818324852859</v>
+        <v>1</v>
       </c>
       <c r="F232">
-        <v>32</v>
+        <v>2</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Manutenção e Operação de Equipamentos Públicos Voltados à Promoção da Igualdade Racial</t>
+          <t>Sistema de Avaliação Escolar dos Alunos da Rede Municipal de Ensino</t>
         </is>
       </c>
       <c r="B233">
         <v>2025</v>
       </c>
       <c r="C233">
-        <v>9401595.109999999</v>
+        <v>9805367.640000001</v>
       </c>
       <c r="D233">
-        <v>9401595.109999999</v>
+        <v>0</v>
       </c>
       <c r="E233">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F233">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Manutenção e Operação de Equipamentos Públicos Voltados ao Atendimento da População de Rua</t>
+          <t>Estudos, Planos e Projetos Ambientais</t>
         </is>
       </c>
       <c r="B234">
         <v>2025</v>
       </c>
       <c r="C234">
-        <v>9356133.699999999</v>
+        <v>9780730.539999999</v>
       </c>
       <c r="D234">
-        <v>9356133.699999999</v>
+        <v>9319880.439999999</v>
       </c>
       <c r="E234">
-        <v>1</v>
+        <v>0.9528818324852859</v>
       </c>
       <c r="F234">
-        <v>2</v>
+        <v>32</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Manutenção e Operação do Policiamento de Trânsito</t>
+          <t>Manutenção e Operação de Equipamentos Públicos Voltados à Promoção da Igualdade Racial</t>
         </is>
       </c>
       <c r="B235">
         <v>2025</v>
       </c>
       <c r="C235">
-        <v>9222878.07</v>
+        <v>9401595.109999999</v>
       </c>
       <c r="D235">
-        <v>0</v>
+        <v>9401595.109999999</v>
       </c>
       <c r="E235">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F235">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Plano de Contingência para Situações de Baixas Temperaturas - Decreto nº 62.760/2023</t>
+          <t>Manutenção e Operação de Equipamentos Públicos Voltados ao Atendimento da População de Rua</t>
         </is>
       </c>
       <c r="B236">
         <v>2025</v>
       </c>
       <c r="C236">
-        <v>9215518.18</v>
+        <v>9356133.699999999</v>
       </c>
       <c r="D236">
-        <v>9215518.18</v>
+        <v>9356133.699999999</v>
       </c>
       <c r="E236">
         <v>1</v>
       </c>
       <c r="F236">
-        <v>32</v>
+        <v>2</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Manutenção e Operação de Equipamentos da Assistência Social</t>
+          <t>Manutenção e Operação do Policiamento de Trânsito</t>
         </is>
       </c>
       <c r="B237">
         <v>2025</v>
       </c>
       <c r="C237">
-        <v>9006914.82</v>
+        <v>9222878.07</v>
       </c>
       <c r="D237">
-        <v>9006914.82</v>
+        <v>0</v>
       </c>
       <c r="E237">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F237">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Prêmio Zé Renato</t>
+          <t>Plano de Contingência para Situações de Baixas Temperaturas - Decreto nº 62.760/2023</t>
         </is>
       </c>
       <c r="B238">
         <v>2025</v>
       </c>
       <c r="C238">
-        <v>8891738.119999999</v>
+        <v>9215518.18</v>
       </c>
       <c r="D238">
-        <v>8891738.119999999</v>
+        <v>9215518.18</v>
       </c>
       <c r="E238">
         <v>1</v>
       </c>
       <c r="F238">
-        <v>3</v>
+        <v>32</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Manutenção e Operação dos Serviços de Atendimento e Manejo da Fauna Silvestre</t>
+          <t>Manutenção e Operação de Equipamentos da Assistência Social</t>
         </is>
       </c>
       <c r="B239">
         <v>2025</v>
       </c>
       <c r="C239">
-        <v>8785942.76</v>
+        <v>9006914.82</v>
       </c>
       <c r="D239">
-        <v>8785942.76</v>
+        <v>9006914.82</v>
       </c>
       <c r="E239">
         <v>1</v>
       </c>
       <c r="F239">
-        <v>3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Manutenção e Operação de Unidades Educacionais - Educação Indígena</t>
+          <t>Prêmio Zé Renato</t>
         </is>
       </c>
       <c r="B240">
         <v>2025</v>
       </c>
       <c r="C240">
-        <v>8733645.470000001</v>
+        <v>8891738.119999999</v>
       </c>
       <c r="D240">
-        <v>8733645.470000001</v>
+        <v>8891738.119999999</v>
       </c>
       <c r="E240">
         <v>1</v>
       </c>
       <c r="F240">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Construção de Escolas Municipais de Ensino Fundamental (EMEF)</t>
+          <t>Manutenção e Operação dos Serviços de Atendimento e Manejo da Fauna Silvestre</t>
         </is>
       </c>
       <c r="B241">
         <v>2025</v>
       </c>
       <c r="C241">
-        <v>8523367.76</v>
+        <v>8785942.76</v>
       </c>
       <c r="D241">
-        <v>8523367.76</v>
+        <v>8785942.76</v>
       </c>
       <c r="E241">
         <v>1</v>
       </c>
       <c r="F241">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Obras e Serviços nas Áreas de Riscos Geológicos - Preventivas</t>
+          <t>Manutenção e Operação de Unidades Educacionais - Educação Indígena</t>
         </is>
       </c>
       <c r="B242">
         <v>2025</v>
       </c>
       <c r="C242">
-        <v>8168306.12</v>
+        <v>8739289.949999999</v>
       </c>
       <c r="D242">
-        <v>8168306.12</v>
+        <v>8739289.949999999</v>
       </c>
       <c r="E242">
         <v>1</v>
       </c>
       <c r="F242">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Incentivo ao Uso de Veículos Elétricos ou Movidos a Hidrogênio</t>
+          <t>Construção de Escolas Municipais de Ensino Fundamental (EMEF)</t>
         </is>
       </c>
       <c r="B243">
         <v>2025</v>
       </c>
       <c r="C243">
-        <v>8045576.24</v>
+        <v>8523367.76</v>
       </c>
       <c r="D243">
-        <v>0</v>
+        <v>8523367.76</v>
       </c>
       <c r="E243">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F243">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Lei de Fomento à Dança</t>
+          <t>Incentivo ao Uso de Veículos Elétricos ou Movidos a Hidrogênio</t>
         </is>
       </c>
       <c r="B244">
         <v>2025</v>
       </c>
       <c r="C244">
-        <v>7722016.45</v>
+        <v>8045576.24</v>
       </c>
       <c r="D244">
-        <v>7722016.45</v>
+        <v>0</v>
       </c>
       <c r="E244">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F244">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="245">
@@ -5742,10 +5742,10 @@
         <v>2025</v>
       </c>
       <c r="C245">
-        <v>7554848.96</v>
+        <v>8009042.46</v>
       </c>
       <c r="D245">
-        <v>7554848.96</v>
+        <v>8009042.46</v>
       </c>
       <c r="E245">
         <v>1</v>
@@ -5757,674 +5757,675 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Serviços de Desfazimento e Demolição de Construções Irregulares em Áreas de Proteção Ambiental</t>
+          <t>Lei de Fomento à Dança</t>
         </is>
       </c>
       <c r="B246">
         <v>2025</v>
       </c>
       <c r="C246">
-        <v>7499872.51</v>
+        <v>7882016.45</v>
       </c>
       <c r="D246">
-        <v>7499872.51</v>
+        <v>7882016.45</v>
       </c>
       <c r="E246">
         <v>1</v>
       </c>
       <c r="F246">
-        <v>32</v>
+        <v>13</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Manutenção e Operação de Unidades Educacionais - Centro Integrado de Jovens e Adultos (CIEJA)</t>
+          <t>Serviços de Desfazimento e Demolição de Construções Irregulares em Áreas de Proteção Ambiental</t>
         </is>
       </c>
       <c r="B247">
         <v>2025</v>
       </c>
       <c r="C247">
-        <v>7343354.75</v>
+        <v>7499872.51</v>
       </c>
       <c r="D247">
-        <v>7343354.75</v>
+        <v>7499872.51</v>
       </c>
       <c r="E247">
         <v>1</v>
       </c>
       <c r="F247">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Fomento e Apoio ao Cooperativismo</t>
+          <t>Manutenção e Operação de Unidades Educacionais - Centro Integrado de Jovens e Adultos (CIEJA)</t>
         </is>
       </c>
       <c r="B248">
         <v>2025</v>
       </c>
       <c r="C248">
-        <v>7296698.54</v>
+        <v>7343903.53</v>
       </c>
       <c r="D248">
-        <v>7296698.54</v>
+        <v>7343903.53</v>
       </c>
       <c r="E248">
         <v>1</v>
       </c>
       <c r="F248">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Programação de Atividades Culturais de Casas de Cultura</t>
+          <t>Fomento e Apoio ao Cooperativismo</t>
         </is>
       </c>
       <c r="B249">
         <v>2025</v>
       </c>
       <c r="C249">
-        <v>7200183.07</v>
+        <v>7296698.54</v>
       </c>
       <c r="D249">
-        <v>7200183.07</v>
+        <v>7296698.54</v>
       </c>
       <c r="E249">
         <v>1</v>
       </c>
       <c r="F249">
-        <v>31</v>
+        <v>21</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Políticas, Programas e Ações Inclusivas</t>
+          <t>Programação de Atividades Culturais de Casas de Cultura</t>
         </is>
       </c>
       <c r="B250">
         <v>2025</v>
       </c>
       <c r="C250">
-        <v>7056576.76</v>
+        <v>7200183.07</v>
       </c>
       <c r="D250">
-        <v>7056576.76</v>
+        <v>7200183.07</v>
       </c>
       <c r="E250">
         <v>1</v>
       </c>
       <c r="F250">
-        <v>1</v>
+        <v>31</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Conservação e Manutenção de Unidades Educacionais - CEU</t>
+          <t>Políticas, Programas e Ações Inclusivas</t>
         </is>
       </c>
       <c r="B251">
         <v>2025</v>
       </c>
       <c r="C251">
-        <v>6981990.76</v>
+        <v>7056576.76</v>
       </c>
       <c r="D251">
-        <v>6981990.76</v>
+        <v>7056576.76</v>
       </c>
       <c r="E251">
         <v>1</v>
       </c>
       <c r="F251">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Fomento ao Circo/Edital Xamego</t>
+          <t>Conservação e Manutenção de Unidades Educacionais - CEU</t>
         </is>
       </c>
       <c r="B252">
         <v>2025</v>
       </c>
       <c r="C252">
-        <v>6754888.52</v>
+        <v>6981990.76</v>
       </c>
       <c r="D252">
-        <v>6754888.52</v>
+        <v>6981990.76</v>
       </c>
       <c r="E252">
         <v>1</v>
       </c>
       <c r="F252">
-        <v>21</v>
+        <v>30</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Corredor Aricanduva - Obras do BRT - 1.1</t>
+          <t>Fomento ao Circo/Edital Xamego</t>
         </is>
       </c>
       <c r="B253">
         <v>2025</v>
       </c>
       <c r="C253">
-        <v>6524148.28</v>
+        <v>6930869.52</v>
       </c>
       <c r="D253">
-        <v>6524148.28</v>
+        <v>6930869.52</v>
       </c>
       <c r="E253">
         <v>1</v>
       </c>
       <c r="F253">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Manutenção da Ouvidoria de Direitos Humanos</t>
+          <t>Corredor Aricanduva - Obras do BRT - 1.1</t>
         </is>
       </c>
       <c r="B254">
         <v>2025</v>
       </c>
       <c r="C254">
-        <v>6432381.47</v>
+        <v>6524148.28</v>
       </c>
       <c r="D254">
-        <v>4167355.87</v>
+        <v>6524148.28</v>
       </c>
       <c r="E254">
-        <v>0.647871381608218</v>
+        <v>1</v>
       </c>
       <c r="F254">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Ações Permanentes de Promoção dos Direitos da População Idosa</t>
+          <t>Manutenção da Ouvidoria de Direitos Humanos</t>
         </is>
       </c>
       <c r="B255">
         <v>2025</v>
       </c>
       <c r="C255">
-        <v>6322795.78</v>
+        <v>6432381.47</v>
       </c>
       <c r="D255">
-        <v>6322795.78</v>
+        <v>4167355.87</v>
       </c>
       <c r="E255">
-        <v>1</v>
+        <v>0.647871381608218</v>
       </c>
       <c r="F255">
-        <v>32</v>
+        <v>3</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Operação e Manutenção do VAI TEC</t>
+          <t>Ações Permanentes de Promoção dos Direitos da População Idosa</t>
         </is>
       </c>
       <c r="B256">
         <v>2025</v>
       </c>
       <c r="C256">
-        <v>6263242</v>
+        <v>6322795.78</v>
       </c>
       <c r="D256">
-        <v>0</v>
+        <v>6322795.78</v>
       </c>
       <c r="E256">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F256">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Acessibilidade, Ampliação, Reforma e Requalificação de Faixas Exclusivas de Ônibus, inclusive Área de Parada e Plataforma de Embarque</t>
+          <t>Operação e Manutenção do VAI TEC</t>
         </is>
       </c>
       <c r="B257">
         <v>2025</v>
       </c>
       <c r="C257">
-        <v>6164968.08</v>
+        <v>6263242</v>
       </c>
       <c r="D257">
-        <v>6164968.08</v>
+        <v>0</v>
       </c>
       <c r="E257">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F257">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>PROCONECTA - Promoção da Conectividade e Inclusão Digital</t>
+          <t>Urbanismo Social</t>
         </is>
       </c>
       <c r="B258">
         <v>2025</v>
       </c>
       <c r="C258">
-        <v>6029276.65</v>
+        <v>6234869.01</v>
       </c>
       <c r="D258">
-        <v>6029276.65</v>
+        <v>6234869.01</v>
       </c>
       <c r="E258">
         <v>1</v>
       </c>
       <c r="F258">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Implantação de Transporte Público Hidroviário</t>
+          <t>Acessibilidade, Ampliação, Reforma e Requalificação de Faixas Exclusivas de Ônibus, inclusive Área de Parada e Plataforma de Embarque</t>
         </is>
       </c>
       <c r="B259">
         <v>2025</v>
       </c>
       <c r="C259">
-        <v>6007993.23</v>
+        <v>6164968.08</v>
       </c>
       <c r="D259">
-        <v>6007993.23</v>
+        <v>6164968.08</v>
       </c>
       <c r="E259">
         <v>1</v>
       </c>
       <c r="F259">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Manutenção e Operação do Programa Sampa+Rural</t>
+          <t>PROCONECTA - Promoção da Conectividade e Inclusão Digital</t>
         </is>
       </c>
       <c r="B260">
         <v>2025</v>
       </c>
       <c r="C260">
-        <v>5980369.12</v>
+        <v>6029276.65</v>
       </c>
       <c r="D260">
-        <v>200000</v>
+        <v>6029276.65</v>
       </c>
       <c r="E260">
-        <v>0.03344275177449248</v>
+        <v>1</v>
       </c>
       <c r="F260">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Corredor Aricanduva - Gerenciamento de Projetos - 3.1</t>
+          <t>Implantação de Transporte Público Hidroviário</t>
         </is>
       </c>
       <c r="B261">
         <v>2025</v>
       </c>
       <c r="C261">
-        <v>5715650.64</v>
+        <v>6007993.23</v>
       </c>
       <c r="D261">
-        <v>5715650.64</v>
+        <v>6007993.23</v>
       </c>
       <c r="E261">
         <v>1</v>
       </c>
       <c r="F261">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Programação de Atividades Culturais de Centros Culturais e Teatros</t>
+          <t>Manutenção e Operação do Programa Sampa+Rural</t>
         </is>
       </c>
       <c r="B262">
         <v>2025</v>
       </c>
       <c r="C262">
-        <v>5545753.5</v>
+        <v>5980369.12</v>
       </c>
       <c r="D262">
-        <v>5545753.5</v>
+        <v>200000</v>
       </c>
       <c r="E262">
-        <v>1</v>
+        <v>0.03344275177449248</v>
       </c>
       <c r="F262">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Contribuição Formação Patrimônio Servidor Público - Parcelamento PASEP</t>
+          <t>Corredor Aricanduva - Gerenciamento de Projetos - 3.1</t>
         </is>
       </c>
       <c r="B263">
         <v>2025</v>
       </c>
       <c r="C263">
-        <v>5413813.899999999</v>
+        <v>5837797.66</v>
       </c>
       <c r="D263">
-        <v>0</v>
+        <v>5837797.66</v>
       </c>
       <c r="E263">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F263">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Manutenção e Operação da Central de Interpretação de Libras, Intérpretes e Guias-Intérpretes</t>
+          <t>Programação de Atividades Culturais de Centros Culturais e Teatros</t>
         </is>
       </c>
       <c r="B264">
         <v>2025</v>
       </c>
       <c r="C264">
-        <v>5230195.81</v>
+        <v>5545753.5</v>
       </c>
       <c r="D264">
-        <v>227971.99</v>
+        <v>5545753.5</v>
       </c>
       <c r="E264">
-        <v>0.0435876587190337</v>
+        <v>1</v>
       </c>
       <c r="F264">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Manutenção e Operação de Unidades Educacionais - Escola Municipal de Educação Bilíngue para Surdos (EMEBS)</t>
+          <t>Contribuição Formação Patrimônio Servidor Público - Parcelamento PASEP</t>
         </is>
       </c>
       <c r="B265">
         <v>2025</v>
       </c>
       <c r="C265">
-        <v>5192321.11</v>
+        <v>5413813.899999999</v>
       </c>
       <c r="D265">
-        <v>5192321.11</v>
+        <v>0</v>
       </c>
       <c r="E265">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F265">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Políticas, Programas e Ações Para Criança e Adolescente</t>
+          <t>Manutenção e Operação da Central de Interpretação de Libras, Intérpretes e Guias-Intérpretes</t>
         </is>
       </c>
       <c r="B266">
         <v>2025</v>
       </c>
       <c r="C266">
-        <v>5112936.54</v>
+        <v>5230195.81</v>
       </c>
       <c r="D266">
-        <v>5112936.54</v>
+        <v>227971.99</v>
       </c>
       <c r="E266">
-        <v>1</v>
+        <v>0.0435876587190337</v>
       </c>
       <c r="F266">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Manutenção e Operação da Defesa Civil</t>
+          <t>Manutenção e Operação de Unidades Educacionais - Escola Municipal de Educação Bilíngue para Surdos (EMEBS)</t>
         </is>
       </c>
       <c r="B267">
         <v>2025</v>
       </c>
       <c r="C267">
-        <v>5092568.1</v>
+        <v>5192923.91</v>
       </c>
       <c r="D267">
-        <v>5092568.1</v>
+        <v>5192923.91</v>
       </c>
       <c r="E267">
         <v>1</v>
       </c>
       <c r="F267">
-        <v>32</v>
+        <v>20</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Urbanismo Social</t>
+          <t>Políticas, Programas e Ações Para Criança e Adolescente</t>
         </is>
       </c>
       <c r="B268">
         <v>2025</v>
       </c>
       <c r="C268">
-        <v>4977111.76</v>
+        <v>5112936.54</v>
       </c>
       <c r="D268">
-        <v>4977111.76</v>
+        <v>5112936.54</v>
       </c>
       <c r="E268">
         <v>1</v>
       </c>
       <c r="F268">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Ações de Difusão Cultural do Theatro Municipal - Patrimônio</t>
+          <t>Manutenção e Operação da Defesa Civil</t>
         </is>
       </c>
       <c r="B269">
         <v>2025</v>
       </c>
       <c r="C269">
-        <v>4716385</v>
+        <v>5092568.1</v>
       </c>
       <c r="D269">
-        <v>4716385</v>
+        <v>5092568.1</v>
       </c>
       <c r="E269">
         <v>1</v>
       </c>
       <c r="F269">
-        <v>1</v>
+        <v>32</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Auxílio Funeral</t>
+          <t>Ações de Difusão Cultural do Theatro Municipal - Patrimônio</t>
         </is>
       </c>
       <c r="B270">
         <v>2025</v>
       </c>
       <c r="C270">
-        <v>4715929.39</v>
+        <v>4716385</v>
       </c>
       <c r="D270">
-        <v>0</v>
+        <v>4716385</v>
       </c>
       <c r="E270">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F270">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Políticas de Promoção Cultural</t>
+          <t>Auxílio Funeral</t>
         </is>
       </c>
       <c r="B271">
         <v>2025</v>
       </c>
       <c r="C271">
-        <v>4613969.87</v>
+        <v>4715929.39</v>
       </c>
       <c r="D271">
-        <v>4613969.87</v>
+        <v>0</v>
       </c>
       <c r="E271">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F271">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Execução do Programa Museu de Arte de Rua - MAR</t>
+          <t>Políticas de Promoção Cultural</t>
         </is>
       </c>
       <c r="B272">
         <v>2025</v>
       </c>
       <c r="C272">
-        <v>4449133.5</v>
+        <v>4613969.87</v>
       </c>
       <c r="D272">
-        <v>4449133.5</v>
+        <v>4613969.87</v>
       </c>
       <c r="E272">
         <v>1</v>
       </c>
       <c r="F272">
-        <v>24</v>
+        <v>4</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Bolsa Atleta</t>
+          <t>Execução do Programa Museu de Arte de Rua - MAR</t>
         </is>
       </c>
       <c r="B273">
         <v>2025</v>
       </c>
       <c r="C273">
-        <v>4423925.75</v>
+        <v>4449133.5</v>
       </c>
       <c r="D273">
-        <v>0</v>
+        <v>4449133.5</v>
       </c>
       <c r="E273">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F273">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Fomento e Difusão do Rock</t>
+          <t>Bolsa Atleta</t>
         </is>
       </c>
       <c r="B274">
         <v>2025</v>
       </c>
       <c r="C274">
-        <v>4382816.26</v>
+        <v>4423925.75</v>
       </c>
       <c r="D274">
-        <v>4382816.26</v>
+        <v>0</v>
       </c>
       <c r="E274">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F274">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Promoção da Educação Antirracista e Não Xenofóbica na RMESP_x000D_</t>
+          <t>Fomento e Difusão do Rock</t>
         </is>
       </c>
       <c r="B275">
         <v>2025</v>
       </c>
       <c r="C275">
-        <v>4305082.14</v>
+        <v>4382816.26</v>
       </c>
       <c r="D275">
-        <v>0</v>
+        <v>4382816.26</v>
       </c>
       <c r="E275">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F275">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Obrigações e Contribuições Patronais - Parcelamento INSS</t>
+          <t xml:space="preserve">Promoção da Educação Antirracista e Não Xenofóbica na RMESP_x000D__x000D_
+</t>
         </is>
       </c>
       <c r="B276">
         <v>2025</v>
       </c>
       <c r="C276">
-        <v>4205808.49</v>
+        <v>4305082.14</v>
       </c>
       <c r="D276">
         <v>0</v>
@@ -6439,457 +6440,457 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Rádios Comunitárias - Lei nº 16.572/2016</t>
+          <t>Obrigações e Contribuições Patronais - Parcelamento INSS</t>
         </is>
       </c>
       <c r="B277">
         <v>2025</v>
       </c>
       <c r="C277">
-        <v>4150400</v>
+        <v>4205808.49</v>
       </c>
       <c r="D277">
-        <v>4150400</v>
+        <v>0</v>
       </c>
       <c r="E277">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F277">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Manutenção e Operação dos Planetários Municipais</t>
+          <t>Rádios Comunitárias - Lei nº 16.572/2016</t>
         </is>
       </c>
       <c r="B278">
         <v>2025</v>
       </c>
       <c r="C278">
-        <v>3892274.54</v>
+        <v>4150400</v>
       </c>
       <c r="D278">
-        <v>3892274.54</v>
+        <v>4150400</v>
       </c>
       <c r="E278">
         <v>1</v>
       </c>
       <c r="F278">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Manutenção e Operação do Arquivo Histórico Municipal</t>
+          <t>Manutenção e Operação dos Planetários Municipais</t>
         </is>
       </c>
       <c r="B279">
         <v>2025</v>
       </c>
       <c r="C279">
-        <v>3845589.79</v>
+        <v>3892274.54</v>
       </c>
       <c r="D279">
-        <v>3845589.79</v>
+        <v>3892274.54</v>
       </c>
       <c r="E279">
         <v>1</v>
       </c>
       <c r="F279">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Programação de Atividades Culturais nas Bibliotecas Públicas</t>
+          <t>Implantação e Construção de Ecopontos</t>
         </is>
       </c>
       <c r="B280">
         <v>2025</v>
       </c>
       <c r="C280">
-        <v>3677248</v>
+        <v>3881432.45</v>
       </c>
       <c r="D280">
-        <v>3677248</v>
+        <v>3881432.45</v>
       </c>
       <c r="E280">
         <v>1</v>
       </c>
       <c r="F280">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Implantação e Construção de Ecopontos</t>
+          <t>Manutenção e Operação do Arquivo Histórico Municipal</t>
         </is>
       </c>
       <c r="B281">
         <v>2025</v>
       </c>
       <c r="C281">
-        <v>3533532.42</v>
+        <v>3848072.79</v>
       </c>
       <c r="D281">
-        <v>3533532.42</v>
+        <v>3848072.79</v>
       </c>
       <c r="E281">
         <v>1</v>
       </c>
       <c r="F281">
-        <v>32</v>
+        <v>8</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Manutenção e Operação de Equipamentos do Patrimônio Histórico</t>
+          <t>Programação de Atividades Culturais nas Bibliotecas Públicas</t>
         </is>
       </c>
       <c r="B282">
         <v>2025</v>
       </c>
       <c r="C282">
-        <v>3533439.26</v>
+        <v>3677248</v>
       </c>
       <c r="D282">
-        <v>3533439.26</v>
+        <v>3677248</v>
       </c>
       <c r="E282">
         <v>1</v>
       </c>
       <c r="F282">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Ampliação, Reforma e Requalificação de Unidade de Abastecimento</t>
+          <t>Manutenção e Operação de Equipamentos do Patrimônio Histórico</t>
         </is>
       </c>
       <c r="B283">
         <v>2025</v>
       </c>
       <c r="C283">
-        <v>3498979.51</v>
+        <v>3533439.26</v>
       </c>
       <c r="D283">
-        <v>3498979.51</v>
+        <v>3533439.26</v>
       </c>
       <c r="E283">
         <v>1</v>
       </c>
       <c r="F283">
-        <v>1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Fomento e Difusão do Samba</t>
+          <t>Ampliação, Reforma e Requalificação de Unidade de Abastecimento</t>
         </is>
       </c>
       <c r="B284">
         <v>2025</v>
       </c>
       <c r="C284">
-        <v>3376027.8</v>
+        <v>3498979.51</v>
       </c>
       <c r="D284">
-        <v>3376027.8</v>
+        <v>3498979.51</v>
       </c>
       <c r="E284">
         <v>1</v>
       </c>
       <c r="F284">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Manutenção e Operação do Programa de Residência em Gestão Pública</t>
+          <t>Fomento e Difusão do Samba</t>
         </is>
       </c>
       <c r="B285">
         <v>2025</v>
       </c>
       <c r="C285">
-        <v>3368355.63</v>
+        <v>3376027.8</v>
       </c>
       <c r="D285">
-        <v>0</v>
+        <v>3376027.8</v>
       </c>
       <c r="E285">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F285">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Programa Piá</t>
+          <t>Manutenção e Operação do Programa de Residência em Gestão Pública</t>
         </is>
       </c>
       <c r="B286">
         <v>2025</v>
       </c>
       <c r="C286">
-        <v>3192295.94</v>
+        <v>3368355.63</v>
       </c>
       <c r="D286">
-        <v>3192295.94</v>
+        <v>0</v>
       </c>
       <c r="E286">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F286">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Fomento às Cadeias Produtivas, Vocações Produtivas e Projetos Locais</t>
+          <t>Programa Piá</t>
         </is>
       </c>
       <c r="B287">
         <v>2025</v>
       </c>
       <c r="C287">
-        <v>3075000</v>
+        <v>3192295.94</v>
       </c>
       <c r="D287">
-        <v>3075000</v>
+        <v>3192295.94</v>
       </c>
       <c r="E287">
         <v>1</v>
       </c>
       <c r="F287">
-        <v>3</v>
+        <v>26</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Bolsa-Trabalho</t>
+          <t>Fomento às Cadeias Produtivas, Vocações Produtivas e Projetos Locais</t>
         </is>
       </c>
       <c r="B288">
         <v>2025</v>
       </c>
       <c r="C288">
-        <v>2986100.12</v>
+        <v>3075000</v>
       </c>
       <c r="D288">
-        <v>0</v>
+        <v>3075000</v>
       </c>
       <c r="E288">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F288">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Execução de Serviços Médicos de Tratamento de Radioterapia</t>
+          <t>Bolsa-Trabalho</t>
         </is>
       </c>
       <c r="B289">
         <v>2025</v>
       </c>
       <c r="C289">
-        <v>2947054.09</v>
+        <v>2986100.12</v>
       </c>
       <c r="D289">
-        <v>2947054.09</v>
+        <v>0</v>
       </c>
       <c r="E289">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F289">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Manutenção e Operação dos Equipamentos Públicos Voltados para Pessoa Idosa</t>
+          <t>Execução de Serviços Médicos de Tratamento de Radioterapia</t>
         </is>
       </c>
       <c r="B290">
         <v>2025</v>
       </c>
       <c r="C290">
-        <v>2794306.38</v>
+        <v>2947054.09</v>
       </c>
       <c r="D290">
-        <v>2794306.38</v>
+        <v>2947054.09</v>
       </c>
       <c r="E290">
         <v>1</v>
       </c>
       <c r="F290">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Fomento e Difusão da Capoeira</t>
+          <t>Manutenção e Operação dos Equipamentos Públicos Voltados para Pessoa Idosa</t>
         </is>
       </c>
       <c r="B291">
         <v>2025</v>
       </c>
       <c r="C291">
-        <v>2784876</v>
+        <v>2794306.38</v>
       </c>
       <c r="D291">
-        <v>2784876</v>
+        <v>2794306.38</v>
       </c>
       <c r="E291">
         <v>1</v>
       </c>
       <c r="F291">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Educação Ambiental</t>
+          <t>Fomento e Difusão da Capoeira</t>
         </is>
       </c>
       <c r="B292">
         <v>2025</v>
       </c>
       <c r="C292">
-        <v>2647738.2</v>
+        <v>2784876</v>
       </c>
       <c r="D292">
-        <v>2647738.2</v>
+        <v>2784876</v>
       </c>
       <c r="E292">
         <v>1</v>
       </c>
       <c r="F292">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Bloqueios Judiciais</t>
+          <t>Educação Ambiental</t>
         </is>
       </c>
       <c r="B293">
         <v>2025</v>
       </c>
       <c r="C293">
-        <v>2647554.45</v>
+        <v>2647738.2</v>
       </c>
       <c r="D293">
-        <v>0</v>
+        <v>2647738.2</v>
       </c>
       <c r="E293">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F293">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Mês do Hip Hop</t>
+          <t>Bloqueios Judiciais</t>
         </is>
       </c>
       <c r="B294">
         <v>2025</v>
       </c>
       <c r="C294">
-        <v>2563760</v>
+        <v>2647554.45</v>
       </c>
       <c r="D294">
-        <v>2563760</v>
+        <v>0</v>
       </c>
       <c r="E294">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F294">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Ampliação, Reforma e Requalificação das Instalações para a Guarda Civil Metropolitana</t>
+          <t>Mês do Hip Hop</t>
         </is>
       </c>
       <c r="B295">
         <v>2025</v>
       </c>
       <c r="C295">
-        <v>2550571.92</v>
+        <v>2563760</v>
       </c>
       <c r="D295">
-        <v>2550571.92</v>
+        <v>2563760</v>
       </c>
       <c r="E295">
         <v>1</v>
       </c>
       <c r="F295">
-        <v>3</v>
+        <v>26</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Ações de Difusão Cultural do Theatro Municipal - Programação Artística</t>
+          <t>Ampliação, Reforma e Requalificação das Instalações para a Guarda Civil Metropolitana</t>
         </is>
       </c>
       <c r="B296">
         <v>2025</v>
       </c>
       <c r="C296">
-        <v>2509158</v>
+        <v>2550571.92</v>
       </c>
       <c r="D296">
-        <v>2509158</v>
+        <v>2550571.92</v>
       </c>
       <c r="E296">
         <v>1</v>
       </c>
       <c r="F296">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Manutenção e Operação de Equipamentos Públicos Voltados ao Atendimento de Imigrantes</t>
+          <t>Ações de Difusão Cultural do Theatro Municipal - Programação Artística</t>
         </is>
       </c>
       <c r="B297">
         <v>2025</v>
       </c>
       <c r="C297">
-        <v>2428734.59</v>
+        <v>2509158</v>
       </c>
       <c r="D297">
-        <v>2428734.59</v>
+        <v>2509158</v>
       </c>
       <c r="E297">
         <v>1</v>
@@ -6901,325 +6902,326 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Políticas, Programas e Ações para Pessoa Idosa</t>
+          <t>Manutenção e Operação de Equipamentos Públicos Voltados ao Atendimento de Imigrantes</t>
         </is>
       </c>
       <c r="B298">
         <v>2025</v>
       </c>
       <c r="C298">
-        <v>2412231.29</v>
+        <v>2428734.59</v>
       </c>
       <c r="D298">
-        <v>2412231.29</v>
+        <v>2428734.59</v>
       </c>
       <c r="E298">
         <v>1</v>
       </c>
       <c r="F298">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Programação de Atividades Culturais do Centro Cultural São Paulo</t>
+          <t>Políticas, Programas e Ações para Pessoa Idosa</t>
         </is>
       </c>
       <c r="B299">
         <v>2025</v>
       </c>
       <c r="C299">
-        <v>2321714.02</v>
+        <v>2412231.29</v>
       </c>
       <c r="D299">
-        <v>2321714.02</v>
+        <v>2412231.29</v>
       </c>
       <c r="E299">
         <v>1</v>
       </c>
       <c r="F299">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Construção e Implantação do Descomplica SP</t>
+          <t>Programação de Atividades Culturais do Centro Cultural São Paulo</t>
         </is>
       </c>
       <c r="B300">
         <v>2025</v>
       </c>
       <c r="C300">
-        <v>2265363.1</v>
+        <v>2321714.02</v>
       </c>
       <c r="D300">
-        <v>2265363.1</v>
+        <v>2321714.02</v>
       </c>
       <c r="E300">
         <v>1</v>
       </c>
       <c r="F300">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Programa de Iniciação Artística para a Primeira Infância - PIAPI</t>
+          <t>Construção e Implantação do Descomplica SP</t>
         </is>
       </c>
       <c r="B301">
         <v>2025</v>
       </c>
       <c r="C301">
-        <v>2092744.64</v>
+        <v>2265363.1</v>
       </c>
       <c r="D301">
-        <v>2092744.64</v>
+        <v>2265363.1</v>
       </c>
       <c r="E301">
         <v>1</v>
       </c>
       <c r="F301">
-        <v>23</v>
+        <v>8</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Operação e Manutenção do Portal da PMSP_x000D_</t>
+          <t>Programa de Iniciação Artística para a Primeira Infância - PIAPI</t>
         </is>
       </c>
       <c r="B302">
         <v>2025</v>
       </c>
       <c r="C302">
-        <v>2063226.26</v>
+        <v>2092744.64</v>
       </c>
       <c r="D302">
-        <v>0</v>
+        <v>2092744.64</v>
       </c>
       <c r="E302">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F302">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Apoio à Cultura Negra</t>
+          <t xml:space="preserve">Operação e Manutenção do Portal da PMSP_x000D__x000D_
+</t>
         </is>
       </c>
       <c r="B303">
         <v>2025</v>
       </c>
       <c r="C303">
-        <v>2015229.58</v>
+        <v>2063226.26</v>
       </c>
       <c r="D303">
-        <v>2015229.58</v>
+        <v>0</v>
       </c>
       <c r="E303">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F303">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Programa Mãos e Mentes Paulistanas</t>
+          <t>Apoio à Cultura Negra</t>
         </is>
       </c>
       <c r="B304">
         <v>2025</v>
       </c>
       <c r="C304">
-        <v>2014786.25</v>
+        <v>2015229.58</v>
       </c>
       <c r="D304">
-        <v>0</v>
+        <v>2015229.58</v>
       </c>
       <c r="E304">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F304">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Manutenção e Operação do Programa de Proteção Escolar</t>
+          <t>Programa Mãos e Mentes Paulistanas</t>
         </is>
       </c>
       <c r="B305">
         <v>2025</v>
       </c>
       <c r="C305">
-        <v>1951606.58</v>
+        <v>2014786.25</v>
       </c>
       <c r="D305">
-        <v>1951606.58</v>
+        <v>0</v>
       </c>
       <c r="E305">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F305">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Difusão, Fomento e Pesquisas Aplicadas para a Gestão Participativa e Desenvolvimento Urbano</t>
+          <t>Manutenção e Operação do Programa de Proteção Escolar</t>
         </is>
       </c>
       <c r="B306">
         <v>2025</v>
       </c>
       <c r="C306">
-        <v>1903309.64</v>
+        <v>1951606.58</v>
       </c>
       <c r="D306">
-        <v>1903309.64</v>
+        <v>1951606.58</v>
       </c>
       <c r="E306">
         <v>1</v>
       </c>
       <c r="F306">
-        <v>3</v>
+        <v>32</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Ações de Desenvolvimento Social</t>
+          <t>Difusão, Fomento e Pesquisas Aplicadas para a Gestão Participativa e Desenvolvimento Urbano</t>
         </is>
       </c>
       <c r="B307">
         <v>2025</v>
       </c>
       <c r="C307">
-        <v>1889901.25</v>
+        <v>1903309.64</v>
       </c>
       <c r="D307">
-        <v>0</v>
+        <v>1903309.64</v>
       </c>
       <c r="E307">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F307">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Vivência Prática de Gestão de Documentos</t>
+          <t>Ações de Desenvolvimento Social</t>
         </is>
       </c>
       <c r="B308">
         <v>2025</v>
       </c>
       <c r="C308">
-        <v>1773320.01</v>
+        <v>1889901.25</v>
       </c>
       <c r="D308">
-        <v>1359277.92</v>
+        <v>0</v>
       </c>
       <c r="E308">
-        <v>0.7665158642178745</v>
+        <v>0</v>
       </c>
       <c r="F308">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Manutenção e Operação dos Conselhos e Espaços Participativos Municipais</t>
+          <t>Vivência Prática de Gestão de Documentos</t>
         </is>
       </c>
       <c r="B309">
         <v>2025</v>
       </c>
       <c r="C309">
-        <v>1767740.75</v>
+        <v>1773320.01</v>
       </c>
       <c r="D309">
-        <v>1280553.81</v>
+        <v>1359277.92</v>
       </c>
       <c r="E309">
-        <v>0.7244013637180678</v>
+        <v>0.7665158642178745</v>
       </c>
       <c r="F309">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Ações de Cooperação para o Desenvolvimento Sustentável</t>
+          <t>Manutenção e Operação dos Conselhos e Espaços Participativos Municipais</t>
         </is>
       </c>
       <c r="B310">
         <v>2025</v>
       </c>
       <c r="C310">
-        <v>1730272.02</v>
+        <v>1767740.75</v>
       </c>
       <c r="D310">
-        <v>965575.03</v>
+        <v>1280553.81</v>
       </c>
       <c r="E310">
-        <v>0.5580481096839328</v>
+        <v>0.7244013637180678</v>
       </c>
       <c r="F310">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Políticas, Programas e Ações para Educação em Direitos Humanos e Promoção do Direito à Cidade</t>
+          <t>Ações de Cooperação para o Desenvolvimento Sustentável</t>
         </is>
       </c>
       <c r="B311">
         <v>2025</v>
       </c>
       <c r="C311">
-        <v>1695936.32</v>
+        <v>1730272.02</v>
       </c>
       <c r="D311">
-        <v>1695936.32</v>
+        <v>965575.03</v>
       </c>
       <c r="E311">
-        <v>1</v>
+        <v>0.5580481096839328</v>
       </c>
       <c r="F311">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Ampliação, Reforma e Requalificação de Equipamentos de Saúde Animal</t>
+          <t>Projeto de Intervenção Urbana - PIU</t>
         </is>
       </c>
       <c r="B312">
         <v>2025</v>
       </c>
       <c r="C312">
-        <v>1483452.83</v>
+        <v>1711211.15</v>
       </c>
       <c r="D312">
-        <v>1483452.83</v>
+        <v>1711211.15</v>
       </c>
       <c r="E312">
         <v>1</v>
@@ -7231,102 +7233,102 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Programa Vocacional</t>
+          <t>Políticas, Programas e Ações para Educação em Direitos Humanos e Promoção do Direito à Cidade</t>
         </is>
       </c>
       <c r="B313">
         <v>2025</v>
       </c>
       <c r="C313">
-        <v>1477259.44</v>
+        <v>1695936.32</v>
       </c>
       <c r="D313">
-        <v>1477259.44</v>
+        <v>1695936.32</v>
       </c>
       <c r="E313">
         <v>1</v>
       </c>
       <c r="F313">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Ações de Educação de Trânsito</t>
+          <t>Ampliação, Reforma e Requalificação de Equipamentos de Saúde Animal</t>
         </is>
       </c>
       <c r="B314">
         <v>2025</v>
       </c>
       <c r="C314">
-        <v>1474107.13</v>
+        <v>1483452.83</v>
       </c>
       <c r="D314">
-        <v>0</v>
+        <v>1483452.83</v>
       </c>
       <c r="E314">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F314">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Acordos Judiciais ou Administrativos</t>
+          <t>Programa Vocacional</t>
         </is>
       </c>
       <c r="B315">
         <v>2025</v>
       </c>
       <c r="C315">
-        <v>1337524.34</v>
+        <v>1477259.44</v>
       </c>
       <c r="D315">
-        <v>0</v>
+        <v>1477259.44</v>
       </c>
       <c r="E315">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F315">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Programa Aldeias</t>
+          <t>Ações de Educação de Trânsito</t>
         </is>
       </c>
       <c r="B316">
         <v>2025</v>
       </c>
       <c r="C316">
-        <v>1199999.96</v>
+        <v>1474107.13</v>
       </c>
       <c r="D316">
-        <v>1199999.96</v>
+        <v>0</v>
       </c>
       <c r="E316">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F316">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Manutenção e Operação do Programa de Residência Jurídica</t>
+          <t>Acordos Judiciais ou Administrativos</t>
         </is>
       </c>
       <c r="B317">
         <v>2025</v>
       </c>
       <c r="C317">
-        <v>1144767.58</v>
+        <v>1337524.34</v>
       </c>
       <c r="D317">
         <v>0</v>
@@ -7341,350 +7343,350 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Fomento à Música</t>
+          <t>Programa Aldeias</t>
         </is>
       </c>
       <c r="B318">
         <v>2025</v>
       </c>
       <c r="C318">
-        <v>1135500</v>
+        <v>1199999.96</v>
       </c>
       <c r="D318">
-        <v>1135500</v>
+        <v>1199999.96</v>
       </c>
       <c r="E318">
         <v>1</v>
       </c>
       <c r="F318">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Manutenção e Operação de Unidades Educacionais - Centro Municipal de Capacitação e Treinamento (CMCT)</t>
+          <t>Manutenção e Operação do Programa de Residência Jurídica</t>
         </is>
       </c>
       <c r="B319">
         <v>2025</v>
       </c>
       <c r="C319">
-        <v>1127079.92</v>
+        <v>1144767.58</v>
       </c>
       <c r="D319">
-        <v>1127079.92</v>
+        <v>0</v>
       </c>
       <c r="E319">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F319">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Manutenção e Operação no Serviço de Guinchamento</t>
+          <t>Fomento à Música</t>
         </is>
       </c>
       <c r="B320">
         <v>2025</v>
       </c>
       <c r="C320">
-        <v>1126616.2</v>
+        <v>1135500</v>
       </c>
       <c r="D320">
-        <v>1126616.2</v>
+        <v>1135500</v>
       </c>
       <c r="E320">
         <v>1</v>
       </c>
       <c r="F320">
-        <v>32</v>
+        <v>9</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Fomento e Difusão do Forró</t>
+          <t>Manutenção e Operação de Unidades Educacionais - Centro Municipal de Capacitação e Treinamento (CMCT)</t>
         </is>
       </c>
       <c r="B321">
         <v>2025</v>
       </c>
       <c r="C321">
-        <v>1079100</v>
+        <v>1127137.82</v>
       </c>
       <c r="D321">
-        <v>1079100</v>
+        <v>1127137.82</v>
       </c>
       <c r="E321">
         <v>1</v>
       </c>
       <c r="F321">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Ações e Atividades Culturais da Biblioteca Mario de Andrade</t>
+          <t>Manutenção e Operação no Serviço de Guinchamento</t>
         </is>
       </c>
       <c r="B322">
         <v>2025</v>
       </c>
       <c r="C322">
-        <v>1058308.02</v>
+        <v>1126616.2</v>
       </c>
       <c r="D322">
-        <v>1058308.02</v>
+        <v>1126616.2</v>
       </c>
       <c r="E322">
         <v>1</v>
       </c>
       <c r="F322">
-        <v>3</v>
+        <v>32</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Ações e Atividades Culturais do Departamento do Patrimônio Histórico</t>
+          <t>Fomento e Difusão do Forró</t>
         </is>
       </c>
       <c r="B323">
         <v>2025</v>
       </c>
       <c r="C323">
-        <v>992147.87</v>
+        <v>1079100</v>
       </c>
       <c r="D323">
-        <v>992147.87</v>
+        <v>1079100</v>
       </c>
       <c r="E323">
         <v>1</v>
       </c>
       <c r="F323">
-        <v>32</v>
+        <v>12</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Circuito Cultural de São Paulo</t>
+          <t>Ações e Atividades Culturais da Biblioteca Mario de Andrade</t>
         </is>
       </c>
       <c r="B324">
         <v>2025</v>
       </c>
       <c r="C324">
-        <v>869500</v>
+        <v>1058308.02</v>
       </c>
       <c r="D324">
-        <v>869500</v>
+        <v>1058308.02</v>
       </c>
       <c r="E324">
         <v>1</v>
       </c>
       <c r="F324">
-        <v>22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Ampliação, Reforma e Requalificação de Posto do Corpo de Bombeiros</t>
+          <t>Ações e Atividades Culturais do Departamento do Patrimônio Histórico</t>
         </is>
       </c>
       <c r="B325">
         <v>2025</v>
       </c>
       <c r="C325">
-        <v>830602.05</v>
+        <v>992147.87</v>
       </c>
       <c r="D325">
-        <v>0</v>
+        <v>992147.87</v>
       </c>
       <c r="E325">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F325">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Publicação de Editais e Outras Publicações Legais e de Interesse do Município</t>
+          <t>Circuito Cultural de São Paulo</t>
         </is>
       </c>
       <c r="B326">
         <v>2025</v>
       </c>
       <c r="C326">
-        <v>817734.03</v>
+        <v>869500</v>
       </c>
       <c r="D326">
-        <v>0</v>
+        <v>869500</v>
       </c>
       <c r="E326">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F326">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Fomento e Difusão do Reggae e da Cultura Rastafari</t>
+          <t>Ampliação, Reforma e Requalificação de Posto do Corpo de Bombeiros</t>
         </is>
       </c>
       <c r="B327">
         <v>2025</v>
       </c>
       <c r="C327">
-        <v>812692</v>
+        <v>830602.05</v>
       </c>
       <c r="D327">
-        <v>812692</v>
+        <v>0</v>
       </c>
       <c r="E327">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F327">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Ampliação, Reforma e Requalificação de Unidades de Conservação</t>
+          <t>Publicação de Editais e Outras Publicações Legais e de Interesse do Município</t>
         </is>
       </c>
       <c r="B328">
         <v>2025</v>
       </c>
       <c r="C328">
-        <v>799425.89</v>
+        <v>817734.03</v>
       </c>
       <c r="D328">
-        <v>799425.89</v>
+        <v>0</v>
       </c>
       <c r="E328">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F328">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Fomento e Difusão do Funk</t>
+          <t>Fomento e Difusão do Reggae e da Cultura Rastafari</t>
         </is>
       </c>
       <c r="B329">
         <v>2025</v>
       </c>
       <c r="C329">
-        <v>785300</v>
+        <v>812692</v>
       </c>
       <c r="D329">
-        <v>785300</v>
+        <v>812692</v>
       </c>
       <c r="E329">
         <v>1</v>
       </c>
       <c r="F329">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Manutenção e Operação do Centro Público de Economia Solidária e Direitos Humanos</t>
+          <t>Ampliação, Reforma e Requalificação de Unidades de Conservação</t>
         </is>
       </c>
       <c r="B330">
         <v>2025</v>
       </c>
       <c r="C330">
-        <v>767347.97</v>
+        <v>799425.89</v>
       </c>
       <c r="D330">
-        <v>767347.97</v>
+        <v>799425.89</v>
       </c>
       <c r="E330">
         <v>1</v>
       </c>
       <c r="F330">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Educação Paulistana Pode Mais - BID</t>
+          <t>Fomento e Difusão do Funk</t>
         </is>
       </c>
       <c r="B331">
         <v>2025</v>
       </c>
       <c r="C331">
-        <v>748083.13</v>
+        <v>785300</v>
       </c>
       <c r="D331">
-        <v>494508.13</v>
+        <v>785300</v>
       </c>
       <c r="E331">
-        <v>0.6610336607911477</v>
+        <v>1</v>
       </c>
       <c r="F331">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Política Municipal de Desenvolvimento Econômico</t>
+          <t>Manutenção e Operação do Centro Público de Economia Solidária e Direitos Humanos</t>
         </is>
       </c>
       <c r="B332">
         <v>2025</v>
       </c>
       <c r="C332">
-        <v>737094.55</v>
+        <v>767347.97</v>
       </c>
       <c r="D332">
-        <v>0</v>
+        <v>767347.97</v>
       </c>
       <c r="E332">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F332">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>BID II - Ampliação, Reforma e Requalificação de Equipamentos de Assistência Hospitalar</t>
+          <t>Educação Paulistana Pode Mais - BID</t>
         </is>
       </c>
       <c r="B333">
         <v>2025</v>
       </c>
       <c r="C333">
-        <v>718382.4400000001</v>
+        <v>748083.13</v>
       </c>
       <c r="D333">
-        <v>718382.4400000001</v>
+        <v>494508.13</v>
       </c>
       <c r="E333">
-        <v>1</v>
+        <v>0.6610336607911477</v>
       </c>
       <c r="F333">
         <v>2</v>
@@ -7693,14 +7695,14 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Restituição de Receitas Descontinuadas</t>
+          <t>Política Municipal de Desenvolvimento Econômico</t>
         </is>
       </c>
       <c r="B334">
         <v>2025</v>
       </c>
       <c r="C334">
-        <v>659534.8100000001</v>
+        <v>737094.55</v>
       </c>
       <c r="D334">
         <v>0</v>
@@ -7715,215 +7717,216 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Plano Municipal do Livro, Leitura, Literatura e Biblioteca (PMLLLB)</t>
+          <t>BID II - Ampliação, Reforma e Requalificação de Equipamentos de Assistência Hospitalar</t>
         </is>
       </c>
       <c r="B335">
         <v>2025</v>
       </c>
       <c r="C335">
-        <v>617593.34</v>
+        <v>718382.4400000001</v>
       </c>
       <c r="D335">
-        <v>617593.34</v>
+        <v>718382.4400000001</v>
       </c>
       <c r="E335">
         <v>1</v>
       </c>
       <c r="F335">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Implantação de Corredores de Ônibus Novos</t>
+          <t>Restituição de Receitas Descontinuadas</t>
         </is>
       </c>
       <c r="B336">
         <v>2025</v>
       </c>
       <c r="C336">
-        <v>559243.79</v>
+        <v>659534.8100000001</v>
       </c>
       <c r="D336">
-        <v>559243.79</v>
+        <v>0</v>
       </c>
       <c r="E336">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F336">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Território Hip Hop (Vocacional Hip Hop)</t>
+          <t>Plano Municipal do Livro, Leitura, Literatura e Biblioteca (PMLLLB)</t>
         </is>
       </c>
       <c r="B337">
         <v>2025</v>
       </c>
       <c r="C337">
-        <v>550550</v>
+        <v>617593.34</v>
       </c>
       <c r="D337">
-        <v>550550</v>
+        <v>617593.34</v>
       </c>
       <c r="E337">
         <v>1</v>
       </c>
       <c r="F337">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Centro de Referência da Dança</t>
+          <t>Implantação de Corredores de Ônibus Novos</t>
         </is>
       </c>
       <c r="B338">
         <v>2025</v>
       </c>
       <c r="C338">
-        <v>521552</v>
+        <v>559243.79</v>
       </c>
       <c r="D338">
-        <v>521552</v>
+        <v>559243.79</v>
       </c>
       <c r="E338">
         <v>1</v>
       </c>
       <c r="F338">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Gestão do Patrimônio Imobiliário Municipal</t>
+          <t>Território Hip Hop (Vocacional Hip Hop)</t>
         </is>
       </c>
       <c r="B339">
         <v>2025</v>
       </c>
       <c r="C339">
-        <v>515530.93</v>
+        <v>550550</v>
       </c>
       <c r="D339">
-        <v>420054.78</v>
+        <v>550550</v>
       </c>
       <c r="E339">
-        <v>0.8148003457328933</v>
+        <v>1</v>
       </c>
       <c r="F339">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Avança Saúde SP - Ampliação, Reforma e Requalificação de Equipamentos de Saúde_x000D_</t>
+          <t>Centro de Referência da Dança</t>
         </is>
       </c>
       <c r="B340">
         <v>2025</v>
       </c>
       <c r="C340">
-        <v>511078.86</v>
+        <v>521552</v>
       </c>
       <c r="D340">
-        <v>511078.86</v>
+        <v>521552</v>
       </c>
       <c r="E340">
         <v>1</v>
       </c>
       <c r="F340">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Políticas, Programas e Ações para Imigrantes e Promoção ao Trabalho Decente</t>
+          <t>Gestão do Patrimônio Imobiliário Municipal</t>
         </is>
       </c>
       <c r="B341">
         <v>2025</v>
       </c>
       <c r="C341">
-        <v>510000</v>
+        <v>515530.93</v>
       </c>
       <c r="D341">
-        <v>510000</v>
+        <v>420054.78</v>
       </c>
       <c r="E341">
-        <v>1</v>
+        <v>0.8148003457328933</v>
       </c>
       <c r="F341">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Centro de Memória do Circo</t>
+          <t xml:space="preserve">Avança Saúde SP - Ampliação, Reforma e Requalificação de Equipamentos de Saúde_x000D__x000D_
+</t>
         </is>
       </c>
       <c r="B342">
         <v>2025</v>
       </c>
       <c r="C342">
-        <v>506160</v>
+        <v>511078.86</v>
       </c>
       <c r="D342">
-        <v>506160</v>
+        <v>511078.86</v>
       </c>
       <c r="E342">
         <v>1</v>
       </c>
       <c r="F342">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Oficina nos Equipamentos Culturais</t>
+          <t>Políticas, Programas e Ações para Imigrantes e Promoção ao Trabalho Decente</t>
         </is>
       </c>
       <c r="B343">
         <v>2025</v>
       </c>
       <c r="C343">
-        <v>499534</v>
+        <v>510000</v>
       </c>
       <c r="D343">
-        <v>499534</v>
+        <v>510000</v>
       </c>
       <c r="E343">
         <v>1</v>
       </c>
       <c r="F343">
-        <v>26</v>
+        <v>3</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Qualificação e Transformação Urbanística - AIU-SCE - Lei 17.844/2022</t>
+          <t>Centro de Memória do Circo</t>
         </is>
       </c>
       <c r="B344">
         <v>2025</v>
       </c>
       <c r="C344">
-        <v>461471.56</v>
+        <v>506160</v>
       </c>
       <c r="D344">
-        <v>461471.56</v>
+        <v>506160</v>
       </c>
       <c r="E344">
         <v>1</v>
@@ -7935,39 +7938,39 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Construção e Implantação de Equipamentos de Saúde Animal</t>
+          <t>Oficina nos Equipamentos Culturais</t>
         </is>
       </c>
       <c r="B345">
         <v>2025</v>
       </c>
       <c r="C345">
-        <v>451115.2</v>
+        <v>499534</v>
       </c>
       <c r="D345">
-        <v>451115.2</v>
+        <v>499534</v>
       </c>
       <c r="E345">
         <v>1</v>
       </c>
       <c r="F345">
-        <v>1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Manutenção e Operação Semafórica</t>
+          <t>Construção e Implantação de Equipamentos de Saúde Animal</t>
         </is>
       </c>
       <c r="B346">
         <v>2025</v>
       </c>
       <c r="C346">
-        <v>448578.89</v>
+        <v>451115.2</v>
       </c>
       <c r="D346">
-        <v>448578.89</v>
+        <v>451115.2</v>
       </c>
       <c r="E346">
         <v>1</v>
@@ -7979,212 +7982,212 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Manutenção e Operação de Espaços Lúdicos e Educativos</t>
+          <t>Manutenção e Operação Semafórica</t>
         </is>
       </c>
       <c r="B347">
         <v>2025</v>
       </c>
       <c r="C347">
-        <v>432278.82</v>
+        <v>448578.89</v>
       </c>
       <c r="D347">
-        <v>432278.82</v>
+        <v>448578.89</v>
       </c>
       <c r="E347">
         <v>1</v>
       </c>
       <c r="F347">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Políticas, Programas e Ações para Promoção da Igualdade Racial</t>
+          <t>Manutenção e Operação de Espaços Lúdicos e Educativos</t>
         </is>
       </c>
       <c r="B348">
         <v>2025</v>
       </c>
       <c r="C348">
-        <v>416450</v>
+        <v>432278.82</v>
       </c>
       <c r="D348">
-        <v>416450</v>
+        <v>432278.82</v>
       </c>
       <c r="E348">
         <v>1</v>
       </c>
       <c r="F348">
-        <v>1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Pesquisa de Satisfação do Cidadão em Relação aos Serviços, Políticas e Programas</t>
+          <t>Políticas, Programas e Ações para Promoção da Igualdade Racial</t>
         </is>
       </c>
       <c r="B349">
         <v>2025</v>
       </c>
       <c r="C349">
-        <v>364095</v>
+        <v>416450</v>
       </c>
       <c r="D349">
-        <v>0</v>
+        <v>416450</v>
       </c>
       <c r="E349">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F349">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Pagamentos de Serviços Ambientais</t>
+          <t>Pesquisa de Satisfação do Cidadão em Relação aos Serviços, Políticas e Programas</t>
         </is>
       </c>
       <c r="B350">
         <v>2025</v>
       </c>
       <c r="C350">
-        <v>344740.91</v>
+        <v>364095</v>
       </c>
       <c r="D350">
-        <v>344740.91</v>
+        <v>0</v>
       </c>
       <c r="E350">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F350">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Programação de Atividades Culturais do Departamento dos Museus Municipais</t>
+          <t>Pagamentos de Serviços Ambientais</t>
         </is>
       </c>
       <c r="B351">
         <v>2025</v>
       </c>
       <c r="C351">
-        <v>331400</v>
+        <v>344740.91</v>
       </c>
       <c r="D351">
-        <v>331400</v>
+        <v>344740.91</v>
       </c>
       <c r="E351">
         <v>1</v>
       </c>
       <c r="F351">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Manutenção de Prédios Administrativos</t>
+          <t>Programação de Atividades Culturais do Departamento dos Museus Municipais</t>
         </is>
       </c>
       <c r="B352">
         <v>2025</v>
       </c>
       <c r="C352">
-        <v>301223.41</v>
+        <v>331400</v>
       </c>
       <c r="D352">
-        <v>287609.56</v>
+        <v>331400</v>
       </c>
       <c r="E352">
-        <v>0.9548048075015151</v>
+        <v>1</v>
       </c>
       <c r="F352">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Instalação de Polo Criativo na Chácara do Jockey</t>
+          <t>Manutenção de Prédios Administrativos</t>
         </is>
       </c>
       <c r="B353">
         <v>2025</v>
       </c>
       <c r="C353">
-        <v>196300</v>
+        <v>301223.41</v>
       </c>
       <c r="D353">
-        <v>196300</v>
+        <v>287609.56</v>
       </c>
       <c r="E353">
-        <v>1</v>
+        <v>0.9548048075015151</v>
       </c>
       <c r="F353">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Manutenção e Operação da Supervisão Geral das Juntas do Serviço Militar</t>
+          <t>Instalação de Polo Criativo na Chácara do Jockey</t>
         </is>
       </c>
       <c r="B354">
         <v>2025</v>
       </c>
       <c r="C354">
-        <v>193385.06</v>
+        <v>196300</v>
       </c>
       <c r="D354">
-        <v>193385.06</v>
+        <v>196300</v>
       </c>
       <c r="E354">
         <v>1</v>
       </c>
       <c r="F354">
-        <v>32</v>
+        <v>1</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Auxílio Destinado a Assistência Odontológica a Agentes Públicos - Lei nº 17.841/2022</t>
+          <t>Manutenção e Operação da Supervisão Geral das Juntas do Serviço Militar</t>
         </is>
       </c>
       <c r="B355">
         <v>2025</v>
       </c>
       <c r="C355">
-        <v>179574.93</v>
+        <v>193385.06</v>
       </c>
       <c r="D355">
-        <v>0</v>
+        <v>193385.06</v>
       </c>
       <c r="E355">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F355">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>FUMCAD - Multas Revertidas ao Fundo</t>
+          <t>Auxílio Destinado a Assistência Odontológica a Agentes Públicos - Lei nº 17.841/2022</t>
         </is>
       </c>
       <c r="B356">
         <v>2025</v>
       </c>
       <c r="C356">
-        <v>173268.85</v>
+        <v>179574.93</v>
       </c>
       <c r="D356">
         <v>0</v>
@@ -8199,105 +8202,105 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Conservação e Valorização de Acervos da Biblioteca Mário de Andrade</t>
+          <t>FUMCAD - Multas Revertidas ao Fundo</t>
         </is>
       </c>
       <c r="B357">
         <v>2025</v>
       </c>
       <c r="C357">
-        <v>156014.95</v>
+        <v>173268.85</v>
       </c>
       <c r="D357">
-        <v>156014.95</v>
+        <v>0</v>
       </c>
       <c r="E357">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F357">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Políticas, Programas e Ações para Povos Indígenas</t>
+          <t>Conservação e Valorização de Acervos da Biblioteca Mário de Andrade</t>
         </is>
       </c>
       <c r="B358">
         <v>2025</v>
       </c>
       <c r="C358">
-        <v>140811.8</v>
+        <v>156014.95</v>
       </c>
       <c r="D358">
-        <v>140811.8</v>
+        <v>156014.95</v>
       </c>
       <c r="E358">
         <v>1</v>
       </c>
       <c r="F358">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Ações de Monitoramento de Mudanças Climáticas</t>
+          <t>Políticas, Programas e Ações para Povos Indígenas</t>
         </is>
       </c>
       <c r="B359">
         <v>2025</v>
       </c>
       <c r="C359">
-        <v>112487.06</v>
+        <v>140811.8</v>
       </c>
       <c r="D359">
-        <v>0</v>
+        <v>140811.8</v>
       </c>
       <c r="E359">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F359">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Implantação de Projetos de Redesenho Urbano para Segurança Viária</t>
+          <t>Ações de Monitoramento de Mudanças Climáticas</t>
         </is>
       </c>
       <c r="B360">
         <v>2025</v>
       </c>
       <c r="C360">
-        <v>103540.04</v>
+        <v>112487.06</v>
       </c>
       <c r="D360">
-        <v>103540.04</v>
+        <v>0</v>
       </c>
       <c r="E360">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F360">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Políticas, Programas e Ações para Pessoas Egressas do Sistema Prisional</t>
+          <t>Implantação de Projetos de Redesenho Urbano para Segurança Viária</t>
         </is>
       </c>
       <c r="B361">
         <v>2025</v>
       </c>
       <c r="C361">
-        <v>100000</v>
+        <v>103540.04</v>
       </c>
       <c r="D361">
-        <v>100000</v>
+        <v>103540.04</v>
       </c>
       <c r="E361">
         <v>1</v>
@@ -8309,130 +8312,130 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Promoção da Transparência, do Acesso à Informação e do Controle Social</t>
+          <t>Políticas, Programas e Ações para Pessoas Egressas do Sistema Prisional</t>
         </is>
       </c>
       <c r="B362">
         <v>2025</v>
       </c>
       <c r="C362">
-        <v>88515.37</v>
+        <v>100000</v>
       </c>
       <c r="D362">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="E362">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F362">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Conservação e Valorização de Acervos do Departamento dos Museus Municipais</t>
+          <t>Promoção da Transparência, do Acesso à Informação e do Controle Social</t>
         </is>
       </c>
       <c r="B363">
         <v>2025</v>
       </c>
       <c r="C363">
-        <v>88497.34</v>
+        <v>88515.37</v>
       </c>
       <c r="D363">
-        <v>88497.34</v>
+        <v>0</v>
       </c>
       <c r="E363">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F363">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Ações e Atividades Culturais do Arquivo Histórico Municipal</t>
+          <t>Conservação e Valorização de Acervos do Departamento dos Museus Municipais</t>
         </is>
       </c>
       <c r="B364">
         <v>2025</v>
       </c>
       <c r="C364">
-        <v>77900</v>
+        <v>88497.34</v>
       </c>
       <c r="D364">
-        <v>77900</v>
+        <v>88497.34</v>
       </c>
       <c r="E364">
         <v>1</v>
       </c>
       <c r="F364">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Programa de Promoção da Imagem de São Paulo no Exterior</t>
+          <t>Ações e Atividades Culturais do Arquivo Histórico Municipal</t>
         </is>
       </c>
       <c r="B365">
         <v>2025</v>
       </c>
       <c r="C365">
-        <v>68806.8</v>
+        <v>78700</v>
       </c>
       <c r="D365">
-        <v>0</v>
+        <v>78700</v>
       </c>
       <c r="E365">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F365">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Ações do Programa Agentes de Governo Aberto</t>
+          <t>Programa de Promoção da Imagem de São Paulo no Exterior</t>
         </is>
       </c>
       <c r="B366">
         <v>2025</v>
       </c>
       <c r="C366">
-        <v>59683.09</v>
+        <v>68806.8</v>
       </c>
       <c r="D366">
-        <v>18531.01</v>
+        <v>0</v>
       </c>
       <c r="E366">
-        <v>0.3104901237519706</v>
+        <v>0</v>
       </c>
       <c r="F366">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Projetos e Ações de Apoio Habitacional</t>
+          <t>Ações do Programa Agentes de Governo Aberto</t>
         </is>
       </c>
       <c r="B367">
         <v>2025</v>
       </c>
       <c r="C367">
-        <v>42973.15</v>
+        <v>59683.09</v>
       </c>
       <c r="D367">
-        <v>42973.15</v>
+        <v>18531.01</v>
       </c>
       <c r="E367">
-        <v>1</v>
+        <v>0.3104901237519706</v>
       </c>
       <c r="F367">
         <v>1</v>
@@ -8441,61 +8444,61 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Manutenção e Operação do Herbário Municipal</t>
+          <t>Projetos e Ações de Apoio Habitacional</t>
         </is>
       </c>
       <c r="B368">
         <v>2025</v>
       </c>
       <c r="C368">
-        <v>42496.08</v>
+        <v>42973.15</v>
       </c>
       <c r="D368">
-        <v>42496.08</v>
+        <v>42973.15</v>
       </c>
       <c r="E368">
         <v>1</v>
       </c>
       <c r="F368">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Corredor Aricanduva - Fortalecimento Institucional - 3.3</t>
+          <t>Manutenção e Operação do Herbário Municipal</t>
         </is>
       </c>
       <c r="B369">
         <v>2025</v>
       </c>
       <c r="C369">
-        <v>40730</v>
+        <v>42496.08</v>
       </c>
       <c r="D369">
-        <v>40730</v>
+        <v>42496.08</v>
       </c>
       <c r="E369">
         <v>1</v>
       </c>
       <c r="F369">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Corredor Aricanduva - Controles Internos - 3.2</t>
+          <t>Corredor Aricanduva - Fortalecimento Institucional - 3.3</t>
         </is>
       </c>
       <c r="B370">
         <v>2025</v>
       </c>
       <c r="C370">
-        <v>39900</v>
+        <v>40730</v>
       </c>
       <c r="D370">
-        <v>39900</v>
+        <v>40730</v>
       </c>
       <c r="E370">
         <v>1</v>
@@ -8507,17 +8510,17 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Corredor Aricanduva - Acompanhamento Ambiental e Social - 1.5</t>
+          <t>Corredor Aricanduva - Controles Internos - 3.2</t>
         </is>
       </c>
       <c r="B371">
         <v>2025</v>
       </c>
       <c r="C371">
-        <v>26250</v>
+        <v>39900</v>
       </c>
       <c r="D371">
-        <v>26250</v>
+        <v>39900</v>
       </c>
       <c r="E371">
         <v>1</v>
@@ -8529,36 +8532,36 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Comunicação e Orientação na Valorização e Cuidado na Primeira Infância</t>
+          <t>Corredor Aricanduva - Acompanhamento Ambiental e Social - 1.5</t>
         </is>
       </c>
       <c r="B372">
         <v>2025</v>
       </c>
       <c r="C372">
-        <v>13420</v>
+        <v>26250</v>
       </c>
       <c r="D372">
-        <v>0</v>
+        <v>26250</v>
       </c>
       <c r="E372">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F372">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Manutenção e Operação do Programa de Pós-Graduação</t>
+          <t>Comunicação e Orientação na Valorização e Cuidado na Primeira Infância</t>
         </is>
       </c>
       <c r="B373">
         <v>2025</v>
       </c>
       <c r="C373">
-        <v>13393.92</v>
+        <v>13420</v>
       </c>
       <c r="D373">
         <v>0</v>
@@ -8573,14 +8576,14 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Fiscalização, Monitoramento e Controle Ambiental</t>
+          <t>Manutenção e Operação do Programa de Pós-Graduação</t>
         </is>
       </c>
       <c r="B374">
         <v>2025</v>
       </c>
       <c r="C374">
-        <v>12000</v>
+        <v>13393.92</v>
       </c>
       <c r="D374">
         <v>0</v>
@@ -8595,16 +8598,19 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Ampliação, Reforma e Requalificação de Edificação da Câmara Municipal de São Paulo</t>
+          <t>Fiscalização, Monitoramento e Controle Ambiental</t>
         </is>
       </c>
       <c r="B375">
         <v>2025</v>
       </c>
       <c r="C375">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="D375">
+        <v>0</v>
+      </c>
+      <c r="E375">
         <v>0</v>
       </c>
       <c r="F375">
@@ -8614,7 +8620,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Ampliação, Reforma e Requalificação de Edificação do Tribunal de Contas do Município</t>
+          <t>Ampliação, Reforma e Requalificação de Edificação da Câmara Municipal de São Paulo</t>
         </is>
       </c>
       <c r="B376">
@@ -8633,7 +8639,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Ações de Vigilância Socioassistencial</t>
+          <t>Ampliação, Reforma e Requalificação de Edificação do Tribunal de Contas do Município</t>
         </is>
       </c>
       <c r="B377">
@@ -8652,7 +8658,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Benefícios Eventuais</t>
+          <t>Ações de Vigilância Socioassistencial</t>
         </is>
       </c>
       <c r="B378">
@@ -8671,7 +8677,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Construção de Edificações da Câmara Municipal de São Paulo</t>
+          <t>Benefícios Eventuais</t>
         </is>
       </c>
       <c r="B379">
@@ -8690,7 +8696,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Contraprestação de Parceria Público-Privada (PPP) - Iluminação Pública</t>
+          <t>Construção de Edificações da Câmara Municipal de São Paulo</t>
         </is>
       </c>
       <c r="B380">
@@ -8709,7 +8715,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Câmara Municipal - Comunicação</t>
+          <t>Contraprestação de Parceria Público-Privada (PPP) - Iluminação Pública</t>
         </is>
       </c>
       <c r="B381">
@@ -8728,7 +8734,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Encargos Referentes a Pagamentos de Manutenção de Conta Corrente</t>
+          <t>Câmara Municipal - Comunicação</t>
         </is>
       </c>
       <c r="B382">
@@ -8747,7 +8753,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Escola de Gestão e Contas Públicas</t>
+          <t>Encargos Referentes a Pagamentos de Manutenção de Conta Corrente</t>
         </is>
       </c>
       <c r="B383">
@@ -8766,7 +8772,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Escola do Parlamento</t>
+          <t>Escola de Gestão e Contas Públicas</t>
         </is>
       </c>
       <c r="B384">
@@ -8785,7 +8791,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Expansão e Aperfeiçoamento das Atividades da CMSP</t>
+          <t>Escola do Parlamento</t>
         </is>
       </c>
       <c r="B385">
@@ -8804,7 +8810,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Expansão e Aperfeiçoamento das Atividades do TCM</t>
+          <t>Expansão e Aperfeiçoamento das Atividades da CMSP</t>
         </is>
       </c>
       <c r="B386">
@@ -8823,7 +8829,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Inserção das Famílias no Cadastro Único</t>
+          <t>Expansão e Aperfeiçoamento das Atividades do TCM</t>
         </is>
       </c>
       <c r="B387">
@@ -8842,7 +8848,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Manutenção e Operação de Edificação da Câmara Municipal de São Paulo</t>
+          <t>Inserção das Famílias no Cadastro Único</t>
         </is>
       </c>
       <c r="B388">
@@ -8861,7 +8867,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Modernização Semafórica</t>
+          <t>Manutenção e Operação de Edificação da Câmara Municipal de São Paulo</t>
         </is>
       </c>
       <c r="B389">
@@ -8880,7 +8886,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Plano de Contingência para Situações de Altas Temperaturas - Decreto nº 62.760/2023</t>
+          <t>Modernização Semafórica</t>
         </is>
       </c>
       <c r="B390">
@@ -8899,7 +8905,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Programa Reencontro</t>
+          <t>Plano de Contingência para Situações de Altas Temperaturas - Decreto nº 62.760/2023</t>
         </is>
       </c>
       <c r="B391">
@@ -8918,7 +8924,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Programa de Garantia de Renda Familiar Mínima</t>
+          <t>Programa Reencontro</t>
         </is>
       </c>
       <c r="B392">
@@ -8937,7 +8943,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Realização de Conferências Municipais Temáticas</t>
+          <t>Programa de Garantia de Renda Familiar Mínima</t>
         </is>
       </c>
       <c r="B393">
@@ -8956,7 +8962,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Servidores Comissionados no Hospital Serv. Públco Municipal - HSPM</t>
+          <t>Realização de Conferências Municipais Temáticas</t>
         </is>
       </c>
       <c r="B394">
@@ -8975,19 +8981,38 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
+          <t>Servidores Comissionados no Hospital Serv. Públco Municipal - HSPM</t>
+        </is>
+      </c>
+      <c r="B395">
+        <v>2025</v>
+      </c>
+      <c r="C395">
+        <v>0</v>
+      </c>
+      <c r="D395">
+        <v>0</v>
+      </c>
+      <c r="F395">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
           <t>Tarifa de Arrecadação de Multas</t>
         </is>
       </c>
-      <c r="B395">
-        <v>2025</v>
-      </c>
-      <c r="C395">
-        <v>0</v>
-      </c>
-      <c r="D395">
-        <v>0</v>
-      </c>
-      <c r="F395">
+      <c r="B396">
+        <v>2025</v>
+      </c>
+      <c r="C396">
+        <v>0</v>
+      </c>
+      <c r="D396">
+        <v>0</v>
+      </c>
+      <c r="F396">
         <v>0</v>
       </c>
     </row>

--- a/R Markdown/resultados/regionalizacao_acoes_2025.xlsx
+++ b/R Markdown/resultados/regionalizacao_acoes_2025.xlsx
@@ -1,21 +1,1238 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cloudprodamazhotmail-my.sharepoint.com/personal/gabrielmachado_prefeitura_sp_gov_br/Documents/Área de Trabalho/IDRGP/IDRGP-2025/R Markdown/resultados/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="5" documentId="11_CAC07DDF8F79A8D366075C52F37BD2724AC78BCD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{448AECE7-0D7F-4B65-BF71-6ED3920A11BA}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="401">
+  <si>
+    <t>descricao_proj_ativ</t>
+  </si>
+  <si>
+    <t>ano</t>
+  </si>
+  <si>
+    <t>valor_total</t>
+  </si>
+  <si>
+    <t>valor_regionalizado</t>
+  </si>
+  <si>
+    <t>perc_regionalizado</t>
+  </si>
+  <si>
+    <t>n_subpref</t>
+  </si>
+  <si>
+    <t>Aposentadorias e Pensões</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação em Atenção Básica, Especialidades e de Serviços Auxiliares de Diagnóstico e Terapia</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação em Atenção Hospitalar e de Urgência e Emergência</t>
+  </si>
+  <si>
+    <t>Compensações Tarifárias do Sistema de Ônibus</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação da Rede Parceira - Centro de Educação Infantil (CEI)</t>
+  </si>
+  <si>
+    <t>Administração da Unidade</t>
+  </si>
+  <si>
+    <t>Aporte do IRRF para cobertura do deficit atuarial do RPPS</t>
+  </si>
+  <si>
+    <t>Obrigações e Contribuições Patronais RPPS Educação</t>
+  </si>
+  <si>
+    <t>Condenações Judiciais - Créditos de Natureza Alimentar</t>
+  </si>
+  <si>
+    <t>Remuneração dos Profissionais da Educação Básica - Ensino Fundamental</t>
+  </si>
+  <si>
+    <t>Sistema Municipal de Regulação, Controle, Avaliação e Auditoria do SUS</t>
+  </si>
+  <si>
+    <t>Serviços de Limpeza Urbana - Varrição e Lavagem de Áreas Públicas</t>
+  </si>
+  <si>
+    <t>Recomposição de Depósitos Judiciais</t>
+  </si>
+  <si>
+    <t>Serviços de Engenharia de Tráfego</t>
+  </si>
+  <si>
+    <t>Eletrificação da frota de veículos do Sistema Municipal de Transporte Coletivo</t>
+  </si>
+  <si>
+    <t>Alimentação Escolar</t>
+  </si>
+  <si>
+    <t>Programa Pode Entrar</t>
+  </si>
+  <si>
+    <t>Obrigações e Contribuições Patronais</t>
+  </si>
+  <si>
+    <t>Remuneração dos Profissionais da Educação Básica - Centro de Educação Infantil (CEI)</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Sistemas de Informação e Comunicação</t>
+  </si>
+  <si>
+    <t>Execução do Programa de Mananciais</t>
+  </si>
+  <si>
+    <t>Serviço da Dívida Pública Interna</t>
+  </si>
+  <si>
+    <t>Promoção de Campanhas e Eventos de Interesse do Município</t>
+  </si>
+  <si>
+    <t>Intervenções no Sistema de Drenagem</t>
+  </si>
+  <si>
+    <t>Contribuição Formação Patrimônio Servidor Público - PASEP</t>
+  </si>
+  <si>
+    <t>Condenações Judiciais - Outras Espécies</t>
+  </si>
+  <si>
+    <t>Administração de Material  Médico Hospitalar e Ambulatorial em Atenção Básica, Especialidades e Vigilância</t>
+  </si>
+  <si>
+    <t>Remuneração dos Profissionais da Educação Básica - Escola Municipal de Educação Infantil (EMEI)</t>
+  </si>
+  <si>
+    <t>Obrigações e Contribuições Patronais RPPS Saúde</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação em Atenção Básica, Especialidades e Vigilância da Assistência Farmacêutica</t>
+  </si>
+  <si>
+    <t>Concessão dos Serviços Divisíveis de Limpeza Urbana em Regime Público</t>
+  </si>
+  <si>
+    <t>Manutenção de Sistemas de Drenagem</t>
+  </si>
+  <si>
+    <t>Operação Tapa Buraco</t>
+  </si>
+  <si>
+    <t>Pavimentação e Recapeamento de Vias</t>
+  </si>
+  <si>
+    <t>Transporte Escolar - Ensino Fundamental</t>
+  </si>
+  <si>
+    <t>Recuperação e Reforço de Obras de Arte Especiais - OAE</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Centros Educacionais Unificados (CEU)</t>
+  </si>
+  <si>
+    <t>Construção de Unidades Habitacionais</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Unidades Educacionais - Escola Municipal de Ensino Fundamental (EMEF)</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Áreas Verdes e Vegetação Arbórea</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Parques Urbanos e Lineares</t>
+  </si>
+  <si>
+    <t>Ações Integradas de Segurança Pública - Operação Delegada - Convênio SSP SO</t>
+  </si>
+  <si>
+    <t>Políticas, Programas e Ações de Subsistência, Segurança Alimentar e Nutricional</t>
+  </si>
+  <si>
+    <t>Aquisição de Materiais, Equipamentos e Serviços de Informação e Comunicação</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Equipamentos de Proteção Social Especial à População em Situação de Rua</t>
+  </si>
+  <si>
+    <t>Administração de Material Médico Hospitalar em Atenção Hospitalar, de Urgência e Emergência</t>
+  </si>
+  <si>
+    <t>Transporte Escolar - Educação Infantil</t>
+  </si>
+  <si>
+    <t>Intervenções no Sistema Viário</t>
+  </si>
+  <si>
+    <t>Ampliação, Reforma e Requalificação de Equipamentos em Atenção Hospitalar e de Urgência e Emergência</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação do Sistema Municipal de Transporte Público</t>
+  </si>
+  <si>
+    <t>Programação de Atividades Culturais</t>
+  </si>
+  <si>
+    <t>Parceria Público-Privada (PPP) - CEU</t>
+  </si>
+  <si>
+    <t>Urbanização de Favelas</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação do Programa de Estágios</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Escolas Municipais de Educação Infantil (EMEI)</t>
+  </si>
+  <si>
+    <t>Publicidade Institucional</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Equipamentos de Convivência e Fortalecimento de Vínculos para Crianças e Adolescentes</t>
+  </si>
+  <si>
+    <t>Fornecimento de Uniformes-Educação Fundamental</t>
+  </si>
+  <si>
+    <t>Transporte de Pessoas com Deficiência ou Mobilidade Reduzida - ATENDE</t>
+  </si>
+  <si>
+    <t>Sistema de Remuneração Variável</t>
+  </si>
+  <si>
+    <t>Contraprestação de Parceria Público-Privada (PPP) - Terminais Urbanos</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Equipamentos de Proteção Social Especial a Crianças, Adolescentes e Jovens em Risco Social</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Vigilância em Saúde</t>
+  </si>
+  <si>
+    <t>Transferência de Recursos Financeiros para as Unidades Educacionais - Ensino Fundamental</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Centros de Educação Infantil (CEI)</t>
+  </si>
+  <si>
+    <t>Ampliação, Reforma e Requalificação de Equipamentos de Atenção Básica e Especialidades</t>
+  </si>
+  <si>
+    <t>Fornecimento de Material Escolar-Educação Infantil</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação no Serviço de Guias e Sarjetas (Vias e Logradouros)</t>
+  </si>
+  <si>
+    <t>Precatórios Pagos com Rendimentos dos Depósitos do Regime Especial</t>
+  </si>
+  <si>
+    <t>Incentivo à Prática de Esportes</t>
+  </si>
+  <si>
+    <t>Condenações Judiciais - Créditos de Pequeno Valor</t>
+  </si>
+  <si>
+    <t>Manutenção de Vias e Áreas Públicas</t>
+  </si>
+  <si>
+    <t>Programa Nacional de Alimentação Escolar - PNAE/ FNDE</t>
+  </si>
+  <si>
+    <t>Ampliação, Reforma e Requalificação do Autódromo de Interlagos</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação da Sinalização do Sistema Viário</t>
+  </si>
+  <si>
+    <t>Capacitação, Formação e Aperfeiçoamento dos Trabalhadores</t>
+  </si>
+  <si>
+    <t>Remuneração dos Profissionais da Educação Básica - Centro Municipal de Educação Infantil( CEMEI)</t>
+  </si>
+  <si>
+    <t>Intervenção, Urbanização e Melhoria de Bairros - Plano de Obras das Subprefeituras</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Equipamentos Esportivos</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação do Controle e Fiscalização de Tráfego</t>
+  </si>
+  <si>
+    <t>Leve-Leite</t>
+  </si>
+  <si>
+    <t>Ações de Apoio à Educação Especial</t>
+  </si>
+  <si>
+    <t>Ações de Difusão Cultural do Theatro Municipal - Grupos Artísticos, Técnicos e Administrativos</t>
+  </si>
+  <si>
+    <t>Ampliação, Reforma e Requalificação de Escola Municipal de Ensino Fundamental (EMEF)</t>
+  </si>
+  <si>
+    <t>Fornecimento de Uniformes-Educação Infantil</t>
+  </si>
+  <si>
+    <t>Ampliação, Reforma e Requalificação de Equipamentos Esportivos</t>
+  </si>
+  <si>
+    <t>Transferência de Recursos Financeiros para as Unidades Educacionais - Educação Infantil</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Terminais de Ônibus</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Serviço de Atendimento Médico de Urgência (SAMU)</t>
+  </si>
+  <si>
+    <t>Serviço de Moradia Transitória</t>
+  </si>
+  <si>
+    <t>Encargos pela Manutenção do Fundo de Depósitos Judiciais nas quais o Município é Parte</t>
+  </si>
+  <si>
+    <t>Intervenções na Área de Mobilidade Urbana</t>
+  </si>
+  <si>
+    <t>Modernização, operação e manutenção dos canais SP156</t>
+  </si>
+  <si>
+    <t>Ações de Fiscalização do Comércio Ilegal</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Equipamentos Intergeracionais de Convivência e Fortalecimento de Vínculos</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Redes de Monitoramento Remoto para Segurança Urbana</t>
+  </si>
+  <si>
+    <t>Parceria Público Privada - Habitação</t>
+  </si>
+  <si>
+    <t>Fornecimento de Material Escolar-Ensino Fundamental</t>
+  </si>
+  <si>
+    <t>Ampliação, Reforma e Requalificação de Escolas Municipais de Educação Infantil (EMEI)</t>
+  </si>
+  <si>
+    <t>Qualificação Profissional e Empreendedora</t>
+  </si>
+  <si>
+    <t>Ampliação, Reforma e Requalificação de Parques Urbanos e Lineares</t>
+  </si>
+  <si>
+    <t>Construção e Implantação de Equipamentos de Atenção Básica e Especialidades</t>
+  </si>
+  <si>
+    <t>Implantação e Construção de Terminais de Ônibus</t>
+  </si>
+  <si>
+    <t>Regularização Fundiária</t>
+  </si>
+  <si>
+    <t>Programa de Incentivo Fiscal Relacionado à Arena Corinthians</t>
+  </si>
+  <si>
+    <t>Inspeção de Obras de Artes Especiais - OAE</t>
+  </si>
+  <si>
+    <t>Servidores Comissionados em Outras Entidades</t>
+  </si>
+  <si>
+    <t>Serviço da Dívida Pública Externa</t>
+  </si>
+  <si>
+    <t>Implantação e Construção de Corredores de Ônibus</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação da Guarda Civil Metropolitana</t>
+  </si>
+  <si>
+    <t>Ações e Materiais de Apoio Didático-Pedagógico Educacional</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Corredores de Ônibus</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação da Atenção Hospitalar da Assistência Farmacêutica</t>
+  </si>
+  <si>
+    <t>Benefício Assistencial - Lei 17.969/2023</t>
+  </si>
+  <si>
+    <t>Administração da Carteira Imobiliária</t>
+  </si>
+  <si>
+    <t>Operação e Manutenção da Agência São Paulo de Desenvolvimento - ADESAMPA</t>
+  </si>
+  <si>
+    <t>Coleta, Transporte, Tratamento e Dest. Final Resíduos Sólidos Inertes</t>
+  </si>
+  <si>
+    <t>Conservação e Manutenção de Unidades Educacionais - Educação Infantil</t>
+  </si>
+  <si>
+    <t>Ações de Educação Integral</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Posto do Corpo de Bombeiros</t>
+  </si>
+  <si>
+    <t>Ações Permanentes de Promoção dos Direitos da Criança e do Adolescente</t>
+  </si>
+  <si>
+    <t>Fomento às Linguagens Artísticas</t>
+  </si>
+  <si>
+    <t>Programação da Virada Cultural</t>
+  </si>
+  <si>
+    <t>Ampliação, Reforma e Requalificação de Centros Educacionais Unificados (CEU)</t>
+  </si>
+  <si>
+    <t>Suporte e Manutenção da Coordenação de Imprensa</t>
+  </si>
+  <si>
+    <t>Desenvolvimento de Estudos, Projetos  e Instrumentos de Políticas Urbanas</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação das Praças Digitais</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação do Descomplica SP</t>
+  </si>
+  <si>
+    <t>Administração dos Conselhos Tutelares</t>
+  </si>
+  <si>
+    <t>Capacitação, Formação e Aperfeiçoamento de Servidores</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Equipamentos de Proteção Social Especial à População Idosa</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Ciclovias, Ciclofaixas e Ciclorrotas</t>
+  </si>
+  <si>
+    <t>Armazém Solidário</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Equipamentos de Proteção Social Especial à Pessoa com Deficiência</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Centros Culturais e Teatros</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Equipamentos de Proteção Social Básica às Famílias</t>
+  </si>
+  <si>
+    <t>Acompanhamento das Aprendizagens e Permanência Escolar</t>
+  </si>
+  <si>
+    <t>Construção de Centros de Educação Infantil - CEI</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Bibliotecas Públicas</t>
+  </si>
+  <si>
+    <t>Transporte Escolar - Educação Especial</t>
+  </si>
+  <si>
+    <t>Apoio às Ações Municipais de Turismo</t>
+  </si>
+  <si>
+    <t>Intervenções em Próprios Municipais</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação em Serviços de Saúde Animal</t>
+  </si>
+  <si>
+    <t>Conservação e Manutenção de Unidades Educacionais - Ensino Fundamental</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Equipamentos Públicos Voltados ao Atendimento de Mulheres</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Ciclofaixas de Lazer</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Unidades de Conservação</t>
+  </si>
+  <si>
+    <t>Ampliação, Reforma e Requalificação de Centros de Educação Infantil (CEI)</t>
+  </si>
+  <si>
+    <t>Operação e Manutenção da São Paulo Investimentos e Negócios</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Casas de Cultura</t>
+  </si>
+  <si>
+    <t>Ampliação, Reforma e Requalificação da Avenida Santo Amaro</t>
+  </si>
+  <si>
+    <t>Políticas de Audiovisual</t>
+  </si>
+  <si>
+    <t>Construção e Implantação de Equipamentos em Atenção Hospitalar e de Urgência e Emergência</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Bilheterias e Postos de Atendimento do Bilhete Único</t>
+  </si>
+  <si>
+    <t>Projetos para Inclusão da Pessoa com Deficiência</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Equipamentos de Convivência e Fortalecimento de Vínculos para a Pessoa Idosa</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação dos Serviços de DST / AIDS</t>
+  </si>
+  <si>
+    <t>Programa Municipal de Apoio a Projetos Culturais (PRO-MAC)</t>
+  </si>
+  <si>
+    <t>Aposentadoria Complementar aos Servidores da São Paulo Transporte S/A</t>
+  </si>
+  <si>
+    <t>Construção de Escolas Municipais de Educação Infantil (EMEI)</t>
+  </si>
+  <si>
+    <t>Ações de Melhorias para Administração Fazendária</t>
+  </si>
+  <si>
+    <t>Centro Municipal para Pessoas com Transtorno do Espectro Autista</t>
+  </si>
+  <si>
+    <t>Ações de Desestatização</t>
+  </si>
+  <si>
+    <t>Compensação Financeira - Outros Fundos de Previdência</t>
+  </si>
+  <si>
+    <t>Contraprestação de Parceria Público-Privada (PPP) - CEUs</t>
+  </si>
+  <si>
+    <t>Eventos Educacionais, Culturais e Esportivos nos Centros Educacionais Unificados</t>
+  </si>
+  <si>
+    <t>Programação da Virada Esportiva</t>
+  </si>
+  <si>
+    <t>Ampliação, Reforma e Requalificação de Clube da Comunidade (CDC)</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Centros Municipais de Educação Infantil(CEMEI)</t>
+  </si>
+  <si>
+    <t>Escola Municipal de Educação Artística - EMIA</t>
+  </si>
+  <si>
+    <t>Administração do Edifício Matarazzo</t>
+  </si>
+  <si>
+    <t>Ações de formação das Escolas de Música e Dança do Theatro Municipal e da Praça das Artes</t>
+  </si>
+  <si>
+    <t>Encargos Referentes a Arrecadação</t>
+  </si>
+  <si>
+    <t>Políticas, Programas e Ações para Juventude</t>
+  </si>
+  <si>
+    <t>Construção de Ciclovias, Ciclofaixas e Ciclorrotas</t>
+  </si>
+  <si>
+    <t>Fomento à Cooperação, Parcerias e Captação de Investimentos Internacionais</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação dos Equipamentos Públicos Voltados ao Atendimento Inclusivo</t>
+  </si>
+  <si>
+    <t>Preservação do Patrimônio Histórico, Artístico, Cultural e Arqueológico</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação do Sistema de Transporte Público Hidroviário</t>
+  </si>
+  <si>
+    <t>Qualificação e Transformação Urbanística - AIU-SCE - Lei 17.844/2022</t>
+  </si>
+  <si>
+    <t>Políticas, Programas e Ações para a População em Situação de Rua</t>
+  </si>
+  <si>
+    <t>Manutenção de Unidades Habitacionais</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação do Centro Cultural São Paulo</t>
+  </si>
+  <si>
+    <t>Ampliação, Reforma e Requalificação de Unidades Habitacionais</t>
+  </si>
+  <si>
+    <t>Apoio e Suporte Técnico para o Desenvolvimento de Ações Pertinentes à Fiscalização e Escrituração de Certificados de Potencial Adicional de Construção - CEPACs</t>
+  </si>
+  <si>
+    <t>Lei de Fomento ao Teatro</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Equipamentos do Departamento dos Museus Municipais</t>
+  </si>
+  <si>
+    <t>Transferência de Recursos Financeiros para as Unidades Educacionais - Centro Educacional Unificado (CEU)</t>
+  </si>
+  <si>
+    <t>Desenvolvimento de Sistemas de Informação e Comunicação</t>
+  </si>
+  <si>
+    <t>Promoção da Arborização Urbana</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Centro de Referência de Segurança Alimentar e Nutricional</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação dos Pólos Regionais de Esporte</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Praças, Canteiros Centrais e Remanescentes</t>
+  </si>
+  <si>
+    <t>Implantação de Estrutura Turística no Triângulo Histórico</t>
+  </si>
+  <si>
+    <t>Operação e Manutenção de Unidade da Fundação Paulistana - FPETC</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Equipamentos Culturais</t>
+  </si>
+  <si>
+    <t>Programa Saúde na Escola</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Telecentros</t>
+  </si>
+  <si>
+    <t>Construção e Implantação de Parques Urbanos e Lineares</t>
+  </si>
+  <si>
+    <t>Fomento à Cultura da Periferia de São Paulo</t>
+  </si>
+  <si>
+    <t>Ampliação, Reforma e Requalificação de Prédios Administrativos</t>
+  </si>
+  <si>
+    <t>Construção e Implantação de Centros Educacionais Unificados (CEU)</t>
+  </si>
+  <si>
+    <t>Execução do Programa para a Valorização de Iniciativas Culturais</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Equipamentos de Proteção Jurídico Social</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Unidades Educacionais - Escola Municipal de Educação Fundamental e Médio (EMEFM)</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação da Rede Parceira - Alfabetização de Jovens e Adultos</t>
+  </si>
+  <si>
+    <t>Manutenção de Modalidades Desportivas do Centro Olímpico de Treinamento e Pesquisa (COTP)</t>
+  </si>
+  <si>
+    <t>Compensações Ambientais</t>
+  </si>
+  <si>
+    <t>Ações de Difusão Cultural do Theatro Municipal - Administrativos</t>
+  </si>
+  <si>
+    <t>Programa Jovem Monitor Cultural</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Viveiros de Produção</t>
+  </si>
+  <si>
+    <t>Operação e Manutenção dos Centros de Apoio ao Trabalho e Empreendedorismo</t>
+  </si>
+  <si>
+    <t>Ampliação, Reforma e Requalificação de Áreas Públicas</t>
+  </si>
+  <si>
+    <t>Corredor Aricanduva - Centro de Controle Operacional - COP - 2.1</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação da Biblioteca Mario de Andrade</t>
+  </si>
+  <si>
+    <t>Ações de Planejamento, Monitoramento e Avaliação de Políticas Públicas</t>
+  </si>
+  <si>
+    <t>Despesas Administrativas para Execução de Ações Judiciais - Processamento de Feitos</t>
+  </si>
+  <si>
+    <t>Obras e Serviços nas Áreas de Riscos Geológicos - Preventivas</t>
+  </si>
+  <si>
+    <t>Promoção à Saúde do Servidor Municipal</t>
+  </si>
+  <si>
+    <t>Subvenção e Contribuições a Entidades Culturais</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação do Programa Melhor em Casa</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação da Rede Parceira - Educação Especial</t>
+  </si>
+  <si>
+    <t>Políticas, Programas e Ações para Mulheres</t>
+  </si>
+  <si>
+    <t>Ampliação, Reforma e Requalificação de Equipamentos Culturais</t>
+  </si>
+  <si>
+    <t>Administração do Autódromo de Interlagos</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação do Serviço de Moto Verificação</t>
+  </si>
+  <si>
+    <t>Operação e Manutenção da Infraestrutura Turística</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação da Casa da Mulher Brasileira</t>
+  </si>
+  <si>
+    <t>Gratificação de Municipalização - Saúde - Lei 13.510/03</t>
+  </si>
+  <si>
+    <t>Construção e Implantação de Unidades de Conservação</t>
+  </si>
+  <si>
+    <t>Locação Social</t>
+  </si>
+  <si>
+    <t>Sistema de Avaliação Escolar dos Alunos da Rede Municipal de Ensino</t>
+  </si>
+  <si>
+    <t>Estudos, Planos e Projetos Ambientais</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Equipamentos Públicos Voltados à Promoção da Igualdade Racial</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Equipamentos Públicos Voltados ao Atendimento da População de Rua</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação do Policiamento de Trânsito</t>
+  </si>
+  <si>
+    <t>Plano de Contingência para Situações de Baixas Temperaturas - Decreto nº 62.760/2023</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Equipamentos da Assistência Social</t>
+  </si>
+  <si>
+    <t>Prêmio Zé Renato</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação dos Serviços de Atendimento e Manejo da Fauna Silvestre</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Unidades Educacionais - Educação Indígena</t>
+  </si>
+  <si>
+    <t>Construção de Escolas Municipais de Ensino Fundamental (EMEF)</t>
+  </si>
+  <si>
+    <t>Incentivo ao Uso de Veículos Elétricos ou Movidos a Hidrogênio</t>
+  </si>
+  <si>
+    <t>Reforma e Acessibilidade em Passeios Públicos</t>
+  </si>
+  <si>
+    <t>Lei de Fomento à Dança</t>
+  </si>
+  <si>
+    <t>Serviços de Desfazimento e Demolição de Construções Irregulares em Áreas de Proteção Ambiental</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Unidades Educacionais - Centro Integrado de Jovens e Adultos (CIEJA)</t>
+  </si>
+  <si>
+    <t>Fomento e Apoio ao Cooperativismo</t>
+  </si>
+  <si>
+    <t>Programação de Atividades Culturais de Casas de Cultura</t>
+  </si>
+  <si>
+    <t>Políticas, Programas e Ações Inclusivas</t>
+  </si>
+  <si>
+    <t>Conservação e Manutenção de Unidades Educacionais - CEU</t>
+  </si>
+  <si>
+    <t>Fomento ao Circo/Edital Xamego</t>
+  </si>
+  <si>
+    <t>Corredor Aricanduva - Obras do BRT - 1.1</t>
+  </si>
+  <si>
+    <t>Manutenção da Ouvidoria de Direitos Humanos</t>
+  </si>
+  <si>
+    <t>Ações Permanentes de Promoção dos Direitos da População Idosa</t>
+  </si>
+  <si>
+    <t>Operação e Manutenção do VAI TEC</t>
+  </si>
+  <si>
+    <t>Urbanismo Social</t>
+  </si>
+  <si>
+    <t>Acessibilidade, Ampliação, Reforma e Requalificação de Faixas Exclusivas de Ônibus, inclusive Área de Parada e Plataforma de Embarque</t>
+  </si>
+  <si>
+    <t>PROCONECTA - Promoção da Conectividade e Inclusão Digital</t>
+  </si>
+  <si>
+    <t>Implantação de Transporte Público Hidroviário</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação do Programa Sampa+Rural</t>
+  </si>
+  <si>
+    <t>Corredor Aricanduva - Gerenciamento de Projetos - 3.1</t>
+  </si>
+  <si>
+    <t>Programação de Atividades Culturais de Centros Culturais e Teatros</t>
+  </si>
+  <si>
+    <t>Contribuição Formação Patrimônio Servidor Público - Parcelamento PASEP</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação da Central de Interpretação de Libras, Intérpretes e Guias-Intérpretes</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Unidades Educacionais - Escola Municipal de Educação Bilíngue para Surdos (EMEBS)</t>
+  </si>
+  <si>
+    <t>Políticas, Programas e Ações Para Criança e Adolescente</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação da Defesa Civil</t>
+  </si>
+  <si>
+    <t>Ações de Difusão Cultural do Theatro Municipal - Patrimônio</t>
+  </si>
+  <si>
+    <t>Auxílio Funeral</t>
+  </si>
+  <si>
+    <t>Políticas de Promoção Cultural</t>
+  </si>
+  <si>
+    <t>Execução do Programa Museu de Arte de Rua - MAR</t>
+  </si>
+  <si>
+    <t>Bolsa Atleta</t>
+  </si>
+  <si>
+    <t>Fomento e Difusão do Rock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Promoção da Educação Antirracista e Não Xenofóbica na RMESP_x000D__x000D_
+</t>
+  </si>
+  <si>
+    <t>Obrigações e Contribuições Patronais - Parcelamento INSS</t>
+  </si>
+  <si>
+    <t>Rádios Comunitárias - Lei nº 16.572/2016</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação dos Planetários Municipais</t>
+  </si>
+  <si>
+    <t>Implantação e Construção de Ecopontos</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação do Arquivo Histórico Municipal</t>
+  </si>
+  <si>
+    <t>Programação de Atividades Culturais nas Bibliotecas Públicas</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Equipamentos do Patrimônio Histórico</t>
+  </si>
+  <si>
+    <t>Ampliação, Reforma e Requalificação de Unidade de Abastecimento</t>
+  </si>
+  <si>
+    <t>Fomento e Difusão do Samba</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação do Programa de Residência em Gestão Pública</t>
+  </si>
+  <si>
+    <t>Programa Piá</t>
+  </si>
+  <si>
+    <t>Fomento às Cadeias Produtivas, Vocações Produtivas e Projetos Locais</t>
+  </si>
+  <si>
+    <t>Bolsa-Trabalho</t>
+  </si>
+  <si>
+    <t>Execução de Serviços Médicos de Tratamento de Radioterapia</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação dos Equipamentos Públicos Voltados para Pessoa Idosa</t>
+  </si>
+  <si>
+    <t>Fomento e Difusão da Capoeira</t>
+  </si>
+  <si>
+    <t>Educação Ambiental</t>
+  </si>
+  <si>
+    <t>Bloqueios Judiciais</t>
+  </si>
+  <si>
+    <t>Mês do Hip Hop</t>
+  </si>
+  <si>
+    <t>Ampliação, Reforma e Requalificação das Instalações para a Guarda Civil Metropolitana</t>
+  </si>
+  <si>
+    <t>Ações de Difusão Cultural do Theatro Municipal - Programação Artística</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Equipamentos Públicos Voltados ao Atendimento de Imigrantes</t>
+  </si>
+  <si>
+    <t>Políticas, Programas e Ações para Pessoa Idosa</t>
+  </si>
+  <si>
+    <t>Programação de Atividades Culturais do Centro Cultural São Paulo</t>
+  </si>
+  <si>
+    <t>Construção e Implantação do Descomplica SP</t>
+  </si>
+  <si>
+    <t>Programa de Iniciação Artística para a Primeira Infância - PIAPI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operação e Manutenção do Portal da PMSP_x000D__x000D_
+</t>
+  </si>
+  <si>
+    <t>Apoio à Cultura Negra</t>
+  </si>
+  <si>
+    <t>Programa Mãos e Mentes Paulistanas</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação do Programa de Proteção Escolar</t>
+  </si>
+  <si>
+    <t>Difusão, Fomento e Pesquisas Aplicadas para a Gestão Participativa e Desenvolvimento Urbano</t>
+  </si>
+  <si>
+    <t>Ações de Desenvolvimento Social</t>
+  </si>
+  <si>
+    <t>Vivência Prática de Gestão de Documentos</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação dos Conselhos e Espaços Participativos Municipais</t>
+  </si>
+  <si>
+    <t>Ações de Cooperação para o Desenvolvimento Sustentável</t>
+  </si>
+  <si>
+    <t>Projeto de Intervenção Urbana - PIU</t>
+  </si>
+  <si>
+    <t>Políticas, Programas e Ações para Educação em Direitos Humanos e Promoção do Direito à Cidade</t>
+  </si>
+  <si>
+    <t>Ampliação, Reforma e Requalificação de Equipamentos de Saúde Animal</t>
+  </si>
+  <si>
+    <t>Programa Vocacional</t>
+  </si>
+  <si>
+    <t>Ações de Educação de Trânsito</t>
+  </si>
+  <si>
+    <t>Acordos Judiciais ou Administrativos</t>
+  </si>
+  <si>
+    <t>Programa Aldeias</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação do Programa de Residência Jurídica</t>
+  </si>
+  <si>
+    <t>Fomento à Música</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Unidades Educacionais - Centro Municipal de Capacitação e Treinamento (CMCT)</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação no Serviço de Guinchamento</t>
+  </si>
+  <si>
+    <t>Fomento e Difusão do Forró</t>
+  </si>
+  <si>
+    <t>Ações e Atividades Culturais da Biblioteca Mario de Andrade</t>
+  </si>
+  <si>
+    <t>Ações e Atividades Culturais do Departamento do Patrimônio Histórico</t>
+  </si>
+  <si>
+    <t>Circuito Cultural de São Paulo</t>
+  </si>
+  <si>
+    <t>Ampliação, Reforma e Requalificação de Posto do Corpo de Bombeiros</t>
+  </si>
+  <si>
+    <t>Publicação de Editais e Outras Publicações Legais e de Interesse do Município</t>
+  </si>
+  <si>
+    <t>Fomento e Difusão do Reggae e da Cultura Rastafari</t>
+  </si>
+  <si>
+    <t>Ampliação, Reforma e Requalificação de Unidades de Conservação</t>
+  </si>
+  <si>
+    <t>Fomento e Difusão do Funk</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação do Centro Público de Economia Solidária e Direitos Humanos</t>
+  </si>
+  <si>
+    <t>Educação Paulistana Pode Mais - BID</t>
+  </si>
+  <si>
+    <t>Política Municipal de Desenvolvimento Econômico</t>
+  </si>
+  <si>
+    <t>BID II - Ampliação, Reforma e Requalificação de Equipamentos de Assistência Hospitalar</t>
+  </si>
+  <si>
+    <t>Restituição de Receitas Descontinuadas</t>
+  </si>
+  <si>
+    <t>Plano Municipal do Livro, Leitura, Literatura e Biblioteca (PMLLLB)</t>
+  </si>
+  <si>
+    <t>Implantação de Corredores de Ônibus Novos</t>
+  </si>
+  <si>
+    <t>Território Hip Hop (Vocacional Hip Hop)</t>
+  </si>
+  <si>
+    <t>Centro de Referência da Dança</t>
+  </si>
+  <si>
+    <t>Gestão do Patrimônio Imobiliário Municipal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avança Saúde SP - Ampliação, Reforma e Requalificação de Equipamentos de Saúde_x000D__x000D_
+</t>
+  </si>
+  <si>
+    <t>Políticas, Programas e Ações para Imigrantes e Promoção ao Trabalho Decente</t>
+  </si>
+  <si>
+    <t>Centro de Memória do Circo</t>
+  </si>
+  <si>
+    <t>Oficina nos Equipamentos Culturais</t>
+  </si>
+  <si>
+    <t>Construção e Implantação de Equipamentos de Saúde Animal</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação Semafórica</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Espaços Lúdicos e Educativos</t>
+  </si>
+  <si>
+    <t>Políticas, Programas e Ações para Promoção da Igualdade Racial</t>
+  </si>
+  <si>
+    <t>Pesquisa de Satisfação do Cidadão em Relação aos Serviços, Políticas e Programas</t>
+  </si>
+  <si>
+    <t>Pagamentos de Serviços Ambientais</t>
+  </si>
+  <si>
+    <t>Programação de Atividades Culturais do Departamento dos Museus Municipais</t>
+  </si>
+  <si>
+    <t>Manutenção de Prédios Administrativos</t>
+  </si>
+  <si>
+    <t>Instalação de Polo Criativo na Chácara do Jockey</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação da Supervisão Geral das Juntas do Serviço Militar</t>
+  </si>
+  <si>
+    <t>Auxílio Destinado a Assistência Odontológica a Agentes Públicos - Lei nº 17.841/2022</t>
+  </si>
+  <si>
+    <t>FUMCAD - Multas Revertidas ao Fundo</t>
+  </si>
+  <si>
+    <t>Conservação e Valorização de Acervos da Biblioteca Mário de Andrade</t>
+  </si>
+  <si>
+    <t>Políticas, Programas e Ações para Povos Indígenas</t>
+  </si>
+  <si>
+    <t>Ações de Monitoramento de Mudanças Climáticas</t>
+  </si>
+  <si>
+    <t>Implantação de Projetos de Redesenho Urbano para Segurança Viária</t>
+  </si>
+  <si>
+    <t>Políticas, Programas e Ações para Pessoas Egressas do Sistema Prisional</t>
+  </si>
+  <si>
+    <t>Promoção da Transparência, do Acesso à Informação e do Controle Social</t>
+  </si>
+  <si>
+    <t>Conservação e Valorização de Acervos do Departamento dos Museus Municipais</t>
+  </si>
+  <si>
+    <t>Ações e Atividades Culturais do Arquivo Histórico Municipal</t>
+  </si>
+  <si>
+    <t>Programa de Promoção da Imagem de São Paulo no Exterior</t>
+  </si>
+  <si>
+    <t>Ações do Programa Agentes de Governo Aberto</t>
+  </si>
+  <si>
+    <t>Projetos e Ações de Apoio Habitacional</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação do Herbário Municipal</t>
+  </si>
+  <si>
+    <t>Corredor Aricanduva - Fortalecimento Institucional - 3.3</t>
+  </si>
+  <si>
+    <t>Corredor Aricanduva - Controles Internos - 3.2</t>
+  </si>
+  <si>
+    <t>Corredor Aricanduva - Acompanhamento Ambiental e Social - 1.5</t>
+  </si>
+  <si>
+    <t>Comunicação e Orientação na Valorização e Cuidado na Primeira Infância</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação do Programa de Pós-Graduação</t>
+  </si>
+  <si>
+    <t>Fiscalização, Monitoramento e Controle Ambiental</t>
+  </si>
+  <si>
+    <t>Ampliação, Reforma e Requalificação de Edificação da Câmara Municipal de São Paulo</t>
+  </si>
+  <si>
+    <t>Ampliação, Reforma e Requalificação de Edificação do Tribunal de Contas do Município</t>
+  </si>
+  <si>
+    <t>Ações de Vigilância Socioassistencial</t>
+  </si>
+  <si>
+    <t>Benefícios Eventuais</t>
+  </si>
+  <si>
+    <t>Construção de Edificações da Câmara Municipal de São Paulo</t>
+  </si>
+  <si>
+    <t>Contraprestação de Parceria Público-Privada (PPP) - Iluminação Pública</t>
+  </si>
+  <si>
+    <t>Câmara Municipal - Comunicação</t>
+  </si>
+  <si>
+    <t>Encargos Referentes a Pagamentos de Manutenção de Conta Corrente</t>
+  </si>
+  <si>
+    <t>Escola de Gestão e Contas Públicas</t>
+  </si>
+  <si>
+    <t>Escola do Parlamento</t>
+  </si>
+  <si>
+    <t>Expansão e Aperfeiçoamento das Atividades da CMSP</t>
+  </si>
+  <si>
+    <t>Expansão e Aperfeiçoamento das Atividades do TCM</t>
+  </si>
+  <si>
+    <t>Inserção das Famílias no Cadastro Único</t>
+  </si>
+  <si>
+    <t>Manutenção e Operação de Edificação da Câmara Municipal de São Paulo</t>
+  </si>
+  <si>
+    <t>Modernização Semafórica</t>
+  </si>
+  <si>
+    <t>Plano de Contingência para Situações de Altas Temperaturas - Decreto nº 62.760/2023</t>
+  </si>
+  <si>
+    <t>Programa Reencontro</t>
+  </si>
+  <si>
+    <t>Programa de Garantia de Renda Familiar Mínima</t>
+  </si>
+  <si>
+    <t>Realização de Conferências Municipais Temáticas</t>
+  </si>
+  <si>
+    <t>Servidores Comissionados no Hospital Serv. Públco Municipal - HSPM</t>
+  </si>
+  <si>
+    <t>Tarifa de Arrecadação de Multas</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,13 +1280,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +1332,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +1366,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +1401,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,47 +1577,40 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F396"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="64.7109375" customWidth="1"/>
+    <col min="2" max="2" width="60.140625" customWidth="1"/>
+    <col min="4" max="4" width="32" customWidth="1"/>
+    <col min="5" max="5" width="43.42578125" customWidth="1"/>
+    <col min="6" max="6" width="53.28515625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>descricao_proj_ativ</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>valor_total</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>valor_regionalizado</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>perc_regionalizado</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>n_subpref</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Aposentadorias e Pensões</t>
-        </is>
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>6</v>
       </c>
       <c r="B2">
         <v>2025</v>
@@ -408,20 +1628,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação em Atenção Básica, Especialidades e de Serviços Auxiliares de Diagnóstico e Terapia</t>
-        </is>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>7</v>
       </c>
       <c r="B3">
         <v>2025</v>
       </c>
       <c r="C3">
-        <v>8261724836.03</v>
+        <v>8261724836.0299997</v>
       </c>
       <c r="D3">
-        <v>7067825312.74</v>
+        <v>7067825312.7399998</v>
       </c>
       <c r="E3">
         <v>0.8554902823580719</v>
@@ -430,33 +1648,29 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação em Atenção Hospitalar e de Urgência e Emergência</t>
-        </is>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>8</v>
       </c>
       <c r="B4">
         <v>2025</v>
       </c>
       <c r="C4">
-        <v>7164711595.23</v>
+        <v>7164711595.2299995</v>
       </c>
       <c r="D4">
-        <v>6910697398.82</v>
+        <v>6910697398.8199997</v>
       </c>
       <c r="E4">
-        <v>0.9645464868984939</v>
+        <v>0.96454648689849387</v>
       </c>
       <c r="F4">
         <v>32</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Compensações Tarifárias do Sistema de Ônibus</t>
-        </is>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>9</v>
       </c>
       <c r="B5">
         <v>2025</v>
@@ -474,20 +1688,18 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação da Rede Parceira - Centro de Educação Infantil (CEI)</t>
-        </is>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>10</v>
       </c>
       <c r="B6">
         <v>2025</v>
       </c>
       <c r="C6">
-        <v>5479255960.37</v>
+        <v>5479255960.3699999</v>
       </c>
       <c r="D6">
-        <v>5479255960.37</v>
+        <v>5479255960.3699999</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -496,17 +1708,15 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Administração da Unidade</t>
-        </is>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>11</v>
       </c>
       <c r="B7">
         <v>2025</v>
       </c>
       <c r="C7">
-        <v>5366178134.74</v>
+        <v>5366178134.7399998</v>
       </c>
       <c r="D7">
         <v>2024847308.26</v>
@@ -518,17 +1728,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Aporte do IRRF para cobertura do deficit atuarial do RPPS</t>
-        </is>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>12</v>
       </c>
       <c r="B8">
         <v>2025</v>
       </c>
       <c r="C8">
-        <v>4757790366.83</v>
+        <v>4757790366.8299999</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -540,17 +1748,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Obrigações e Contribuições Patronais RPPS Educação</t>
-        </is>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>13</v>
       </c>
       <c r="B9">
         <v>2025</v>
       </c>
       <c r="C9">
-        <v>3651283855.14</v>
+        <v>3651283855.1399999</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -562,17 +1768,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Condenações Judiciais - Créditos de Natureza Alimentar</t>
-        </is>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>14</v>
       </c>
       <c r="B10">
         <v>2025</v>
       </c>
       <c r="C10">
-        <v>3245895041.66</v>
+        <v>3245895041.6599998</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -584,20 +1788,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Remuneração dos Profissionais da Educação Básica - Ensino Fundamental</t>
-        </is>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>15</v>
       </c>
       <c r="B11">
         <v>2025</v>
       </c>
       <c r="C11">
-        <v>2226719423.61</v>
+        <v>2226719423.6100001</v>
       </c>
       <c r="D11">
-        <v>2226719423.61</v>
+        <v>2226719423.6100001</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -606,20 +1808,18 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Sistema Municipal de Regulação, Controle, Avaliação e Auditoria do SUS</t>
-        </is>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>16</v>
       </c>
       <c r="B12">
         <v>2025</v>
       </c>
       <c r="C12">
-        <v>1714693086.13</v>
+        <v>1714693086.1300001</v>
       </c>
       <c r="D12">
-        <v>1714693086.13</v>
+        <v>1714693086.1300001</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -628,20 +1828,18 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Serviços de Limpeza Urbana - Varrição e Lavagem de Áreas Públicas</t>
-        </is>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>17</v>
       </c>
       <c r="B13">
         <v>2025</v>
       </c>
       <c r="C13">
-        <v>1343405878.18</v>
+        <v>1343405878.1800001</v>
       </c>
       <c r="D13">
-        <v>1343405878.18</v>
+        <v>1343405878.1800001</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -650,11 +1848,9 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Recomposição de Depósitos Judiciais</t>
-        </is>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>18</v>
       </c>
       <c r="B14">
         <v>2025</v>
@@ -672,11 +1868,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Serviços de Engenharia de Tráfego</t>
-        </is>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>19</v>
       </c>
       <c r="B15">
         <v>2025</v>
@@ -694,20 +1888,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Eletrificação da frota de veículos do Sistema Municipal de Transporte Coletivo</t>
-        </is>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>20</v>
       </c>
       <c r="B16">
         <v>2025</v>
       </c>
       <c r="C16">
-        <v>1236807895.4</v>
+        <v>1236807895.4000001</v>
       </c>
       <c r="D16">
-        <v>1236807895.4</v>
+        <v>1236807895.4000001</v>
       </c>
       <c r="E16">
         <v>1</v>
@@ -716,11 +1908,9 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Alimentação Escolar</t>
-        </is>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>21</v>
       </c>
       <c r="B17">
         <v>2025</v>
@@ -732,26 +1922,24 @@
         <v>1045629822.51</v>
       </c>
       <c r="E17">
-        <v>0.8996323891511389</v>
+        <v>0.89963238915113886</v>
       </c>
       <c r="F17">
         <v>32</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Programa Pode Entrar</t>
-        </is>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>22</v>
       </c>
       <c r="B18">
         <v>2025</v>
       </c>
       <c r="C18">
-        <v>1162178834.16</v>
+        <v>1162178834.1600001</v>
       </c>
       <c r="D18">
-        <v>1162178834.16</v>
+        <v>1162178834.1600001</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -760,11 +1948,9 @@
         <v>21</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Obrigações e Contribuições Patronais</t>
-        </is>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>23</v>
       </c>
       <c r="B19">
         <v>2025</v>
@@ -782,11 +1968,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Remuneração dos Profissionais da Educação Básica - Centro de Educação Infantil (CEI)</t>
-        </is>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>24</v>
       </c>
       <c r="B20">
         <v>2025</v>
@@ -804,33 +1988,29 @@
         <v>32</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Sistemas de Informação e Comunicação</t>
-        </is>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>25</v>
       </c>
       <c r="B21">
         <v>2025</v>
       </c>
       <c r="C21">
-        <v>1019540967.32</v>
+        <v>1019540967.3200001</v>
       </c>
       <c r="D21">
-        <v>8345190.03</v>
+        <v>8345190.0300000003</v>
       </c>
       <c r="E21">
-        <v>0.008185242474303361</v>
+        <v>8.185242474303361E-3</v>
       </c>
       <c r="F21">
         <v>32</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Execução do Programa de Mananciais</t>
-        </is>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>26</v>
       </c>
       <c r="B22">
         <v>2025</v>
@@ -848,17 +2028,15 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Serviço da Dívida Pública Interna</t>
-        </is>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>27</v>
       </c>
       <c r="B23">
         <v>2025</v>
       </c>
       <c r="C23">
-        <v>903977257.89</v>
+        <v>903977257.88999999</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -870,17 +2048,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Promoção de Campanhas e Eventos de Interesse do Município</t>
-        </is>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>28</v>
       </c>
       <c r="B24">
         <v>2025</v>
       </c>
       <c r="C24">
-        <v>885539107.28</v>
+        <v>885539107.27999997</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -892,20 +2068,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Intervenções no Sistema de Drenagem</t>
-        </is>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>29</v>
       </c>
       <c r="B25">
         <v>2025</v>
       </c>
       <c r="C25">
-        <v>870828465.46</v>
+        <v>870828465.46000004</v>
       </c>
       <c r="D25">
-        <v>870828465.46</v>
+        <v>870828465.46000004</v>
       </c>
       <c r="E25">
         <v>1</v>
@@ -914,11 +2088,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Contribuição Formação Patrimônio Servidor Público - PASEP</t>
-        </is>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>30</v>
       </c>
       <c r="B26">
         <v>2025</v>
@@ -936,17 +2108,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Condenações Judiciais - Outras Espécies</t>
-        </is>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>31</v>
       </c>
       <c r="B27">
         <v>2025</v>
       </c>
       <c r="C27">
-        <v>760629580.3099999</v>
+        <v>760629580.30999994</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -958,42 +2128,38 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Administração de Material  Médico Hospitalar e Ambulatorial em Atenção Básica, Especialidades e Vigilância</t>
-        </is>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>32</v>
       </c>
       <c r="B28">
         <v>2025</v>
       </c>
       <c r="C28">
-        <v>733214196.28</v>
+        <v>733214196.27999997</v>
       </c>
       <c r="D28">
-        <v>262466.9</v>
+        <v>262466.90000000002</v>
       </c>
       <c r="E28">
-        <v>0.0003579675643647373</v>
+        <v>3.5796756436473729E-4</v>
       </c>
       <c r="F28">
         <v>12</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Remuneração dos Profissionais da Educação Básica - Escola Municipal de Educação Infantil (EMEI)</t>
-        </is>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>33</v>
       </c>
       <c r="B29">
         <v>2025</v>
       </c>
       <c r="C29">
-        <v>723172261.59</v>
+        <v>723172261.59000003</v>
       </c>
       <c r="D29">
-        <v>723172261.59</v>
+        <v>723172261.59000003</v>
       </c>
       <c r="E29">
         <v>1</v>
@@ -1002,17 +2168,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Obrigações e Contribuições Patronais RPPS Saúde</t>
-        </is>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>34</v>
       </c>
       <c r="B30">
         <v>2025</v>
       </c>
       <c r="C30">
-        <v>685610615.86</v>
+        <v>685610615.86000001</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -1024,33 +2188,29 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação em Atenção Básica, Especialidades e Vigilância da Assistência Farmacêutica</t>
-        </is>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>35</v>
       </c>
       <c r="B31">
         <v>2025</v>
       </c>
       <c r="C31">
-        <v>667122608.52</v>
+        <v>667122608.51999998</v>
       </c>
       <c r="D31">
         <v>14846749.4</v>
       </c>
       <c r="E31">
-        <v>0.02225490368695083</v>
+        <v>2.2254903686950829E-2</v>
       </c>
       <c r="F31">
         <v>11</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Concessão dos Serviços Divisíveis de Limpeza Urbana em Regime Público</t>
-        </is>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>36</v>
       </c>
       <c r="B32">
         <v>2025</v>
@@ -1068,20 +2228,18 @@
         <v>32</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Manutenção de Sistemas de Drenagem</t>
-        </is>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>37</v>
       </c>
       <c r="B33">
         <v>2025</v>
       </c>
       <c r="C33">
-        <v>574203846.22</v>
+        <v>574203846.22000003</v>
       </c>
       <c r="D33">
-        <v>574203846.22</v>
+        <v>574203846.22000003</v>
       </c>
       <c r="E33">
         <v>1</v>
@@ -1090,11 +2248,9 @@
         <v>32</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Operação Tapa Buraco</t>
-        </is>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>38</v>
       </c>
       <c r="B34">
         <v>2025</v>
@@ -1112,20 +2268,18 @@
         <v>32</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Pavimentação e Recapeamento de Vias</t>
-        </is>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>39</v>
       </c>
       <c r="B35">
         <v>2025</v>
       </c>
       <c r="C35">
-        <v>505536363.2</v>
+        <v>505536363.19999999</v>
       </c>
       <c r="D35">
-        <v>505536363.2</v>
+        <v>505536363.19999999</v>
       </c>
       <c r="E35">
         <v>1</v>
@@ -1134,42 +2288,38 @@
         <v>32</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Transporte Escolar - Ensino Fundamental</t>
-        </is>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>40</v>
       </c>
       <c r="B36">
         <v>2025</v>
       </c>
       <c r="C36">
-        <v>485497474.49</v>
+        <v>485497474.49000001</v>
       </c>
       <c r="D36">
         <v>410262736</v>
       </c>
       <c r="E36">
-        <v>0.8450357778502725</v>
+        <v>0.84503577785027251</v>
       </c>
       <c r="F36">
         <v>32</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Recuperação e Reforço de Obras de Arte Especiais - OAE</t>
-        </is>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>41</v>
       </c>
       <c r="B37">
         <v>2025</v>
       </c>
       <c r="C37">
-        <v>462226776.85</v>
+        <v>462226776.85000002</v>
       </c>
       <c r="D37">
-        <v>462226776.85</v>
+        <v>462226776.85000002</v>
       </c>
       <c r="E37">
         <v>1</v>
@@ -1178,20 +2328,18 @@
         <v>22</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Centros Educacionais Unificados (CEU)</t>
-        </is>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>42</v>
       </c>
       <c r="B38">
         <v>2025</v>
       </c>
       <c r="C38">
-        <v>448180450.58</v>
+        <v>448180450.57999998</v>
       </c>
       <c r="D38">
-        <v>448180450.58</v>
+        <v>448180450.57999998</v>
       </c>
       <c r="E38">
         <v>1</v>
@@ -1200,11 +2348,9 @@
         <v>32</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Construção de Unidades Habitacionais</t>
-        </is>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>43</v>
       </c>
       <c r="B39">
         <v>2025</v>
@@ -1222,20 +2368,18 @@
         <v>32</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Unidades Educacionais - Escola Municipal de Ensino Fundamental (EMEF)</t>
-        </is>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>44</v>
       </c>
       <c r="B40">
         <v>2025</v>
       </c>
       <c r="C40">
-        <v>414821738.89</v>
+        <v>414821738.88999999</v>
       </c>
       <c r="D40">
-        <v>414821738.89</v>
+        <v>414821738.88999999</v>
       </c>
       <c r="E40">
         <v>1</v>
@@ -1244,20 +2388,18 @@
         <v>32</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Áreas Verdes e Vegetação Arbórea</t>
-        </is>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>45</v>
       </c>
       <c r="B41">
         <v>2025</v>
       </c>
       <c r="C41">
-        <v>401175229.7</v>
+        <v>401175229.69999999</v>
       </c>
       <c r="D41">
-        <v>401175229.7</v>
+        <v>401175229.69999999</v>
       </c>
       <c r="E41">
         <v>1</v>
@@ -1266,20 +2408,18 @@
         <v>32</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Parques Urbanos e Lineares</t>
-        </is>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>46</v>
       </c>
       <c r="B42">
         <v>2025</v>
       </c>
       <c r="C42">
-        <v>386242231.91</v>
+        <v>386242231.91000003</v>
       </c>
       <c r="D42">
-        <v>386242231.91</v>
+        <v>386242231.91000003</v>
       </c>
       <c r="E42">
         <v>1</v>
@@ -1288,20 +2428,18 @@
         <v>32</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Ações Integradas de Segurança Pública - Operação Delegada - Convênio SSP SO</t>
-        </is>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>47</v>
       </c>
       <c r="B43">
         <v>2025</v>
       </c>
       <c r="C43">
-        <v>383514285.97</v>
+        <v>383514285.97000003</v>
       </c>
       <c r="D43">
-        <v>383514285.97</v>
+        <v>383514285.97000003</v>
       </c>
       <c r="E43">
         <v>1</v>
@@ -1310,64 +2448,58 @@
         <v>30</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Políticas, Programas e Ações de Subsistência, Segurança Alimentar e Nutricional</t>
-        </is>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>48</v>
       </c>
       <c r="B44">
         <v>2025</v>
       </c>
       <c r="C44">
-        <v>381292677.26</v>
+        <v>381292677.25999999</v>
       </c>
       <c r="D44">
-        <v>381132684.59</v>
+        <v>381132684.58999997</v>
       </c>
       <c r="E44">
-        <v>0.9995803940659188</v>
+        <v>0.99958039406591881</v>
       </c>
       <c r="F44">
         <v>32</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Aquisição de Materiais, Equipamentos e Serviços de Informação e Comunicação</t>
-        </is>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>49</v>
       </c>
       <c r="B45">
         <v>2025</v>
       </c>
       <c r="C45">
-        <v>374268404.92</v>
+        <v>374268404.92000002</v>
       </c>
       <c r="D45">
         <v>13490306.1</v>
       </c>
       <c r="E45">
-        <v>0.0360444694840954</v>
+        <v>3.6044469484095398E-2</v>
       </c>
       <c r="F45">
         <v>32</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Equipamentos de Proteção Social Especial à População em Situação de Rua</t>
-        </is>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>50</v>
       </c>
       <c r="B46">
         <v>2025</v>
       </c>
       <c r="C46">
-        <v>361170530.09</v>
+        <v>361170530.08999997</v>
       </c>
       <c r="D46">
-        <v>361170530.09</v>
+        <v>361170530.08999997</v>
       </c>
       <c r="E46">
         <v>1</v>
@@ -1376,11 +2508,9 @@
         <v>32</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Administração de Material Médico Hospitalar em Atenção Hospitalar, de Urgência e Emergência</t>
-        </is>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>51</v>
       </c>
       <c r="B47">
         <v>2025</v>
@@ -1389,51 +2519,47 @@
         <v>359028610.88</v>
       </c>
       <c r="D47">
-        <v>97927103.81</v>
+        <v>97927103.810000002</v>
       </c>
       <c r="E47">
-        <v>0.2727557103874674</v>
+        <v>0.27275571038746738</v>
       </c>
       <c r="F47">
         <v>19</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Transporte Escolar - Educação Infantil</t>
-        </is>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>52</v>
       </c>
       <c r="B48">
         <v>2025</v>
       </c>
       <c r="C48">
-        <v>343073802.16</v>
+        <v>343073802.16000003</v>
       </c>
       <c r="D48">
         <v>280270943</v>
       </c>
       <c r="E48">
-        <v>0.8169406735093386</v>
+        <v>0.81694067350933863</v>
       </c>
       <c r="F48">
         <v>32</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Intervenções no Sistema Viário</t>
-        </is>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>53</v>
       </c>
       <c r="B49">
         <v>2025</v>
       </c>
       <c r="C49">
-        <v>339617203.45</v>
+        <v>339617203.44999999</v>
       </c>
       <c r="D49">
-        <v>339617203.45</v>
+        <v>339617203.44999999</v>
       </c>
       <c r="E49">
         <v>1</v>
@@ -1442,39 +2568,35 @@
         <v>19</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Ampliação, Reforma e Requalificação de Equipamentos em Atenção Hospitalar e de Urgência e Emergência</t>
-        </is>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>54</v>
       </c>
       <c r="B50">
         <v>2025</v>
       </c>
       <c r="C50">
-        <v>339270127.05</v>
+        <v>339270127.05000001</v>
       </c>
       <c r="D50">
-        <v>327248104.57</v>
+        <v>327248104.56999999</v>
       </c>
       <c r="E50">
-        <v>0.9645650426563248</v>
+        <v>0.96456504265632481</v>
       </c>
       <c r="F50">
         <v>22</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação do Sistema Municipal de Transporte Público</t>
-        </is>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>55</v>
       </c>
       <c r="B51">
         <v>2025</v>
       </c>
       <c r="C51">
-        <v>327284818.58</v>
+        <v>327284818.57999998</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -1486,20 +2608,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Programação de Atividades Culturais</t>
-        </is>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>56</v>
       </c>
       <c r="B52">
         <v>2025</v>
       </c>
       <c r="C52">
-        <v>322823606.95</v>
+        <v>322823606.94999999</v>
       </c>
       <c r="D52">
-        <v>322823606.95</v>
+        <v>322823606.94999999</v>
       </c>
       <c r="E52">
         <v>1</v>
@@ -1508,11 +2628,9 @@
         <v>32</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Parceria Público-Privada (PPP) - CEU</t>
-        </is>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>57</v>
       </c>
       <c r="B53">
         <v>2025</v>
@@ -1524,26 +2642,24 @@
         <v>168000000</v>
       </c>
       <c r="E53">
-        <v>0.5450198744092536</v>
+        <v>0.54501987440925359</v>
       </c>
       <c r="F53">
         <v>5</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Urbanização de Favelas</t>
-        </is>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>58</v>
       </c>
       <c r="B54">
         <v>2025</v>
       </c>
       <c r="C54">
-        <v>277357318.52</v>
+        <v>277357318.51999998</v>
       </c>
       <c r="D54">
-        <v>277357318.52</v>
+        <v>277357318.51999998</v>
       </c>
       <c r="E54">
         <v>1</v>
@@ -1552,11 +2668,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação do Programa de Estágios</t>
-        </is>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>59</v>
       </c>
       <c r="B55">
         <v>2025</v>
@@ -1568,17 +2682,15 @@
         <v>1769097.52</v>
       </c>
       <c r="E55">
-        <v>0.006388076075862864</v>
+        <v>6.3880760758628641E-3</v>
       </c>
       <c r="F55">
         <v>1</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Escolas Municipais de Educação Infantil (EMEI)</t>
-        </is>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>60</v>
       </c>
       <c r="B56">
         <v>2025</v>
@@ -1596,17 +2708,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Publicidade Institucional</t>
-        </is>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>61</v>
       </c>
       <c r="B57">
         <v>2025</v>
       </c>
       <c r="C57">
-        <v>249420578.8</v>
+        <v>249420578.80000001</v>
       </c>
       <c r="D57">
         <v>0</v>
@@ -1618,11 +2728,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Equipamentos de Convivência e Fortalecimento de Vínculos para Crianças e Adolescentes</t>
-        </is>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>62</v>
       </c>
       <c r="B58">
         <v>2025</v>
@@ -1640,17 +2748,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Fornecimento de Uniformes-Educação Fundamental</t>
-        </is>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>63</v>
       </c>
       <c r="B59">
         <v>2025</v>
       </c>
       <c r="C59">
-        <v>245007088.73</v>
+        <v>245007088.72999999</v>
       </c>
       <c r="D59">
         <v>0</v>
@@ -1662,11 +2768,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Transporte de Pessoas com Deficiência ou Mobilidade Reduzida - ATENDE</t>
-        </is>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>64</v>
       </c>
       <c r="B60">
         <v>2025</v>
@@ -1684,11 +2788,9 @@
         <v>32</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Sistema de Remuneração Variável</t>
-        </is>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>65</v>
       </c>
       <c r="B61">
         <v>2025</v>
@@ -1706,20 +2808,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Contraprestação de Parceria Público-Privada (PPP) - Terminais Urbanos</t>
-        </is>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>66</v>
       </c>
       <c r="B62">
         <v>2025</v>
       </c>
       <c r="C62">
-        <v>209189636.76</v>
+        <v>209189636.75999999</v>
       </c>
       <c r="D62">
-        <v>209189636.76</v>
+        <v>209189636.75999999</v>
       </c>
       <c r="E62">
         <v>1</v>
@@ -1728,20 +2828,18 @@
         <v>20</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Equipamentos de Proteção Social Especial a Crianças, Adolescentes e Jovens em Risco Social</t>
-        </is>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>67</v>
       </c>
       <c r="B63">
         <v>2025</v>
       </c>
       <c r="C63">
-        <v>205430243.49</v>
+        <v>205430243.49000001</v>
       </c>
       <c r="D63">
-        <v>205430243.49</v>
+        <v>205430243.49000001</v>
       </c>
       <c r="E63">
         <v>1</v>
@@ -1750,20 +2848,18 @@
         <v>32</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Vigilância em Saúde</t>
-        </is>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>68</v>
       </c>
       <c r="B64">
         <v>2025</v>
       </c>
       <c r="C64">
-        <v>189404712.23</v>
+        <v>189404712.22999999</v>
       </c>
       <c r="D64">
-        <v>189404712.23</v>
+        <v>189404712.22999999</v>
       </c>
       <c r="E64">
         <v>1</v>
@@ -1772,11 +2868,9 @@
         <v>32</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Transferência de Recursos Financeiros para as Unidades Educacionais - Ensino Fundamental</t>
-        </is>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>69</v>
       </c>
       <c r="B65">
         <v>2025</v>
@@ -1794,20 +2888,18 @@
         <v>30</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Centros de Educação Infantil (CEI)</t>
-        </is>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>70</v>
       </c>
       <c r="B66">
         <v>2025</v>
       </c>
       <c r="C66">
-        <v>187543337.51</v>
+        <v>187543337.50999999</v>
       </c>
       <c r="D66">
-        <v>187543337.51</v>
+        <v>187543337.50999999</v>
       </c>
       <c r="E66">
         <v>1</v>
@@ -1816,39 +2908,35 @@
         <v>32</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Ampliação, Reforma e Requalificação de Equipamentos de Atenção Básica e Especialidades</t>
-        </is>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>71</v>
       </c>
       <c r="B67">
         <v>2025</v>
       </c>
       <c r="C67">
-        <v>187438774.95</v>
+        <v>187438774.94999999</v>
       </c>
       <c r="D67">
-        <v>186913959.61</v>
+        <v>186913959.61000001</v>
       </c>
       <c r="E67">
-        <v>0.9972000705823008</v>
+        <v>0.99720007058230076</v>
       </c>
       <c r="F67">
         <v>32</v>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Fornecimento de Material Escolar-Educação Infantil</t>
-        </is>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>72</v>
       </c>
       <c r="B68">
         <v>2025</v>
       </c>
       <c r="C68">
-        <v>184272452.57</v>
+        <v>184272452.56999999</v>
       </c>
       <c r="D68">
         <v>0</v>
@@ -1860,20 +2948,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação no Serviço de Guias e Sarjetas (Vias e Logradouros)</t>
-        </is>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>73</v>
       </c>
       <c r="B69">
         <v>2025</v>
       </c>
       <c r="C69">
-        <v>181226491.55</v>
+        <v>181226491.55000001</v>
       </c>
       <c r="D69">
-        <v>181226491.55</v>
+        <v>181226491.55000001</v>
       </c>
       <c r="E69">
         <v>1</v>
@@ -1882,17 +2968,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Precatórios Pagos com Rendimentos dos Depósitos do Regime Especial</t>
-        </is>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>74</v>
       </c>
       <c r="B70">
         <v>2025</v>
       </c>
       <c r="C70">
-        <v>177978277.01</v>
+        <v>177978277.00999999</v>
       </c>
       <c r="D70">
         <v>0</v>
@@ -1904,11 +2988,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Incentivo à Prática de Esportes</t>
-        </is>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>75</v>
       </c>
       <c r="B71">
         <v>2025</v>
@@ -1926,17 +3008,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Condenações Judiciais - Créditos de Pequeno Valor</t>
-        </is>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>76</v>
       </c>
       <c r="B72">
         <v>2025</v>
       </c>
       <c r="C72">
-        <v>171235300.79</v>
+        <v>171235300.78999999</v>
       </c>
       <c r="D72">
         <v>0</v>
@@ -1948,20 +3028,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Manutenção de Vias e Áreas Públicas</t>
-        </is>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>77</v>
       </c>
       <c r="B73">
         <v>2025</v>
       </c>
       <c r="C73">
-        <v>168720856.2</v>
+        <v>168720856.19999999</v>
       </c>
       <c r="D73">
-        <v>168720856.2</v>
+        <v>168720856.19999999</v>
       </c>
       <c r="E73">
         <v>1</v>
@@ -1970,42 +3048,38 @@
         <v>32</v>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Programa Nacional de Alimentação Escolar - PNAE/ FNDE</t>
-        </is>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>78</v>
       </c>
       <c r="B74">
         <v>2025</v>
       </c>
       <c r="C74">
-        <v>167030730.92</v>
+        <v>167030730.91999999</v>
       </c>
       <c r="D74">
-        <v>22063956.22</v>
+        <v>22063956.219999999</v>
       </c>
       <c r="E74">
-        <v>0.1320951904986132</v>
+        <v>0.13209519049861321</v>
       </c>
       <c r="F74">
         <v>7</v>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Ampliação, Reforma e Requalificação do Autódromo de Interlagos</t>
-        </is>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>79</v>
       </c>
       <c r="B75">
         <v>2025</v>
       </c>
       <c r="C75">
-        <v>166910635.07</v>
+        <v>166910635.06999999</v>
       </c>
       <c r="D75">
-        <v>166910635.07</v>
+        <v>166910635.06999999</v>
       </c>
       <c r="E75">
         <v>1</v>
@@ -2014,11 +3088,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação da Sinalização do Sistema Viário</t>
-        </is>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>80</v>
       </c>
       <c r="B76">
         <v>2025</v>
@@ -2030,23 +3102,21 @@
         <v>109767104.03</v>
       </c>
       <c r="E76">
-        <v>0.665254422347248</v>
+        <v>0.66525442234724796</v>
       </c>
       <c r="F76">
         <v>32</v>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Capacitação, Formação e Aperfeiçoamento dos Trabalhadores</t>
-        </is>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>81</v>
       </c>
       <c r="B77">
         <v>2025</v>
       </c>
       <c r="C77">
-        <v>162503253.15</v>
+        <v>162503253.15000001</v>
       </c>
       <c r="D77">
         <v>0</v>
@@ -2058,11 +3128,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Remuneração dos Profissionais da Educação Básica - Centro Municipal de Educação Infantil( CEMEI)</t>
-        </is>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>82</v>
       </c>
       <c r="B78">
         <v>2025</v>
@@ -2080,11 +3148,9 @@
         <v>32</v>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Intervenção, Urbanização e Melhoria de Bairros - Plano de Obras das Subprefeituras</t>
-        </is>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>83</v>
       </c>
       <c r="B79">
         <v>2025</v>
@@ -2102,20 +3168,18 @@
         <v>32</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Equipamentos Esportivos</t>
-        </is>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>84</v>
       </c>
       <c r="B80">
         <v>2025</v>
       </c>
       <c r="C80">
-        <v>154900929.52</v>
+        <v>154900929.52000001</v>
       </c>
       <c r="D80">
-        <v>154900929.52</v>
+        <v>154900929.52000001</v>
       </c>
       <c r="E80">
         <v>1</v>
@@ -2124,17 +3188,15 @@
         <v>25</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação do Controle e Fiscalização de Tráfego</t>
-        </is>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>85</v>
       </c>
       <c r="B81">
         <v>2025</v>
       </c>
       <c r="C81">
-        <v>150767148.2</v>
+        <v>150767148.19999999</v>
       </c>
       <c r="D81">
         <v>0</v>
@@ -2146,11 +3208,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Leve-Leite</t>
-        </is>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>86</v>
       </c>
       <c r="B82">
         <v>2025</v>
@@ -2168,33 +3228,29 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Ações de Apoio à Educação Especial</t>
-        </is>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>87</v>
       </c>
       <c r="B83">
         <v>2025</v>
       </c>
       <c r="C83">
-        <v>142728776.7</v>
+        <v>142728776.69999999</v>
       </c>
       <c r="D83">
         <v>3127.64</v>
       </c>
       <c r="E83">
-        <v>2.191317036629517E-05</v>
+        <v>2.191317036629517E-5</v>
       </c>
       <c r="F83">
         <v>1</v>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Ações de Difusão Cultural do Theatro Municipal - Grupos Artísticos, Técnicos e Administrativos</t>
-        </is>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>88</v>
       </c>
       <c r="B84">
         <v>2025</v>
@@ -2212,11 +3268,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Ampliação, Reforma e Requalificação de Escola Municipal de Ensino Fundamental (EMEF)</t>
-        </is>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>89</v>
       </c>
       <c r="B85">
         <v>2025</v>
@@ -2234,11 +3288,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Fornecimento de Uniformes-Educação Infantil</t>
-        </is>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>90</v>
       </c>
       <c r="B86">
         <v>2025</v>
@@ -2256,20 +3308,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Ampliação, Reforma e Requalificação de Equipamentos Esportivos</t>
-        </is>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>91</v>
       </c>
       <c r="B87">
         <v>2025</v>
       </c>
       <c r="C87">
-        <v>130515638.57</v>
+        <v>130515638.56999999</v>
       </c>
       <c r="D87">
-        <v>130515638.57</v>
+        <v>130515638.56999999</v>
       </c>
       <c r="E87">
         <v>1</v>
@@ -2278,11 +3328,9 @@
         <v>19</v>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Transferência de Recursos Financeiros para as Unidades Educacionais - Educação Infantil</t>
-        </is>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>92</v>
       </c>
       <c r="B88">
         <v>2025</v>
@@ -2300,11 +3348,9 @@
         <v>29</v>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Terminais de Ônibus</t>
-        </is>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>93</v>
       </c>
       <c r="B89">
         <v>2025</v>
@@ -2322,11 +3368,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Serviço de Atendimento Médico de Urgência (SAMU)</t>
-        </is>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>94</v>
       </c>
       <c r="B90">
         <v>2025</v>
@@ -2335,20 +3379,18 @@
         <v>120487655.09</v>
       </c>
       <c r="D90">
-        <v>67227558.78</v>
+        <v>67227558.780000001</v>
       </c>
       <c r="E90">
-        <v>0.5579622138864218</v>
+        <v>0.55796221388642175</v>
       </c>
       <c r="F90">
         <v>28</v>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Serviço de Moradia Transitória</t>
-        </is>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>95</v>
       </c>
       <c r="B91">
         <v>2025</v>
@@ -2360,17 +3402,15 @@
         <v>31988405</v>
       </c>
       <c r="E91">
-        <v>0.2695044851059754</v>
+        <v>0.26950448510597541</v>
       </c>
       <c r="F91">
         <v>31</v>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Encargos pela Manutenção do Fundo de Depósitos Judiciais nas quais o Município é Parte</t>
-        </is>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>96</v>
       </c>
       <c r="B92">
         <v>2025</v>
@@ -2388,11 +3428,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Intervenções na Área de Mobilidade Urbana</t>
-        </is>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>97</v>
       </c>
       <c r="B93">
         <v>2025</v>
@@ -2410,17 +3448,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Modernização, operação e manutenção dos canais SP156</t>
-        </is>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>98</v>
       </c>
       <c r="B94">
         <v>2025</v>
       </c>
       <c r="C94">
-        <v>111588773.96</v>
+        <v>111588773.95999999</v>
       </c>
       <c r="D94">
         <v>0</v>
@@ -2432,11 +3468,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Ações de Fiscalização do Comércio Ilegal</t>
-        </is>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>99</v>
       </c>
       <c r="B95">
         <v>2025</v>
@@ -2454,11 +3488,9 @@
         <v>32</v>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Equipamentos Intergeracionais de Convivência e Fortalecimento de Vínculos</t>
-        </is>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>100</v>
       </c>
       <c r="B96">
         <v>2025</v>
@@ -2476,11 +3508,9 @@
         <v>29</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Redes de Monitoramento Remoto para Segurança Urbana</t>
-        </is>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>101</v>
       </c>
       <c r="B97">
         <v>2025</v>
@@ -2498,11 +3528,9 @@
         <v>32</v>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Parceria Público Privada - Habitação</t>
-        </is>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>102</v>
       </c>
       <c r="B98">
         <v>2025</v>
@@ -2520,11 +3548,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Fornecimento de Material Escolar-Ensino Fundamental</t>
-        </is>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>103</v>
       </c>
       <c r="B99">
         <v>2025</v>
@@ -2542,20 +3568,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Ampliação, Reforma e Requalificação de Escolas Municipais de Educação Infantil (EMEI)</t>
-        </is>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>104</v>
       </c>
       <c r="B100">
         <v>2025</v>
       </c>
       <c r="C100">
-        <v>96418666.62</v>
+        <v>96418666.620000005</v>
       </c>
       <c r="D100">
-        <v>96418666.62</v>
+        <v>96418666.620000005</v>
       </c>
       <c r="E100">
         <v>1</v>
@@ -2564,42 +3588,38 @@
         <v>3</v>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Qualificação Profissional e Empreendedora</t>
-        </is>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>105</v>
       </c>
       <c r="B101">
         <v>2025</v>
       </c>
       <c r="C101">
-        <v>95001223.98</v>
+        <v>95001223.980000004</v>
       </c>
       <c r="D101">
-        <v>45973833.2</v>
+        <v>45973833.200000003</v>
       </c>
       <c r="E101">
-        <v>0.4839288513764683</v>
+        <v>0.48392885137646829</v>
       </c>
       <c r="F101">
         <v>2</v>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Ampliação, Reforma e Requalificação de Parques Urbanos e Lineares</t>
-        </is>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>106</v>
       </c>
       <c r="B102">
         <v>2025</v>
       </c>
       <c r="C102">
-        <v>93869612.55</v>
+        <v>93869612.549999997</v>
       </c>
       <c r="D102">
-        <v>93869612.55</v>
+        <v>93869612.549999997</v>
       </c>
       <c r="E102">
         <v>1</v>
@@ -2608,20 +3628,18 @@
         <v>8</v>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Construção e Implantação de Equipamentos de Atenção Básica e Especialidades</t>
-        </is>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>107</v>
       </c>
       <c r="B103">
         <v>2025</v>
       </c>
       <c r="C103">
-        <v>93558835.55</v>
+        <v>93558835.549999997</v>
       </c>
       <c r="D103">
-        <v>93558835.55</v>
+        <v>93558835.549999997</v>
       </c>
       <c r="E103">
         <v>1</v>
@@ -2630,20 +3648,18 @@
         <v>21</v>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Implantação e Construção de Terminais de Ônibus</t>
-        </is>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>108</v>
       </c>
       <c r="B104">
         <v>2025</v>
       </c>
       <c r="C104">
-        <v>92522521.27</v>
+        <v>92522521.269999996</v>
       </c>
       <c r="D104">
-        <v>92522521.27</v>
+        <v>92522521.269999996</v>
       </c>
       <c r="E104">
         <v>1</v>
@@ -2652,20 +3668,18 @@
         <v>5</v>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Regularização Fundiária</t>
-        </is>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>109</v>
       </c>
       <c r="B105">
         <v>2025</v>
       </c>
       <c r="C105">
-        <v>91904312.92</v>
+        <v>91904312.920000002</v>
       </c>
       <c r="D105">
-        <v>91904312.92</v>
+        <v>91904312.920000002</v>
       </c>
       <c r="E105">
         <v>1</v>
@@ -2674,11 +3688,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Programa de Incentivo Fiscal Relacionado à Arena Corinthians</t>
-        </is>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>110</v>
       </c>
       <c r="B106">
         <v>2025</v>
@@ -2696,20 +3708,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Inspeção de Obras de Artes Especiais - OAE</t>
-        </is>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>111</v>
       </c>
       <c r="B107">
         <v>2025</v>
       </c>
       <c r="C107">
-        <v>88767327.64</v>
+        <v>88767327.640000001</v>
       </c>
       <c r="D107">
-        <v>88767327.64</v>
+        <v>88767327.640000001</v>
       </c>
       <c r="E107">
         <v>1</v>
@@ -2718,17 +3728,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Servidores Comissionados em Outras Entidades</t>
-        </is>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>112</v>
       </c>
       <c r="B108">
         <v>2025</v>
       </c>
       <c r="C108">
-        <v>85225169.36</v>
+        <v>85225169.359999999</v>
       </c>
       <c r="D108">
         <v>0</v>
@@ -2740,11 +3748,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Serviço da Dívida Pública Externa</t>
-        </is>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>113</v>
       </c>
       <c r="B109">
         <v>2025</v>
@@ -2762,20 +3768,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Implantação e Construção de Corredores de Ônibus</t>
-        </is>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>114</v>
       </c>
       <c r="B110">
         <v>2025</v>
       </c>
       <c r="C110">
-        <v>82322186.26000001</v>
+        <v>82322186.260000005</v>
       </c>
       <c r="D110">
-        <v>82322186.26000001</v>
+        <v>82322186.260000005</v>
       </c>
       <c r="E110">
         <v>1</v>
@@ -2784,20 +3788,18 @@
         <v>15</v>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação da Guarda Civil Metropolitana</t>
-        </is>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>115</v>
       </c>
       <c r="B111">
         <v>2025</v>
       </c>
       <c r="C111">
-        <v>81628215.27</v>
+        <v>81628215.269999996</v>
       </c>
       <c r="D111">
-        <v>81628215.27</v>
+        <v>81628215.269999996</v>
       </c>
       <c r="E111">
         <v>1</v>
@@ -2806,17 +3808,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Ações e Materiais de Apoio Didático-Pedagógico Educacional</t>
-        </is>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>116</v>
       </c>
       <c r="B112">
         <v>2025</v>
       </c>
       <c r="C112">
-        <v>81570508.48</v>
+        <v>81570508.480000004</v>
       </c>
       <c r="D112">
         <v>14916390.43</v>
@@ -2828,20 +3828,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Corredores de Ônibus</t>
-        </is>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>117</v>
       </c>
       <c r="B113">
         <v>2025</v>
       </c>
       <c r="C113">
-        <v>81332054.06</v>
+        <v>81332054.060000002</v>
       </c>
       <c r="D113">
-        <v>81332054.06</v>
+        <v>81332054.060000002</v>
       </c>
       <c r="E113">
         <v>1</v>
@@ -2850,39 +3848,35 @@
         <v>31</v>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação da Atenção Hospitalar da Assistência Farmacêutica</t>
-        </is>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>118</v>
       </c>
       <c r="B114">
         <v>2025</v>
       </c>
       <c r="C114">
-        <v>80869670.3</v>
+        <v>80869670.299999997</v>
       </c>
       <c r="D114">
         <v>202925</v>
       </c>
       <c r="E114">
-        <v>0.002509284373822902</v>
+        <v>2.509284373822902E-3</v>
       </c>
       <c r="F114">
         <v>3</v>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Benefício Assistencial - Lei 17.969/2023</t>
-        </is>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>119</v>
       </c>
       <c r="B115">
         <v>2025</v>
       </c>
       <c r="C115">
-        <v>71633935.72</v>
+        <v>71633935.719999999</v>
       </c>
       <c r="D115">
         <v>0</v>
@@ -2894,17 +3888,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Administração da Carteira Imobiliária</t>
-        </is>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>120</v>
       </c>
       <c r="B116">
         <v>2025</v>
       </c>
       <c r="C116">
-        <v>69504659.27</v>
+        <v>69504659.269999996</v>
       </c>
       <c r="D116">
         <v>0</v>
@@ -2916,17 +3908,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Operação e Manutenção da Agência São Paulo de Desenvolvimento - ADESAMPA</t>
-        </is>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>121</v>
       </c>
       <c r="B117">
         <v>2025</v>
       </c>
       <c r="C117">
-        <v>69331946.73</v>
+        <v>69331946.730000004</v>
       </c>
       <c r="D117">
         <v>0</v>
@@ -2938,20 +3928,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Coleta, Transporte, Tratamento e Dest. Final Resíduos Sólidos Inertes</t>
-        </is>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>122</v>
       </c>
       <c r="B118">
         <v>2025</v>
       </c>
       <c r="C118">
-        <v>68749166.97</v>
+        <v>68749166.969999999</v>
       </c>
       <c r="D118">
-        <v>68749166.97</v>
+        <v>68749166.969999999</v>
       </c>
       <c r="E118">
         <v>1</v>
@@ -2960,20 +3948,18 @@
         <v>32</v>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Conservação e Manutenção de Unidades Educacionais - Educação Infantil</t>
-        </is>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>123</v>
       </c>
       <c r="B119">
         <v>2025</v>
       </c>
       <c r="C119">
-        <v>67307983.89</v>
+        <v>67307983.890000001</v>
       </c>
       <c r="D119">
-        <v>67307983.89</v>
+        <v>67307983.890000001</v>
       </c>
       <c r="E119">
         <v>1</v>
@@ -2982,11 +3968,9 @@
         <v>32</v>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Ações de Educação Integral</t>
-        </is>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>124</v>
       </c>
       <c r="B120">
         <v>2025</v>
@@ -2995,26 +3979,24 @@
         <v>66553772.75</v>
       </c>
       <c r="D120">
-        <v>17214932.94</v>
+        <v>17214932.940000001</v>
       </c>
       <c r="E120">
-        <v>0.2586620146188482</v>
+        <v>0.25866201461884819</v>
       </c>
       <c r="F120">
         <v>30</v>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Posto do Corpo de Bombeiros</t>
-        </is>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>125</v>
       </c>
       <c r="B121">
         <v>2025</v>
       </c>
       <c r="C121">
-        <v>59124622.84</v>
+        <v>59124622.840000004</v>
       </c>
       <c r="D121">
         <v>0</v>
@@ -3026,20 +4008,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Ações Permanentes de Promoção dos Direitos da Criança e do Adolescente</t>
-        </is>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>126</v>
       </c>
       <c r="B122">
         <v>2025</v>
       </c>
       <c r="C122">
-        <v>58040993.95</v>
+        <v>58040993.950000003</v>
       </c>
       <c r="D122">
-        <v>58040993.95</v>
+        <v>58040993.950000003</v>
       </c>
       <c r="E122">
         <v>1</v>
@@ -3048,20 +4028,18 @@
         <v>29</v>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Fomento às Linguagens Artísticas</t>
-        </is>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>127</v>
       </c>
       <c r="B123">
         <v>2025</v>
       </c>
       <c r="C123">
-        <v>57784238.34</v>
+        <v>57784238.340000004</v>
       </c>
       <c r="D123">
-        <v>57784238.34</v>
+        <v>57784238.340000004</v>
       </c>
       <c r="E123">
         <v>1</v>
@@ -3070,20 +4048,18 @@
         <v>32</v>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Programação da Virada Cultural</t>
-        </is>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>128</v>
       </c>
       <c r="B124">
         <v>2025</v>
       </c>
       <c r="C124">
-        <v>56705534.53</v>
+        <v>56705534.530000001</v>
       </c>
       <c r="D124">
-        <v>56705534.53</v>
+        <v>56705534.530000001</v>
       </c>
       <c r="E124">
         <v>1</v>
@@ -3092,20 +4068,18 @@
         <v>32</v>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Ampliação, Reforma e Requalificação de Centros Educacionais Unificados (CEU)</t>
-        </is>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>129</v>
       </c>
       <c r="B125">
         <v>2025</v>
       </c>
       <c r="C125">
-        <v>55959202.62</v>
+        <v>55959202.619999997</v>
       </c>
       <c r="D125">
-        <v>55959202.62</v>
+        <v>55959202.619999997</v>
       </c>
       <c r="E125">
         <v>1</v>
@@ -3114,17 +4088,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Suporte e Manutenção da Coordenação de Imprensa</t>
-        </is>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>130</v>
       </c>
       <c r="B126">
         <v>2025</v>
       </c>
       <c r="C126">
-        <v>54875018.52</v>
+        <v>54875018.520000003</v>
       </c>
       <c r="D126">
         <v>0</v>
@@ -3136,33 +4108,29 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Desenvolvimento de Estudos, Projetos  e Instrumentos de Políticas Urbanas</t>
-        </is>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>131</v>
       </c>
       <c r="B127">
         <v>2025</v>
       </c>
       <c r="C127">
-        <v>54505414.71</v>
+        <v>54505414.710000001</v>
       </c>
       <c r="D127">
-        <v>14576506.04</v>
+        <v>14576506.039999999</v>
       </c>
       <c r="E127">
-        <v>0.2674322563649016</v>
+        <v>0.26743225636490159</v>
       </c>
       <c r="F127">
         <v>5</v>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação das Praças Digitais</t>
-        </is>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>132</v>
       </c>
       <c r="B128">
         <v>2025</v>
@@ -3180,20 +4148,18 @@
         <v>32</v>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação do Descomplica SP</t>
-        </is>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>133</v>
       </c>
       <c r="B129">
         <v>2025</v>
       </c>
       <c r="C129">
-        <v>53892820.59</v>
+        <v>53892820.590000004</v>
       </c>
       <c r="D129">
-        <v>53892820.59</v>
+        <v>53892820.590000004</v>
       </c>
       <c r="E129">
         <v>1</v>
@@ -3202,20 +4168,18 @@
         <v>32</v>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Administração dos Conselhos Tutelares</t>
-        </is>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>134</v>
       </c>
       <c r="B130">
         <v>2025</v>
       </c>
       <c r="C130">
-        <v>52932143.21</v>
+        <v>52932143.210000001</v>
       </c>
       <c r="D130">
-        <v>52932143.21</v>
+        <v>52932143.210000001</v>
       </c>
       <c r="E130">
         <v>1</v>
@@ -3224,17 +4188,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Capacitação, Formação e Aperfeiçoamento de Servidores</t>
-        </is>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>135</v>
       </c>
       <c r="B131">
         <v>2025</v>
       </c>
       <c r="C131">
-        <v>51119866.28</v>
+        <v>51119866.280000001</v>
       </c>
       <c r="D131">
         <v>0</v>
@@ -3246,11 +4208,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Equipamentos de Proteção Social Especial à População Idosa</t>
-        </is>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>136</v>
       </c>
       <c r="B132">
         <v>2025</v>
@@ -3268,20 +4228,18 @@
         <v>31</v>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Ciclovias, Ciclofaixas e Ciclorrotas</t>
-        </is>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>137</v>
       </c>
       <c r="B133">
         <v>2025</v>
       </c>
       <c r="C133">
-        <v>49160838.74</v>
+        <v>49160838.740000002</v>
       </c>
       <c r="D133">
-        <v>49160838.74</v>
+        <v>49160838.740000002</v>
       </c>
       <c r="E133">
         <v>1</v>
@@ -3290,20 +4248,18 @@
         <v>19</v>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Armazém Solidário</t>
-        </is>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>138</v>
       </c>
       <c r="B134">
         <v>2025</v>
       </c>
       <c r="C134">
-        <v>48748359.48</v>
+        <v>48748359.479999997</v>
       </c>
       <c r="D134">
-        <v>48748359.48</v>
+        <v>48748359.479999997</v>
       </c>
       <c r="E134">
         <v>1</v>
@@ -3312,20 +4268,18 @@
         <v>7</v>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Equipamentos de Proteção Social Especial à Pessoa com Deficiência</t>
-        </is>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>139</v>
       </c>
       <c r="B135">
         <v>2025</v>
       </c>
       <c r="C135">
-        <v>48094878.56</v>
+        <v>48094878.560000002</v>
       </c>
       <c r="D135">
-        <v>48094878.56</v>
+        <v>48094878.560000002</v>
       </c>
       <c r="E135">
         <v>1</v>
@@ -3334,20 +4288,18 @@
         <v>26</v>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Centros Culturais e Teatros</t>
-        </is>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>140</v>
       </c>
       <c r="B136">
         <v>2025</v>
       </c>
       <c r="C136">
-        <v>46840144.7</v>
+        <v>46840144.700000003</v>
       </c>
       <c r="D136">
-        <v>46840144.7</v>
+        <v>46840144.700000003</v>
       </c>
       <c r="E136">
         <v>1</v>
@@ -3356,20 +4308,18 @@
         <v>32</v>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Equipamentos de Proteção Social Básica às Famílias</t>
-        </is>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>141</v>
       </c>
       <c r="B137">
         <v>2025</v>
       </c>
       <c r="C137">
-        <v>44887191.8</v>
+        <v>44887191.799999997</v>
       </c>
       <c r="D137">
-        <v>44887191.8</v>
+        <v>44887191.799999997</v>
       </c>
       <c r="E137">
         <v>1</v>
@@ -3378,17 +4328,15 @@
         <v>27</v>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Acompanhamento das Aprendizagens e Permanência Escolar</t>
-        </is>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>142</v>
       </c>
       <c r="B138">
         <v>2025</v>
       </c>
       <c r="C138">
-        <v>43754632.48</v>
+        <v>43754632.479999997</v>
       </c>
       <c r="D138">
         <v>0</v>
@@ -3400,20 +4348,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Construção de Centros de Educação Infantil - CEI</t>
-        </is>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>143</v>
       </c>
       <c r="B139">
         <v>2025</v>
       </c>
       <c r="C139">
-        <v>43484521.34</v>
+        <v>43484521.340000004</v>
       </c>
       <c r="D139">
-        <v>43484521.34</v>
+        <v>43484521.340000004</v>
       </c>
       <c r="E139">
         <v>1</v>
@@ -3422,20 +4368,18 @@
         <v>13</v>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Bibliotecas Públicas</t>
-        </is>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>144</v>
       </c>
       <c r="B140">
         <v>2025</v>
       </c>
       <c r="C140">
-        <v>41188995.66</v>
+        <v>41188995.659999996</v>
       </c>
       <c r="D140">
-        <v>41188995.66</v>
+        <v>41188995.659999996</v>
       </c>
       <c r="E140">
         <v>1</v>
@@ -3444,55 +4388,49 @@
         <v>32</v>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Transporte Escolar - Educação Especial</t>
-        </is>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>145</v>
       </c>
       <c r="B141">
         <v>2025</v>
       </c>
       <c r="C141">
-        <v>40779801.9</v>
+        <v>40779801.899999999</v>
       </c>
       <c r="D141">
         <v>31376910.25</v>
       </c>
       <c r="E141">
-        <v>0.7694228217915889</v>
+        <v>0.76942282179158894</v>
       </c>
       <c r="F141">
         <v>32</v>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Apoio às Ações Municipais de Turismo</t>
-        </is>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>146</v>
       </c>
       <c r="B142">
         <v>2025</v>
       </c>
       <c r="C142">
-        <v>39960705.22</v>
+        <v>39960705.219999999</v>
       </c>
       <c r="D142">
         <v>2706000</v>
       </c>
       <c r="E142">
-        <v>0.06771652264649397</v>
+        <v>6.7716522646493971E-2</v>
       </c>
       <c r="F142">
         <v>2</v>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>Intervenções em Próprios Municipais</t>
-        </is>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>147</v>
       </c>
       <c r="B143">
         <v>2025</v>
@@ -3510,20 +4448,18 @@
         <v>5</v>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação em Serviços de Saúde Animal</t>
-        </is>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>148</v>
       </c>
       <c r="B144">
         <v>2025</v>
       </c>
       <c r="C144">
-        <v>38553092.6</v>
+        <v>38553092.600000001</v>
       </c>
       <c r="D144">
-        <v>38553092.6</v>
+        <v>38553092.600000001</v>
       </c>
       <c r="E144">
         <v>1</v>
@@ -3532,20 +4468,18 @@
         <v>5</v>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Conservação e Manutenção de Unidades Educacionais - Ensino Fundamental</t>
-        </is>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>149</v>
       </c>
       <c r="B145">
         <v>2025</v>
       </c>
       <c r="C145">
-        <v>38005928.3</v>
+        <v>38005928.299999997</v>
       </c>
       <c r="D145">
-        <v>38005928.3</v>
+        <v>38005928.299999997</v>
       </c>
       <c r="E145">
         <v>1</v>
@@ -3554,20 +4488,18 @@
         <v>32</v>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Equipamentos Públicos Voltados ao Atendimento de Mulheres</t>
-        </is>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>150</v>
       </c>
       <c r="B146">
         <v>2025</v>
       </c>
       <c r="C146">
-        <v>37278357.17</v>
+        <v>37278357.170000002</v>
       </c>
       <c r="D146">
-        <v>37278357.17</v>
+        <v>37278357.170000002</v>
       </c>
       <c r="E146">
         <v>1</v>
@@ -3576,20 +4508,18 @@
         <v>27</v>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Ciclofaixas de Lazer</t>
-        </is>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>151</v>
       </c>
       <c r="B147">
         <v>2025</v>
       </c>
       <c r="C147">
-        <v>36351026.71</v>
+        <v>36351026.710000001</v>
       </c>
       <c r="D147">
-        <v>36351026.71</v>
+        <v>36351026.710000001</v>
       </c>
       <c r="E147">
         <v>1</v>
@@ -3598,20 +4528,18 @@
         <v>7</v>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Unidades de Conservação</t>
-        </is>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>152</v>
       </c>
       <c r="B148">
         <v>2025</v>
       </c>
       <c r="C148">
-        <v>35751598.37</v>
+        <v>35751598.369999997</v>
       </c>
       <c r="D148">
-        <v>35751598.37</v>
+        <v>35751598.369999997</v>
       </c>
       <c r="E148">
         <v>1</v>
@@ -3620,20 +4548,18 @@
         <v>8</v>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Ampliação, Reforma e Requalificação de Centros de Educação Infantil (CEI)</t>
-        </is>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>153</v>
       </c>
       <c r="B149">
         <v>2025</v>
       </c>
       <c r="C149">
-        <v>35456866.39</v>
+        <v>35456866.390000001</v>
       </c>
       <c r="D149">
-        <v>35456866.39</v>
+        <v>35456866.390000001</v>
       </c>
       <c r="E149">
         <v>1</v>
@@ -3642,11 +4568,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Operação e Manutenção da São Paulo Investimentos e Negócios</t>
-        </is>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>154</v>
       </c>
       <c r="B150">
         <v>2025</v>
@@ -3664,20 +4588,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Casas de Cultura</t>
-        </is>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>155</v>
       </c>
       <c r="B151">
         <v>2025</v>
       </c>
       <c r="C151">
-        <v>34529029.52</v>
+        <v>34529029.520000003</v>
       </c>
       <c r="D151">
-        <v>34529029.52</v>
+        <v>34529029.520000003</v>
       </c>
       <c r="E151">
         <v>1</v>
@@ -3686,20 +4608,18 @@
         <v>32</v>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Ampliação, Reforma e Requalificação da Avenida Santo Amaro</t>
-        </is>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>156</v>
       </c>
       <c r="B152">
         <v>2025</v>
       </c>
       <c r="C152">
-        <v>32043919.03</v>
+        <v>32043919.030000001</v>
       </c>
       <c r="D152">
-        <v>32043919.03</v>
+        <v>32043919.030000001</v>
       </c>
       <c r="E152">
         <v>1</v>
@@ -3708,20 +4628,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Políticas de Audiovisual</t>
-        </is>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>157</v>
       </c>
       <c r="B153">
         <v>2025</v>
       </c>
       <c r="C153">
-        <v>32001998.39</v>
+        <v>32001998.390000001</v>
       </c>
       <c r="D153">
-        <v>32001998.39</v>
+        <v>32001998.390000001</v>
       </c>
       <c r="E153">
         <v>1</v>
@@ -3730,20 +4648,18 @@
         <v>32</v>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Construção e Implantação de Equipamentos em Atenção Hospitalar e de Urgência e Emergência</t>
-        </is>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>158</v>
       </c>
       <c r="B154">
         <v>2025</v>
       </c>
       <c r="C154">
-        <v>30834691.29</v>
+        <v>30834691.289999999</v>
       </c>
       <c r="D154">
-        <v>30834691.29</v>
+        <v>30834691.289999999</v>
       </c>
       <c r="E154">
         <v>1</v>
@@ -3752,20 +4668,18 @@
         <v>9</v>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Bilheterias e Postos de Atendimento do Bilhete Único</t>
-        </is>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>159</v>
       </c>
       <c r="B155">
         <v>2025</v>
       </c>
       <c r="C155">
-        <v>30635126.63</v>
+        <v>30635126.629999999</v>
       </c>
       <c r="D155">
-        <v>30635126.63</v>
+        <v>30635126.629999999</v>
       </c>
       <c r="E155">
         <v>1</v>
@@ -3774,11 +4688,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>Projetos para Inclusão da Pessoa com Deficiência</t>
-        </is>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>160</v>
       </c>
       <c r="B156">
         <v>2025</v>
@@ -3787,7 +4699,7 @@
         <v>29993023.82</v>
       </c>
       <c r="D156">
-        <v>21783547.49</v>
+        <v>21783547.489999998</v>
       </c>
       <c r="E156">
         <v>0.7262871399940094</v>
@@ -3796,20 +4708,18 @@
         <v>31</v>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Equipamentos de Convivência e Fortalecimento de Vínculos para a Pessoa Idosa</t>
-        </is>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>161</v>
       </c>
       <c r="B157">
         <v>2025</v>
       </c>
       <c r="C157">
-        <v>29348458.54</v>
+        <v>29348458.539999999</v>
       </c>
       <c r="D157">
-        <v>29348458.54</v>
+        <v>29348458.539999999</v>
       </c>
       <c r="E157">
         <v>1</v>
@@ -3818,42 +4728,38 @@
         <v>30</v>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação dos Serviços de DST / AIDS</t>
-        </is>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>162</v>
       </c>
       <c r="B158">
         <v>2025</v>
       </c>
       <c r="C158">
-        <v>28844062.65</v>
+        <v>28844062.649999999</v>
       </c>
       <c r="D158">
-        <v>19121584.06</v>
+        <v>19121584.059999999</v>
       </c>
       <c r="E158">
-        <v>0.6629296396983106</v>
+        <v>0.66292963969831065</v>
       </c>
       <c r="F158">
         <v>28</v>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>Programa Municipal de Apoio a Projetos Culturais (PRO-MAC)</t>
-        </is>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>163</v>
       </c>
       <c r="B159">
         <v>2025</v>
       </c>
       <c r="C159">
-        <v>28754680.83</v>
+        <v>28754680.829999998</v>
       </c>
       <c r="D159">
-        <v>28754680.83</v>
+        <v>28754680.829999998</v>
       </c>
       <c r="E159">
         <v>1</v>
@@ -3862,11 +4768,9 @@
         <v>25</v>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>Aposentadoria Complementar aos Servidores da São Paulo Transporte S/A</t>
-        </is>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>164</v>
       </c>
       <c r="B160">
         <v>2025</v>
@@ -3884,20 +4788,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>Construção de Escolas Municipais de Educação Infantil (EMEI)</t>
-        </is>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>165</v>
       </c>
       <c r="B161">
         <v>2025</v>
       </c>
       <c r="C161">
-        <v>27048914.35</v>
+        <v>27048914.350000001</v>
       </c>
       <c r="D161">
-        <v>27048914.35</v>
+        <v>27048914.350000001</v>
       </c>
       <c r="E161">
         <v>1</v>
@@ -3906,11 +4808,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>Ações de Melhorias para Administração Fazendária</t>
-        </is>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>166</v>
       </c>
       <c r="B162">
         <v>2025</v>
@@ -3928,11 +4828,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>Centro Municipal para Pessoas com Transtorno do Espectro Autista</t>
-        </is>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>167</v>
       </c>
       <c r="B163">
         <v>2025</v>
@@ -3950,17 +4848,15 @@
         <v>4</v>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>Ações de Desestatização</t>
-        </is>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>168</v>
       </c>
       <c r="B164">
         <v>2025</v>
       </c>
       <c r="C164">
-        <v>25120930.7</v>
+        <v>25120930.699999999</v>
       </c>
       <c r="D164">
         <v>0</v>
@@ -3972,17 +4868,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>Compensação Financeira - Outros Fundos de Previdência</t>
-        </is>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>169</v>
       </c>
       <c r="B165">
         <v>2025</v>
       </c>
       <c r="C165">
-        <v>24763727.36</v>
+        <v>24763727.359999999</v>
       </c>
       <c r="D165">
         <v>0</v>
@@ -3994,17 +4888,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>Contraprestação de Parceria Público-Privada (PPP) - CEUs</t>
-        </is>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>170</v>
       </c>
       <c r="B166">
         <v>2025</v>
       </c>
       <c r="C166">
-        <v>24305962.83</v>
+        <v>24305962.829999998</v>
       </c>
       <c r="D166">
         <v>0</v>
@@ -4016,11 +4908,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>Eventos Educacionais, Culturais e Esportivos nos Centros Educacionais Unificados</t>
-        </is>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>171</v>
       </c>
       <c r="B167">
         <v>2025</v>
@@ -4038,20 +4928,18 @@
         <v>31</v>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>Programação da Virada Esportiva</t>
-        </is>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>172</v>
       </c>
       <c r="B168">
         <v>2025</v>
       </c>
       <c r="C168">
-        <v>21826729.53</v>
+        <v>21826729.530000001</v>
       </c>
       <c r="D168">
-        <v>21826729.53</v>
+        <v>21826729.530000001</v>
       </c>
       <c r="E168">
         <v>1</v>
@@ -4060,11 +4948,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>Ampliação, Reforma e Requalificação de Clube da Comunidade (CDC)</t>
-        </is>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>173</v>
       </c>
       <c r="B169">
         <v>2025</v>
@@ -4082,20 +4968,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Centros Municipais de Educação Infantil(CEMEI)</t>
-        </is>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>174</v>
       </c>
       <c r="B170">
         <v>2025</v>
       </c>
       <c r="C170">
-        <v>21662494.24</v>
+        <v>21662494.239999998</v>
       </c>
       <c r="D170">
-        <v>21662494.24</v>
+        <v>21662494.239999998</v>
       </c>
       <c r="E170">
         <v>1</v>
@@ -4104,20 +4988,18 @@
         <v>32</v>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>Escola Municipal de Educação Artística - EMIA</t>
-        </is>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>175</v>
       </c>
       <c r="B171">
         <v>2025</v>
       </c>
       <c r="C171">
-        <v>21662072.44</v>
+        <v>21662072.440000001</v>
       </c>
       <c r="D171">
-        <v>21662072.44</v>
+        <v>21662072.440000001</v>
       </c>
       <c r="E171">
         <v>1</v>
@@ -4126,42 +5008,38 @@
         <v>20</v>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>Administração do Edifício Matarazzo</t>
-        </is>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>176</v>
       </c>
       <c r="B172">
         <v>2025</v>
       </c>
       <c r="C172">
-        <v>21592963.78</v>
+        <v>21592963.780000001</v>
       </c>
       <c r="D172">
-        <v>5781452.18</v>
+        <v>5781452.1799999997</v>
       </c>
       <c r="E172">
-        <v>0.2677470419949919</v>
+        <v>0.26774704199499189</v>
       </c>
       <c r="F172">
         <v>1</v>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>Ações de formação das Escolas de Música e Dança do Theatro Municipal e da Praça das Artes</t>
-        </is>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>177</v>
       </c>
       <c r="B173">
         <v>2025</v>
       </c>
       <c r="C173">
-        <v>21113462.38</v>
+        <v>21113462.379999999</v>
       </c>
       <c r="D173">
-        <v>21113462.38</v>
+        <v>21113462.379999999</v>
       </c>
       <c r="E173">
         <v>1</v>
@@ -4170,17 +5048,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>Encargos Referentes a Arrecadação</t>
-        </is>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>178</v>
       </c>
       <c r="B174">
         <v>2025</v>
       </c>
       <c r="C174">
-        <v>21034577.37</v>
+        <v>21034577.370000001</v>
       </c>
       <c r="D174">
         <v>0</v>
@@ -4192,20 +5068,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>Políticas, Programas e Ações para Juventude</t>
-        </is>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>179</v>
       </c>
       <c r="B175">
         <v>2025</v>
       </c>
       <c r="C175">
-        <v>20294506.05</v>
+        <v>20294506.050000001</v>
       </c>
       <c r="D175">
-        <v>20294506.05</v>
+        <v>20294506.050000001</v>
       </c>
       <c r="E175">
         <v>1</v>
@@ -4214,20 +5088,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>Construção de Ciclovias, Ciclofaixas e Ciclorrotas</t>
-        </is>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>180</v>
       </c>
       <c r="B176">
         <v>2025</v>
       </c>
       <c r="C176">
-        <v>19854937.38</v>
+        <v>19854937.379999999</v>
       </c>
       <c r="D176">
-        <v>19854937.38</v>
+        <v>19854937.379999999</v>
       </c>
       <c r="E176">
         <v>1</v>
@@ -4236,42 +5108,38 @@
         <v>7</v>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>Fomento à Cooperação, Parcerias e Captação de Investimentos Internacionais</t>
-        </is>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>181</v>
       </c>
       <c r="B177">
         <v>2025</v>
       </c>
       <c r="C177">
-        <v>19828722.42</v>
+        <v>19828722.420000002</v>
       </c>
       <c r="D177">
-        <v>5588711.02</v>
+        <v>5588711.0199999996</v>
       </c>
       <c r="E177">
-        <v>0.2818492740794543</v>
+        <v>0.28184927407945431</v>
       </c>
       <c r="F177">
         <v>1</v>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação dos Equipamentos Públicos Voltados ao Atendimento Inclusivo</t>
-        </is>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>182</v>
       </c>
       <c r="B178">
         <v>2025</v>
       </c>
       <c r="C178">
-        <v>19391707.08</v>
+        <v>19391707.079999998</v>
       </c>
       <c r="D178">
-        <v>19391707.08</v>
+        <v>19391707.079999998</v>
       </c>
       <c r="E178">
         <v>1</v>
@@ -4280,20 +5148,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>Preservação do Patrimônio Histórico, Artístico, Cultural e Arqueológico</t>
-        </is>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>183</v>
       </c>
       <c r="B179">
         <v>2025</v>
       </c>
       <c r="C179">
-        <v>19182373.71</v>
+        <v>19182373.710000001</v>
       </c>
       <c r="D179">
-        <v>19182373.71</v>
+        <v>19182373.710000001</v>
       </c>
       <c r="E179">
         <v>1</v>
@@ -4302,20 +5168,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação do Sistema de Transporte Público Hidroviário</t>
-        </is>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>184</v>
       </c>
       <c r="B180">
         <v>2025</v>
       </c>
       <c r="C180">
-        <v>19091682.67</v>
+        <v>19091682.670000002</v>
       </c>
       <c r="D180">
-        <v>19091682.67</v>
+        <v>19091682.670000002</v>
       </c>
       <c r="E180">
         <v>1</v>
@@ -4324,20 +5188,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>Qualificação e Transformação Urbanística - AIU-SCE - Lei 17.844/2022</t>
-        </is>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>185</v>
       </c>
       <c r="B181">
         <v>2025</v>
       </c>
       <c r="C181">
-        <v>19023008.24</v>
+        <v>19023008.239999998</v>
       </c>
       <c r="D181">
-        <v>19023008.24</v>
+        <v>19023008.239999998</v>
       </c>
       <c r="E181">
         <v>1</v>
@@ -4346,11 +5208,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>Políticas, Programas e Ações para a População em Situação de Rua</t>
-        </is>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>186</v>
       </c>
       <c r="B182">
         <v>2025</v>
@@ -4368,20 +5228,18 @@
         <v>13</v>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>Manutenção de Unidades Habitacionais</t>
-        </is>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>187</v>
       </c>
       <c r="B183">
         <v>2025</v>
       </c>
       <c r="C183">
-        <v>18802206.94</v>
+        <v>18802206.940000001</v>
       </c>
       <c r="D183">
-        <v>18802206.94</v>
+        <v>18802206.940000001</v>
       </c>
       <c r="E183">
         <v>1</v>
@@ -4390,20 +5248,18 @@
         <v>7</v>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação do Centro Cultural São Paulo</t>
-        </is>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>188</v>
       </c>
       <c r="B184">
         <v>2025</v>
       </c>
       <c r="C184">
-        <v>18666060.12</v>
+        <v>18666060.120000001</v>
       </c>
       <c r="D184">
-        <v>18666060.12</v>
+        <v>18666060.120000001</v>
       </c>
       <c r="E184">
         <v>1</v>
@@ -4412,20 +5268,18 @@
         <v>5</v>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>Ampliação, Reforma e Requalificação de Unidades Habitacionais</t>
-        </is>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>189</v>
       </c>
       <c r="B185">
         <v>2025</v>
       </c>
       <c r="C185">
-        <v>18652479.58</v>
+        <v>18652479.579999998</v>
       </c>
       <c r="D185">
-        <v>18652479.58</v>
+        <v>18652479.579999998</v>
       </c>
       <c r="E185">
         <v>1</v>
@@ -4434,17 +5288,15 @@
         <v>7</v>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>Apoio e Suporte Técnico para o Desenvolvimento de Ações Pertinentes à Fiscalização e Escrituração de Certificados de Potencial Adicional de Construção - CEPACs</t>
-        </is>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>190</v>
       </c>
       <c r="B186">
         <v>2025</v>
       </c>
       <c r="C186">
-        <v>18636143.6</v>
+        <v>18636143.600000001</v>
       </c>
       <c r="D186">
         <v>0</v>
@@ -4456,20 +5308,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>Lei de Fomento ao Teatro</t>
-        </is>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>191</v>
       </c>
       <c r="B187">
         <v>2025</v>
       </c>
       <c r="C187">
-        <v>18441276.12</v>
+        <v>18441276.120000001</v>
       </c>
       <c r="D187">
-        <v>18441276.12</v>
+        <v>18441276.120000001</v>
       </c>
       <c r="E187">
         <v>1</v>
@@ -4478,20 +5328,18 @@
         <v>15</v>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Equipamentos do Departamento dos Museus Municipais</t>
-        </is>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>192</v>
       </c>
       <c r="B188">
         <v>2025</v>
       </c>
       <c r="C188">
-        <v>18381071.38</v>
+        <v>18381071.379999999</v>
       </c>
       <c r="D188">
-        <v>18381071.38</v>
+        <v>18381071.379999999</v>
       </c>
       <c r="E188">
         <v>1</v>
@@ -4500,11 +5348,9 @@
         <v>19</v>
       </c>
     </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>Transferência de Recursos Financeiros para as Unidades Educacionais - Centro Educacional Unificado (CEU)</t>
-        </is>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>193</v>
       </c>
       <c r="B189">
         <v>2025</v>
@@ -4522,17 +5368,15 @@
         <v>22</v>
       </c>
     </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>Desenvolvimento de Sistemas de Informação e Comunicação</t>
-        </is>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>194</v>
       </c>
       <c r="B190">
         <v>2025</v>
       </c>
       <c r="C190">
-        <v>17387407.83</v>
+        <v>17387407.829999998</v>
       </c>
       <c r="D190">
         <v>0</v>
@@ -4544,11 +5388,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>Promoção da Arborização Urbana</t>
-        </is>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>195</v>
       </c>
       <c r="B191">
         <v>2025</v>
@@ -4566,11 +5408,9 @@
         <v>32</v>
       </c>
     </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Centro de Referência de Segurança Alimentar e Nutricional</t>
-        </is>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>196</v>
       </c>
       <c r="B192">
         <v>2025</v>
@@ -4588,11 +5428,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação dos Pólos Regionais de Esporte</t>
-        </is>
+    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>197</v>
       </c>
       <c r="B193">
         <v>2025</v>
@@ -4610,20 +5448,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Praças, Canteiros Centrais e Remanescentes</t>
-        </is>
+    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>198</v>
       </c>
       <c r="B194">
         <v>2025</v>
       </c>
       <c r="C194">
-        <v>16084835.87</v>
+        <v>16084835.869999999</v>
       </c>
       <c r="D194">
-        <v>16084835.87</v>
+        <v>16084835.869999999</v>
       </c>
       <c r="E194">
         <v>1</v>
@@ -4632,20 +5468,18 @@
         <v>32</v>
       </c>
     </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>Implantação de Estrutura Turística no Triângulo Histórico</t>
-        </is>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>199</v>
       </c>
       <c r="B195">
         <v>2025</v>
       </c>
       <c r="C195">
-        <v>15120864.55</v>
+        <v>15120864.550000001</v>
       </c>
       <c r="D195">
-        <v>15120864.55</v>
+        <v>15120864.550000001</v>
       </c>
       <c r="E195">
         <v>1</v>
@@ -4654,20 +5488,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>Operação e Manutenção de Unidade da Fundação Paulistana - FPETC</t>
-        </is>
+    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>200</v>
       </c>
       <c r="B196">
         <v>2025</v>
       </c>
       <c r="C196">
-        <v>14963285.94</v>
+        <v>14963285.939999999</v>
       </c>
       <c r="D196">
-        <v>14963285.94</v>
+        <v>14963285.939999999</v>
       </c>
       <c r="E196">
         <v>1</v>
@@ -4676,20 +5508,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Equipamentos Culturais</t>
-        </is>
+    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>201</v>
       </c>
       <c r="B197">
         <v>2025</v>
       </c>
       <c r="C197">
-        <v>14870885.79</v>
+        <v>14870885.789999999</v>
       </c>
       <c r="D197">
-        <v>14870885.79</v>
+        <v>14870885.789999999</v>
       </c>
       <c r="E197">
         <v>1</v>
@@ -4698,11 +5528,9 @@
         <v>22</v>
       </c>
     </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>Programa Saúde na Escola</t>
-        </is>
+    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>202</v>
       </c>
       <c r="B198">
         <v>2025</v>
@@ -4720,20 +5548,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Telecentros</t>
-        </is>
+    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>203</v>
       </c>
       <c r="B199">
         <v>2025</v>
       </c>
       <c r="C199">
-        <v>14291121.78</v>
+        <v>14291121.779999999</v>
       </c>
       <c r="D199">
-        <v>14291121.78</v>
+        <v>14291121.779999999</v>
       </c>
       <c r="E199">
         <v>1</v>
@@ -4742,20 +5568,18 @@
         <v>29</v>
       </c>
     </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>Construção e Implantação de Parques Urbanos e Lineares</t>
-        </is>
+    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>204</v>
       </c>
       <c r="B200">
         <v>2025</v>
       </c>
       <c r="C200">
-        <v>14222824.96</v>
+        <v>14222824.960000001</v>
       </c>
       <c r="D200">
-        <v>14222824.96</v>
+        <v>14222824.960000001</v>
       </c>
       <c r="E200">
         <v>1</v>
@@ -4764,20 +5588,18 @@
         <v>9</v>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>Fomento à Cultura da Periferia de São Paulo</t>
-        </is>
+    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>205</v>
       </c>
       <c r="B201">
         <v>2025</v>
       </c>
       <c r="C201">
-        <v>13951513.62</v>
+        <v>13951513.619999999</v>
       </c>
       <c r="D201">
-        <v>13951513.62</v>
+        <v>13951513.619999999</v>
       </c>
       <c r="E201">
         <v>1</v>
@@ -4786,11 +5608,9 @@
         <v>18</v>
       </c>
     </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>Ampliação, Reforma e Requalificação de Prédios Administrativos</t>
-        </is>
+    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>206</v>
       </c>
       <c r="B202">
         <v>2025</v>
@@ -4808,11 +5628,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>Construção e Implantação de Centros Educacionais Unificados (CEU)</t>
-        </is>
+    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>207</v>
       </c>
       <c r="B203">
         <v>2025</v>
@@ -4830,20 +5648,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>Execução do Programa para a Valorização de Iniciativas Culturais</t>
-        </is>
+    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>208</v>
       </c>
       <c r="B204">
         <v>2025</v>
       </c>
       <c r="C204">
-        <v>13103647.53</v>
+        <v>13103647.529999999</v>
       </c>
       <c r="D204">
-        <v>13103647.53</v>
+        <v>13103647.529999999</v>
       </c>
       <c r="E204">
         <v>1</v>
@@ -4852,11 +5668,9 @@
         <v>32</v>
       </c>
     </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Equipamentos de Proteção Jurídico Social</t>
-        </is>
+    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>209</v>
       </c>
       <c r="B205">
         <v>2025</v>
@@ -4874,11 +5688,9 @@
         <v>32</v>
       </c>
     </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Unidades Educacionais - Escola Municipal de Educação Fundamental e Médio (EMEFM)</t>
-        </is>
+    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>210</v>
       </c>
       <c r="B206">
         <v>2025</v>
@@ -4896,11 +5708,9 @@
         <v>18</v>
       </c>
     </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação da Rede Parceira - Alfabetização de Jovens e Adultos</t>
-        </is>
+    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>211</v>
       </c>
       <c r="B207">
         <v>2025</v>
@@ -4918,11 +5728,9 @@
         <v>25</v>
       </c>
     </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>Manutenção de Modalidades Desportivas do Centro Olímpico de Treinamento e Pesquisa (COTP)</t>
-        </is>
+    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>212</v>
       </c>
       <c r="B208">
         <v>2025</v>
@@ -4940,11 +5748,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>Compensações Ambientais</t>
-        </is>
+    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>213</v>
       </c>
       <c r="B209">
         <v>2025</v>
@@ -4962,11 +5768,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>Ações de Difusão Cultural do Theatro Municipal - Administrativos</t>
-        </is>
+    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>214</v>
       </c>
       <c r="B210">
         <v>2025</v>
@@ -4984,20 +5788,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>Programa Jovem Monitor Cultural</t>
-        </is>
+    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>215</v>
       </c>
       <c r="B211">
         <v>2025</v>
       </c>
       <c r="C211">
-        <v>12207597.05</v>
+        <v>12207597.050000001</v>
       </c>
       <c r="D211">
-        <v>12207597.05</v>
+        <v>12207597.050000001</v>
       </c>
       <c r="E211">
         <v>1</v>
@@ -5006,20 +5808,18 @@
         <v>32</v>
       </c>
     </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Viveiros de Produção</t>
-        </is>
+    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>216</v>
       </c>
       <c r="B212">
         <v>2025</v>
       </c>
       <c r="C212">
-        <v>12081547.05</v>
+        <v>12081547.050000001</v>
       </c>
       <c r="D212">
-        <v>12081547.05</v>
+        <v>12081547.050000001</v>
       </c>
       <c r="E212">
         <v>1</v>
@@ -5028,20 +5828,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>Operação e Manutenção dos Centros de Apoio ao Trabalho e Empreendedorismo</t>
-        </is>
+    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>217</v>
       </c>
       <c r="B213">
         <v>2025</v>
       </c>
       <c r="C213">
-        <v>11866192.69</v>
+        <v>11866192.689999999</v>
       </c>
       <c r="D213">
-        <v>11866192.69</v>
+        <v>11866192.689999999</v>
       </c>
       <c r="E213">
         <v>1</v>
@@ -5050,20 +5848,18 @@
         <v>32</v>
       </c>
     </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>Ampliação, Reforma e Requalificação de Áreas Públicas</t>
-        </is>
+    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>218</v>
       </c>
       <c r="B214">
         <v>2025</v>
       </c>
       <c r="C214">
-        <v>11852982.06</v>
+        <v>11852982.060000001</v>
       </c>
       <c r="D214">
-        <v>11852982.06</v>
+        <v>11852982.060000001</v>
       </c>
       <c r="E214">
         <v>1</v>
@@ -5072,11 +5868,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>Corredor Aricanduva - Centro de Controle Operacional - COP - 2.1</t>
-        </is>
+    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>219</v>
       </c>
       <c r="B215">
         <v>2025</v>
@@ -5094,11 +5888,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação da Biblioteca Mario de Andrade</t>
-        </is>
+    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>220</v>
       </c>
       <c r="B216">
         <v>2025</v>
@@ -5116,17 +5908,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>Ações de Planejamento, Monitoramento e Avaliação de Políticas Públicas</t>
-        </is>
+    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>221</v>
       </c>
       <c r="B217">
         <v>2025</v>
       </c>
       <c r="C217">
-        <v>11219880.54</v>
+        <v>11219880.539999999</v>
       </c>
       <c r="D217">
         <v>0</v>
@@ -5138,11 +5928,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>Despesas Administrativas para Execução de Ações Judiciais - Processamento de Feitos</t>
-        </is>
+    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>222</v>
       </c>
       <c r="B218">
         <v>2025</v>
@@ -5160,11 +5948,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>Obras e Serviços nas Áreas de Riscos Geológicos - Preventivas</t>
-        </is>
+    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>223</v>
       </c>
       <c r="B219">
         <v>2025</v>
@@ -5182,11 +5968,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>Promoção à Saúde do Servidor Municipal</t>
-        </is>
+    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>224</v>
       </c>
       <c r="B220">
         <v>2025</v>
@@ -5204,20 +5988,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>Subvenção e Contribuições a Entidades Culturais</t>
-        </is>
+    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>225</v>
       </c>
       <c r="B221">
         <v>2025</v>
       </c>
       <c r="C221">
-        <v>10944338.53</v>
+        <v>10944338.529999999</v>
       </c>
       <c r="D221">
-        <v>10944338.53</v>
+        <v>10944338.529999999</v>
       </c>
       <c r="E221">
         <v>1</v>
@@ -5226,11 +6008,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação do Programa Melhor em Casa</t>
-        </is>
+    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>226</v>
       </c>
       <c r="B222">
         <v>2025</v>
@@ -5248,11 +6028,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação da Rede Parceira - Educação Especial</t>
-        </is>
+    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>227</v>
       </c>
       <c r="B223">
         <v>2025</v>
@@ -5270,11 +6048,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>Políticas, Programas e Ações para Mulheres</t>
-        </is>
+    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>228</v>
       </c>
       <c r="B224">
         <v>2025</v>
@@ -5292,11 +6068,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>Ampliação, Reforma e Requalificação de Equipamentos Culturais</t>
-        </is>
+    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>229</v>
       </c>
       <c r="B225">
         <v>2025</v>
@@ -5314,11 +6088,9 @@
         <v>19</v>
       </c>
     </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>Administração do Autódromo de Interlagos</t>
-        </is>
+    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>230</v>
       </c>
       <c r="B226">
         <v>2025</v>
@@ -5336,11 +6108,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação do Serviço de Moto Verificação</t>
-        </is>
+    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>231</v>
       </c>
       <c r="B227">
         <v>2025</v>
@@ -5358,17 +6128,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>Operação e Manutenção da Infraestrutura Turística</t>
-        </is>
+    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>232</v>
       </c>
       <c r="B228">
         <v>2025</v>
       </c>
       <c r="C228">
-        <v>10425671.89</v>
+        <v>10425671.890000001</v>
       </c>
       <c r="D228">
         <v>0</v>
@@ -5380,20 +6148,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação da Casa da Mulher Brasileira</t>
-        </is>
+    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>233</v>
       </c>
       <c r="B229">
         <v>2025</v>
       </c>
       <c r="C229">
-        <v>10354999.05</v>
+        <v>10354999.050000001</v>
       </c>
       <c r="D229">
-        <v>10354999.05</v>
+        <v>10354999.050000001</v>
       </c>
       <c r="E229">
         <v>1</v>
@@ -5402,17 +6168,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>Gratificação de Municipalização - Saúde - Lei 13.510/03</t>
-        </is>
+    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>234</v>
       </c>
       <c r="B230">
         <v>2025</v>
       </c>
       <c r="C230">
-        <v>10326196.94</v>
+        <v>10326196.939999999</v>
       </c>
       <c r="D230">
         <v>0</v>
@@ -5424,11 +6188,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>Construção e Implantação de Unidades de Conservação</t>
-        </is>
+    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>235</v>
       </c>
       <c r="B231">
         <v>2025</v>
@@ -5446,20 +6208,18 @@
         <v>5</v>
       </c>
     </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>Locação Social</t>
-        </is>
+    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>236</v>
       </c>
       <c r="B232">
         <v>2025</v>
       </c>
       <c r="C232">
-        <v>9862344.91</v>
+        <v>9862344.9100000001</v>
       </c>
       <c r="D232">
-        <v>9862344.91</v>
+        <v>9862344.9100000001</v>
       </c>
       <c r="E232">
         <v>1</v>
@@ -5468,17 +6228,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>Sistema de Avaliação Escolar dos Alunos da Rede Municipal de Ensino</t>
-        </is>
+    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>237</v>
       </c>
       <c r="B233">
         <v>2025</v>
       </c>
       <c r="C233">
-        <v>9805367.640000001</v>
+        <v>9805367.6400000006</v>
       </c>
       <c r="D233">
         <v>0</v>
@@ -5490,42 +6248,38 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>Estudos, Planos e Projetos Ambientais</t>
-        </is>
+    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>238</v>
       </c>
       <c r="B234">
         <v>2025</v>
       </c>
       <c r="C234">
-        <v>9780730.539999999</v>
+        <v>9780730.5399999991</v>
       </c>
       <c r="D234">
-        <v>9319880.439999999</v>
+        <v>9319880.4399999995</v>
       </c>
       <c r="E234">
-        <v>0.9528818324852859</v>
+        <v>0.95288183248528591</v>
       </c>
       <c r="F234">
         <v>32</v>
       </c>
     </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Equipamentos Públicos Voltados à Promoção da Igualdade Racial</t>
-        </is>
+    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>239</v>
       </c>
       <c r="B235">
         <v>2025</v>
       </c>
       <c r="C235">
-        <v>9401595.109999999</v>
+        <v>9401595.1099999994</v>
       </c>
       <c r="D235">
-        <v>9401595.109999999</v>
+        <v>9401595.1099999994</v>
       </c>
       <c r="E235">
         <v>1</v>
@@ -5534,20 +6288,18 @@
         <v>5</v>
       </c>
     </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Equipamentos Públicos Voltados ao Atendimento da População de Rua</t>
-        </is>
+    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>240</v>
       </c>
       <c r="B236">
         <v>2025</v>
       </c>
       <c r="C236">
-        <v>9356133.699999999</v>
+        <v>9356133.6999999993</v>
       </c>
       <c r="D236">
-        <v>9356133.699999999</v>
+        <v>9356133.6999999993</v>
       </c>
       <c r="E236">
         <v>1</v>
@@ -5556,17 +6308,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação do Policiamento de Trânsito</t>
-        </is>
+    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>241</v>
       </c>
       <c r="B237">
         <v>2025</v>
       </c>
       <c r="C237">
-        <v>9222878.07</v>
+        <v>9222878.0700000003</v>
       </c>
       <c r="D237">
         <v>0</v>
@@ -5578,20 +6328,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>Plano de Contingência para Situações de Baixas Temperaturas - Decreto nº 62.760/2023</t>
-        </is>
+    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>242</v>
       </c>
       <c r="B238">
         <v>2025</v>
       </c>
       <c r="C238">
-        <v>9215518.18</v>
+        <v>9215518.1799999997</v>
       </c>
       <c r="D238">
-        <v>9215518.18</v>
+        <v>9215518.1799999997</v>
       </c>
       <c r="E238">
         <v>1</v>
@@ -5600,20 +6348,18 @@
         <v>32</v>
       </c>
     </row>
-    <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Equipamentos da Assistência Social</t>
-        </is>
+    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>243</v>
       </c>
       <c r="B239">
         <v>2025</v>
       </c>
       <c r="C239">
-        <v>9006914.82</v>
+        <v>9006914.8200000003</v>
       </c>
       <c r="D239">
-        <v>9006914.82</v>
+        <v>9006914.8200000003</v>
       </c>
       <c r="E239">
         <v>1</v>
@@ -5622,20 +6368,18 @@
         <v>30</v>
       </c>
     </row>
-    <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>Prêmio Zé Renato</t>
-        </is>
+    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>244</v>
       </c>
       <c r="B240">
         <v>2025</v>
       </c>
       <c r="C240">
-        <v>8891738.119999999</v>
+        <v>8891738.1199999992</v>
       </c>
       <c r="D240">
-        <v>8891738.119999999</v>
+        <v>8891738.1199999992</v>
       </c>
       <c r="E240">
         <v>1</v>
@@ -5644,20 +6388,18 @@
         <v>3</v>
       </c>
     </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação dos Serviços de Atendimento e Manejo da Fauna Silvestre</t>
-        </is>
+    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>245</v>
       </c>
       <c r="B241">
         <v>2025</v>
       </c>
       <c r="C241">
-        <v>8785942.76</v>
+        <v>8785942.7599999998</v>
       </c>
       <c r="D241">
-        <v>8785942.76</v>
+        <v>8785942.7599999998</v>
       </c>
       <c r="E241">
         <v>1</v>
@@ -5666,20 +6408,18 @@
         <v>3</v>
       </c>
     </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Unidades Educacionais - Educação Indígena</t>
-        </is>
+    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>246</v>
       </c>
       <c r="B242">
         <v>2025</v>
       </c>
       <c r="C242">
-        <v>8739289.949999999</v>
+        <v>8739289.9499999993</v>
       </c>
       <c r="D242">
-        <v>8739289.949999999</v>
+        <v>8739289.9499999993</v>
       </c>
       <c r="E242">
         <v>1</v>
@@ -5688,20 +6428,18 @@
         <v>6</v>
       </c>
     </row>
-    <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>Construção de Escolas Municipais de Ensino Fundamental (EMEF)</t>
-        </is>
+    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>247</v>
       </c>
       <c r="B243">
         <v>2025</v>
       </c>
       <c r="C243">
-        <v>8523367.76</v>
+        <v>8523367.7599999998</v>
       </c>
       <c r="D243">
-        <v>8523367.76</v>
+        <v>8523367.7599999998</v>
       </c>
       <c r="E243">
         <v>1</v>
@@ -5710,17 +6448,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="244">
-      <c r="A244" t="inlineStr">
-        <is>
-          <t>Incentivo ao Uso de Veículos Elétricos ou Movidos a Hidrogênio</t>
-        </is>
+    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>248</v>
       </c>
       <c r="B244">
         <v>2025</v>
       </c>
       <c r="C244">
-        <v>8045576.24</v>
+        <v>8045576.2400000002</v>
       </c>
       <c r="D244">
         <v>0</v>
@@ -5732,11 +6468,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245">
-      <c r="A245" t="inlineStr">
-        <is>
-          <t>Reforma e Acessibilidade em Passeios Públicos</t>
-        </is>
+    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
+        <v>249</v>
       </c>
       <c r="B245">
         <v>2025</v>
@@ -5754,20 +6488,18 @@
         <v>3</v>
       </c>
     </row>
-    <row r="246">
-      <c r="A246" t="inlineStr">
-        <is>
-          <t>Lei de Fomento à Dança</t>
-        </is>
+    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A246" t="s">
+        <v>250</v>
       </c>
       <c r="B246">
         <v>2025</v>
       </c>
       <c r="C246">
-        <v>7882016.45</v>
+        <v>7882016.4500000002</v>
       </c>
       <c r="D246">
-        <v>7882016.45</v>
+        <v>7882016.4500000002</v>
       </c>
       <c r="E246">
         <v>1</v>
@@ -5776,20 +6508,18 @@
         <v>13</v>
       </c>
     </row>
-    <row r="247">
-      <c r="A247" t="inlineStr">
-        <is>
-          <t>Serviços de Desfazimento e Demolição de Construções Irregulares em Áreas de Proteção Ambiental</t>
-        </is>
+    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
+        <v>251</v>
       </c>
       <c r="B247">
         <v>2025</v>
       </c>
       <c r="C247">
-        <v>7499872.51</v>
+        <v>7499872.5099999998</v>
       </c>
       <c r="D247">
-        <v>7499872.51</v>
+        <v>7499872.5099999998</v>
       </c>
       <c r="E247">
         <v>1</v>
@@ -5798,20 +6528,18 @@
         <v>32</v>
       </c>
     </row>
-    <row r="248">
-      <c r="A248" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Unidades Educacionais - Centro Integrado de Jovens e Adultos (CIEJA)</t>
-        </is>
+    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A248" t="s">
+        <v>252</v>
       </c>
       <c r="B248">
         <v>2025</v>
       </c>
       <c r="C248">
-        <v>7343903.53</v>
+        <v>7343903.5300000003</v>
       </c>
       <c r="D248">
-        <v>7343903.53</v>
+        <v>7343903.5300000003</v>
       </c>
       <c r="E248">
         <v>1</v>
@@ -5820,11 +6548,9 @@
         <v>27</v>
       </c>
     </row>
-    <row r="249">
-      <c r="A249" t="inlineStr">
-        <is>
-          <t>Fomento e Apoio ao Cooperativismo</t>
-        </is>
+    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A249" t="s">
+        <v>253</v>
       </c>
       <c r="B249">
         <v>2025</v>
@@ -5842,20 +6568,18 @@
         <v>21</v>
       </c>
     </row>
-    <row r="250">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>Programação de Atividades Culturais de Casas de Cultura</t>
-        </is>
+    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A250" t="s">
+        <v>254</v>
       </c>
       <c r="B250">
         <v>2025</v>
       </c>
       <c r="C250">
-        <v>7200183.07</v>
+        <v>7200183.0700000003</v>
       </c>
       <c r="D250">
-        <v>7200183.07</v>
+        <v>7200183.0700000003</v>
       </c>
       <c r="E250">
         <v>1</v>
@@ -5864,20 +6588,18 @@
         <v>31</v>
       </c>
     </row>
-    <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>Políticas, Programas e Ações Inclusivas</t>
-        </is>
+    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A251" t="s">
+        <v>255</v>
       </c>
       <c r="B251">
         <v>2025</v>
       </c>
       <c r="C251">
-        <v>7056576.76</v>
+        <v>7056576.7599999998</v>
       </c>
       <c r="D251">
-        <v>7056576.76</v>
+        <v>7056576.7599999998</v>
       </c>
       <c r="E251">
         <v>1</v>
@@ -5886,20 +6608,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>Conservação e Manutenção de Unidades Educacionais - CEU</t>
-        </is>
+    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A252" t="s">
+        <v>256</v>
       </c>
       <c r="B252">
         <v>2025</v>
       </c>
       <c r="C252">
-        <v>6981990.76</v>
+        <v>6981990.7599999998</v>
       </c>
       <c r="D252">
-        <v>6981990.76</v>
+        <v>6981990.7599999998</v>
       </c>
       <c r="E252">
         <v>1</v>
@@ -5908,20 +6628,18 @@
         <v>30</v>
       </c>
     </row>
-    <row r="253">
-      <c r="A253" t="inlineStr">
-        <is>
-          <t>Fomento ao Circo/Edital Xamego</t>
-        </is>
+    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A253" t="s">
+        <v>257</v>
       </c>
       <c r="B253">
         <v>2025</v>
       </c>
       <c r="C253">
-        <v>6930869.52</v>
+        <v>6930869.5199999996</v>
       </c>
       <c r="D253">
-        <v>6930869.52</v>
+        <v>6930869.5199999996</v>
       </c>
       <c r="E253">
         <v>1</v>
@@ -5930,20 +6648,18 @@
         <v>21</v>
       </c>
     </row>
-    <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t>Corredor Aricanduva - Obras do BRT - 1.1</t>
-        </is>
+    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A254" t="s">
+        <v>258</v>
       </c>
       <c r="B254">
         <v>2025</v>
       </c>
       <c r="C254">
-        <v>6524148.28</v>
+        <v>6524148.2800000003</v>
       </c>
       <c r="D254">
-        <v>6524148.28</v>
+        <v>6524148.2800000003</v>
       </c>
       <c r="E254">
         <v>1</v>
@@ -5952,17 +6668,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="255">
-      <c r="A255" t="inlineStr">
-        <is>
-          <t>Manutenção da Ouvidoria de Direitos Humanos</t>
-        </is>
+    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A255" t="s">
+        <v>259</v>
       </c>
       <c r="B255">
         <v>2025</v>
       </c>
       <c r="C255">
-        <v>6432381.47</v>
+        <v>6432381.4699999997</v>
       </c>
       <c r="D255">
         <v>4167355.87</v>
@@ -5974,20 +6688,18 @@
         <v>3</v>
       </c>
     </row>
-    <row r="256">
-      <c r="A256" t="inlineStr">
-        <is>
-          <t>Ações Permanentes de Promoção dos Direitos da População Idosa</t>
-        </is>
+    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A256" t="s">
+        <v>260</v>
       </c>
       <c r="B256">
         <v>2025</v>
       </c>
       <c r="C256">
-        <v>6322795.78</v>
+        <v>6322795.7800000003</v>
       </c>
       <c r="D256">
-        <v>6322795.78</v>
+        <v>6322795.7800000003</v>
       </c>
       <c r="E256">
         <v>1</v>
@@ -5996,11 +6708,9 @@
         <v>32</v>
       </c>
     </row>
-    <row r="257">
-      <c r="A257" t="inlineStr">
-        <is>
-          <t>Operação e Manutenção do VAI TEC</t>
-        </is>
+    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A257" t="s">
+        <v>261</v>
       </c>
       <c r="B257">
         <v>2025</v>
@@ -6018,20 +6728,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258">
-      <c r="A258" t="inlineStr">
-        <is>
-          <t>Urbanismo Social</t>
-        </is>
+    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A258" t="s">
+        <v>262</v>
       </c>
       <c r="B258">
         <v>2025</v>
       </c>
       <c r="C258">
-        <v>6234869.01</v>
+        <v>6234869.0099999998</v>
       </c>
       <c r="D258">
-        <v>6234869.01</v>
+        <v>6234869.0099999998</v>
       </c>
       <c r="E258">
         <v>1</v>
@@ -6040,20 +6748,18 @@
         <v>3</v>
       </c>
     </row>
-    <row r="259">
-      <c r="A259" t="inlineStr">
-        <is>
-          <t>Acessibilidade, Ampliação, Reforma e Requalificação de Faixas Exclusivas de Ônibus, inclusive Área de Parada e Plataforma de Embarque</t>
-        </is>
+    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A259" t="s">
+        <v>263</v>
       </c>
       <c r="B259">
         <v>2025</v>
       </c>
       <c r="C259">
-        <v>6164968.08</v>
+        <v>6164968.0800000001</v>
       </c>
       <c r="D259">
-        <v>6164968.08</v>
+        <v>6164968.0800000001</v>
       </c>
       <c r="E259">
         <v>1</v>
@@ -6062,20 +6768,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="260">
-      <c r="A260" t="inlineStr">
-        <is>
-          <t>PROCONECTA - Promoção da Conectividade e Inclusão Digital</t>
-        </is>
+    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A260" t="s">
+        <v>264</v>
       </c>
       <c r="B260">
         <v>2025</v>
       </c>
       <c r="C260">
-        <v>6029276.65</v>
+        <v>6029276.6500000004</v>
       </c>
       <c r="D260">
-        <v>6029276.65</v>
+        <v>6029276.6500000004</v>
       </c>
       <c r="E260">
         <v>1</v>
@@ -6084,20 +6788,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t>Implantação de Transporte Público Hidroviário</t>
-        </is>
+    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A261" t="s">
+        <v>265</v>
       </c>
       <c r="B261">
         <v>2025</v>
       </c>
       <c r="C261">
-        <v>6007993.23</v>
+        <v>6007993.2300000004</v>
       </c>
       <c r="D261">
-        <v>6007993.23</v>
+        <v>6007993.2300000004</v>
       </c>
       <c r="E261">
         <v>1</v>
@@ -6106,42 +6808,38 @@
         <v>3</v>
       </c>
     </row>
-    <row r="262">
-      <c r="A262" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação do Programa Sampa+Rural</t>
-        </is>
+    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A262" t="s">
+        <v>266</v>
       </c>
       <c r="B262">
         <v>2025</v>
       </c>
       <c r="C262">
-        <v>5980369.12</v>
+        <v>5980369.1200000001</v>
       </c>
       <c r="D262">
         <v>200000</v>
       </c>
       <c r="E262">
-        <v>0.03344275177449248</v>
+        <v>3.3442751774492477E-2</v>
       </c>
       <c r="F262">
         <v>1</v>
       </c>
     </row>
-    <row r="263">
-      <c r="A263" t="inlineStr">
-        <is>
-          <t>Corredor Aricanduva - Gerenciamento de Projetos - 3.1</t>
-        </is>
+    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A263" t="s">
+        <v>267</v>
       </c>
       <c r="B263">
         <v>2025</v>
       </c>
       <c r="C263">
-        <v>5837797.66</v>
+        <v>5837797.6600000001</v>
       </c>
       <c r="D263">
-        <v>5837797.66</v>
+        <v>5837797.6600000001</v>
       </c>
       <c r="E263">
         <v>1</v>
@@ -6150,11 +6848,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="264">
-      <c r="A264" t="inlineStr">
-        <is>
-          <t>Programação de Atividades Culturais de Centros Culturais e Teatros</t>
-        </is>
+    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A264" t="s">
+        <v>268</v>
       </c>
       <c r="B264">
         <v>2025</v>
@@ -6172,17 +6868,15 @@
         <v>16</v>
       </c>
     </row>
-    <row r="265">
-      <c r="A265" t="inlineStr">
-        <is>
-          <t>Contribuição Formação Patrimônio Servidor Público - Parcelamento PASEP</t>
-        </is>
+    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A265" t="s">
+        <v>269</v>
       </c>
       <c r="B265">
         <v>2025</v>
       </c>
       <c r="C265">
-        <v>5413813.899999999</v>
+        <v>5413813.8999999994</v>
       </c>
       <c r="D265">
         <v>0</v>
@@ -6194,33 +6888,29 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266">
-      <c r="A266" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação da Central de Interpretação de Libras, Intérpretes e Guias-Intérpretes</t>
-        </is>
+    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A266" t="s">
+        <v>270</v>
       </c>
       <c r="B266">
         <v>2025</v>
       </c>
       <c r="C266">
-        <v>5230195.81</v>
+        <v>5230195.8099999996</v>
       </c>
       <c r="D266">
         <v>227971.99</v>
       </c>
       <c r="E266">
-        <v>0.0435876587190337</v>
+        <v>4.3587658719033702E-2</v>
       </c>
       <c r="F266">
         <v>1</v>
       </c>
     </row>
-    <row r="267">
-      <c r="A267" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Unidades Educacionais - Escola Municipal de Educação Bilíngue para Surdos (EMEBS)</t>
-        </is>
+    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A267" t="s">
+        <v>271</v>
       </c>
       <c r="B267">
         <v>2025</v>
@@ -6238,11 +6928,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="268">
-      <c r="A268" t="inlineStr">
-        <is>
-          <t>Políticas, Programas e Ações Para Criança e Adolescente</t>
-        </is>
+    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A268" t="s">
+        <v>272</v>
       </c>
       <c r="B268">
         <v>2025</v>
@@ -6260,20 +6948,18 @@
         <v>15</v>
       </c>
     </row>
-    <row r="269">
-      <c r="A269" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação da Defesa Civil</t>
-        </is>
+    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A269" t="s">
+        <v>273</v>
       </c>
       <c r="B269">
         <v>2025</v>
       </c>
       <c r="C269">
-        <v>5092568.1</v>
+        <v>5092568.0999999996</v>
       </c>
       <c r="D269">
-        <v>5092568.1</v>
+        <v>5092568.0999999996</v>
       </c>
       <c r="E269">
         <v>1</v>
@@ -6282,11 +6968,9 @@
         <v>32</v>
       </c>
     </row>
-    <row r="270">
-      <c r="A270" t="inlineStr">
-        <is>
-          <t>Ações de Difusão Cultural do Theatro Municipal - Patrimônio</t>
-        </is>
+    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A270" t="s">
+        <v>274</v>
       </c>
       <c r="B270">
         <v>2025</v>
@@ -6304,17 +6988,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="271">
-      <c r="A271" t="inlineStr">
-        <is>
-          <t>Auxílio Funeral</t>
-        </is>
+    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A271" t="s">
+        <v>275</v>
       </c>
       <c r="B271">
         <v>2025</v>
       </c>
       <c r="C271">
-        <v>4715929.39</v>
+        <v>4715929.3899999997</v>
       </c>
       <c r="D271">
         <v>0</v>
@@ -6326,11 +7008,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>Políticas de Promoção Cultural</t>
-        </is>
+    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A272" t="s">
+        <v>276</v>
       </c>
       <c r="B272">
         <v>2025</v>
@@ -6348,11 +7028,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>Execução do Programa Museu de Arte de Rua - MAR</t>
-        </is>
+    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A273" t="s">
+        <v>277</v>
       </c>
       <c r="B273">
         <v>2025</v>
@@ -6370,11 +7048,9 @@
         <v>24</v>
       </c>
     </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>Bolsa Atleta</t>
-        </is>
+    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A274" t="s">
+        <v>278</v>
       </c>
       <c r="B274">
         <v>2025</v>
@@ -6392,11 +7068,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>Fomento e Difusão do Rock</t>
-        </is>
+    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A275" t="s">
+        <v>279</v>
       </c>
       <c r="B275">
         <v>2025</v>
@@ -6414,18 +7088,15 @@
         <v>16</v>
       </c>
     </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Promoção da Educação Antirracista e Não Xenofóbica na RMESP_x000D__x000D_
-</t>
-        </is>
+    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A276" t="s">
+        <v>280</v>
       </c>
       <c r="B276">
         <v>2025</v>
       </c>
       <c r="C276">
-        <v>4305082.14</v>
+        <v>4305082.1399999997</v>
       </c>
       <c r="D276">
         <v>0</v>
@@ -6437,11 +7108,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>Obrigações e Contribuições Patronais - Parcelamento INSS</t>
-        </is>
+    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A277" t="s">
+        <v>281</v>
       </c>
       <c r="B277">
         <v>2025</v>
@@ -6459,11 +7128,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>Rádios Comunitárias - Lei nº 16.572/2016</t>
-        </is>
+    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A278" t="s">
+        <v>282</v>
       </c>
       <c r="B278">
         <v>2025</v>
@@ -6481,11 +7148,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação dos Planetários Municipais</t>
-        </is>
+    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A279" t="s">
+        <v>283</v>
       </c>
       <c r="B279">
         <v>2025</v>
@@ -6503,11 +7168,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>Implantação e Construção de Ecopontos</t>
-        </is>
+    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A280" t="s">
+        <v>284</v>
       </c>
       <c r="B280">
         <v>2025</v>
@@ -6525,11 +7188,9 @@
         <v>32</v>
       </c>
     </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação do Arquivo Histórico Municipal</t>
-        </is>
+    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A281" t="s">
+        <v>285</v>
       </c>
       <c r="B281">
         <v>2025</v>
@@ -6547,11 +7208,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="282">
-      <c r="A282" t="inlineStr">
-        <is>
-          <t>Programação de Atividades Culturais nas Bibliotecas Públicas</t>
-        </is>
+    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A282" t="s">
+        <v>286</v>
       </c>
       <c r="B282">
         <v>2025</v>
@@ -6569,11 +7228,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="283">
-      <c r="A283" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Equipamentos do Patrimônio Histórico</t>
-        </is>
+    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A283" t="s">
+        <v>287</v>
       </c>
       <c r="B283">
         <v>2025</v>
@@ -6591,11 +7248,9 @@
         <v>25</v>
       </c>
     </row>
-    <row r="284">
-      <c r="A284" t="inlineStr">
-        <is>
-          <t>Ampliação, Reforma e Requalificação de Unidade de Abastecimento</t>
-        </is>
+    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A284" t="s">
+        <v>288</v>
       </c>
       <c r="B284">
         <v>2025</v>
@@ -6613,11 +7268,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="285">
-      <c r="A285" t="inlineStr">
-        <is>
-          <t>Fomento e Difusão do Samba</t>
-        </is>
+    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A285" t="s">
+        <v>289</v>
       </c>
       <c r="B285">
         <v>2025</v>
@@ -6635,11 +7288,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="286">
-      <c r="A286" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação do Programa de Residência em Gestão Pública</t>
-        </is>
+    <row r="286" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A286" t="s">
+        <v>290</v>
       </c>
       <c r="B286">
         <v>2025</v>
@@ -6657,11 +7308,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287">
-      <c r="A287" t="inlineStr">
-        <is>
-          <t>Programa Piá</t>
-        </is>
+    <row r="287" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A287" t="s">
+        <v>291</v>
       </c>
       <c r="B287">
         <v>2025</v>
@@ -6679,11 +7328,9 @@
         <v>26</v>
       </c>
     </row>
-    <row r="288">
-      <c r="A288" t="inlineStr">
-        <is>
-          <t>Fomento às Cadeias Produtivas, Vocações Produtivas e Projetos Locais</t>
-        </is>
+    <row r="288" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A288" t="s">
+        <v>292</v>
       </c>
       <c r="B288">
         <v>2025</v>
@@ -6701,11 +7348,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="289">
-      <c r="A289" t="inlineStr">
-        <is>
-          <t>Bolsa-Trabalho</t>
-        </is>
+    <row r="289" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A289" t="s">
+        <v>293</v>
       </c>
       <c r="B289">
         <v>2025</v>
@@ -6723,11 +7368,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290">
-      <c r="A290" t="inlineStr">
-        <is>
-          <t>Execução de Serviços Médicos de Tratamento de Radioterapia</t>
-        </is>
+    <row r="290" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A290" t="s">
+        <v>294</v>
       </c>
       <c r="B290">
         <v>2025</v>
@@ -6745,11 +7388,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="291">
-      <c r="A291" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação dos Equipamentos Públicos Voltados para Pessoa Idosa</t>
-        </is>
+    <row r="291" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A291" t="s">
+        <v>295</v>
       </c>
       <c r="B291">
         <v>2025</v>
@@ -6767,11 +7408,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="292">
-      <c r="A292" t="inlineStr">
-        <is>
-          <t>Fomento e Difusão da Capoeira</t>
-        </is>
+    <row r="292" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A292" t="s">
+        <v>296</v>
       </c>
       <c r="B292">
         <v>2025</v>
@@ -6789,20 +7428,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="293">
-      <c r="A293" t="inlineStr">
-        <is>
-          <t>Educação Ambiental</t>
-        </is>
+    <row r="293" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A293" t="s">
+        <v>297</v>
       </c>
       <c r="B293">
         <v>2025</v>
       </c>
       <c r="C293">
-        <v>2647738.2</v>
+        <v>2647738.2000000002</v>
       </c>
       <c r="D293">
-        <v>2647738.2</v>
+        <v>2647738.2000000002</v>
       </c>
       <c r="E293">
         <v>1</v>
@@ -6811,17 +7448,15 @@
         <v>14</v>
       </c>
     </row>
-    <row r="294">
-      <c r="A294" t="inlineStr">
-        <is>
-          <t>Bloqueios Judiciais</t>
-        </is>
+    <row r="294" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A294" t="s">
+        <v>298</v>
       </c>
       <c r="B294">
         <v>2025</v>
       </c>
       <c r="C294">
-        <v>2647554.45</v>
+        <v>2647554.4500000002</v>
       </c>
       <c r="D294">
         <v>0</v>
@@ -6833,11 +7468,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295">
-      <c r="A295" t="inlineStr">
-        <is>
-          <t>Mês do Hip Hop</t>
-        </is>
+    <row r="295" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A295" t="s">
+        <v>299</v>
       </c>
       <c r="B295">
         <v>2025</v>
@@ -6855,11 +7488,9 @@
         <v>26</v>
       </c>
     </row>
-    <row r="296">
-      <c r="A296" t="inlineStr">
-        <is>
-          <t>Ampliação, Reforma e Requalificação das Instalações para a Guarda Civil Metropolitana</t>
-        </is>
+    <row r="296" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A296" t="s">
+        <v>300</v>
       </c>
       <c r="B296">
         <v>2025</v>
@@ -6877,11 +7508,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="297">
-      <c r="A297" t="inlineStr">
-        <is>
-          <t>Ações de Difusão Cultural do Theatro Municipal - Programação Artística</t>
-        </is>
+    <row r="297" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A297" t="s">
+        <v>301</v>
       </c>
       <c r="B297">
         <v>2025</v>
@@ -6899,11 +7528,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="298">
-      <c r="A298" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Equipamentos Públicos Voltados ao Atendimento de Imigrantes</t>
-        </is>
+    <row r="298" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A298" t="s">
+        <v>302</v>
       </c>
       <c r="B298">
         <v>2025</v>
@@ -6921,11 +7548,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="299">
-      <c r="A299" t="inlineStr">
-        <is>
-          <t>Políticas, Programas e Ações para Pessoa Idosa</t>
-        </is>
+    <row r="299" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A299" t="s">
+        <v>303</v>
       </c>
       <c r="B299">
         <v>2025</v>
@@ -6943,11 +7568,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="300">
-      <c r="A300" t="inlineStr">
-        <is>
-          <t>Programação de Atividades Culturais do Centro Cultural São Paulo</t>
-        </is>
+    <row r="300" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A300" t="s">
+        <v>304</v>
       </c>
       <c r="B300">
         <v>2025</v>
@@ -6965,11 +7588,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="301">
-      <c r="A301" t="inlineStr">
-        <is>
-          <t>Construção e Implantação do Descomplica SP</t>
-        </is>
+    <row r="301" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A301" t="s">
+        <v>305</v>
       </c>
       <c r="B301">
         <v>2025</v>
@@ -6987,11 +7608,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="302">
-      <c r="A302" t="inlineStr">
-        <is>
-          <t>Programa de Iniciação Artística para a Primeira Infância - PIAPI</t>
-        </is>
+    <row r="302" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A302" t="s">
+        <v>306</v>
       </c>
       <c r="B302">
         <v>2025</v>
@@ -7009,12 +7628,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="303">
-      <c r="A303" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Operação e Manutenção do Portal da PMSP_x000D__x000D_
-</t>
-        </is>
+    <row r="303" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A303" t="s">
+        <v>307</v>
       </c>
       <c r="B303">
         <v>2025</v>
@@ -7032,11 +7648,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304">
-      <c r="A304" t="inlineStr">
-        <is>
-          <t>Apoio à Cultura Negra</t>
-        </is>
+    <row r="304" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A304" t="s">
+        <v>308</v>
       </c>
       <c r="B304">
         <v>2025</v>
@@ -7054,11 +7668,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="305">
-      <c r="A305" t="inlineStr">
-        <is>
-          <t>Programa Mãos e Mentes Paulistanas</t>
-        </is>
+    <row r="305" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A305" t="s">
+        <v>309</v>
       </c>
       <c r="B305">
         <v>2025</v>
@@ -7076,11 +7688,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306">
-      <c r="A306" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação do Programa de Proteção Escolar</t>
-        </is>
+    <row r="306" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A306" t="s">
+        <v>310</v>
       </c>
       <c r="B306">
         <v>2025</v>
@@ -7098,11 +7708,9 @@
         <v>32</v>
       </c>
     </row>
-    <row r="307">
-      <c r="A307" t="inlineStr">
-        <is>
-          <t>Difusão, Fomento e Pesquisas Aplicadas para a Gestão Participativa e Desenvolvimento Urbano</t>
-        </is>
+    <row r="307" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A307" t="s">
+        <v>311</v>
       </c>
       <c r="B307">
         <v>2025</v>
@@ -7120,11 +7728,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="308">
-      <c r="A308" t="inlineStr">
-        <is>
-          <t>Ações de Desenvolvimento Social</t>
-        </is>
+    <row r="308" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A308" t="s">
+        <v>312</v>
       </c>
       <c r="B308">
         <v>2025</v>
@@ -7142,11 +7748,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309">
-      <c r="A309" t="inlineStr">
-        <is>
-          <t>Vivência Prática de Gestão de Documentos</t>
-        </is>
+    <row r="309" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A309" t="s">
+        <v>313</v>
       </c>
       <c r="B309">
         <v>2025</v>
@@ -7158,17 +7762,15 @@
         <v>1359277.92</v>
       </c>
       <c r="E309">
-        <v>0.7665158642178745</v>
+        <v>0.76651586421787454</v>
       </c>
       <c r="F309">
         <v>1</v>
       </c>
     </row>
-    <row r="310">
-      <c r="A310" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação dos Conselhos e Espaços Participativos Municipais</t>
-        </is>
+    <row r="310" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A310" t="s">
+        <v>314</v>
       </c>
       <c r="B310">
         <v>2025</v>
@@ -7180,17 +7782,15 @@
         <v>1280553.81</v>
       </c>
       <c r="E310">
-        <v>0.7244013637180678</v>
+        <v>0.72440136371806785</v>
       </c>
       <c r="F310">
         <v>15</v>
       </c>
     </row>
-    <row r="311">
-      <c r="A311" t="inlineStr">
-        <is>
-          <t>Ações de Cooperação para o Desenvolvimento Sustentável</t>
-        </is>
+    <row r="311" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A311" t="s">
+        <v>315</v>
       </c>
       <c r="B311">
         <v>2025</v>
@@ -7202,17 +7802,15 @@
         <v>965575.03</v>
       </c>
       <c r="E311">
-        <v>0.5580481096839328</v>
+        <v>0.55804810968393281</v>
       </c>
       <c r="F311">
         <v>1</v>
       </c>
     </row>
-    <row r="312">
-      <c r="A312" t="inlineStr">
-        <is>
-          <t>Projeto de Intervenção Urbana - PIU</t>
-        </is>
+    <row r="312" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A312" t="s">
+        <v>316</v>
       </c>
       <c r="B312">
         <v>2025</v>
@@ -7230,11 +7828,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="313">
-      <c r="A313" t="inlineStr">
-        <is>
-          <t>Políticas, Programas e Ações para Educação em Direitos Humanos e Promoção do Direito à Cidade</t>
-        </is>
+    <row r="313" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A313" t="s">
+        <v>317</v>
       </c>
       <c r="B313">
         <v>2025</v>
@@ -7252,11 +7848,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="314">
-      <c r="A314" t="inlineStr">
-        <is>
-          <t>Ampliação, Reforma e Requalificação de Equipamentos de Saúde Animal</t>
-        </is>
+    <row r="314" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A314" t="s">
+        <v>318</v>
       </c>
       <c r="B314">
         <v>2025</v>
@@ -7274,11 +7868,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="315">
-      <c r="A315" t="inlineStr">
-        <is>
-          <t>Programa Vocacional</t>
-        </is>
+    <row r="315" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A315" t="s">
+        <v>319</v>
       </c>
       <c r="B315">
         <v>2025</v>
@@ -7296,11 +7888,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="316">
-      <c r="A316" t="inlineStr">
-        <is>
-          <t>Ações de Educação de Trânsito</t>
-        </is>
+    <row r="316" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A316" t="s">
+        <v>320</v>
       </c>
       <c r="B316">
         <v>2025</v>
@@ -7318,17 +7908,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317">
-      <c r="A317" t="inlineStr">
-        <is>
-          <t>Acordos Judiciais ou Administrativos</t>
-        </is>
+    <row r="317" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A317" t="s">
+        <v>321</v>
       </c>
       <c r="B317">
         <v>2025</v>
       </c>
       <c r="C317">
-        <v>1337524.34</v>
+        <v>1337524.3400000001</v>
       </c>
       <c r="D317">
         <v>0</v>
@@ -7340,11 +7928,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318">
-      <c r="A318" t="inlineStr">
-        <is>
-          <t>Programa Aldeias</t>
-        </is>
+    <row r="318" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A318" t="s">
+        <v>322</v>
       </c>
       <c r="B318">
         <v>2025</v>
@@ -7362,11 +7948,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="319">
-      <c r="A319" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação do Programa de Residência Jurídica</t>
-        </is>
+    <row r="319" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A319" t="s">
+        <v>323</v>
       </c>
       <c r="B319">
         <v>2025</v>
@@ -7384,11 +7968,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="320">
-      <c r="A320" t="inlineStr">
-        <is>
-          <t>Fomento à Música</t>
-        </is>
+    <row r="320" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A320" t="s">
+        <v>324</v>
       </c>
       <c r="B320">
         <v>2025</v>
@@ -7406,11 +7988,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="321">
-      <c r="A321" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Unidades Educacionais - Centro Municipal de Capacitação e Treinamento (CMCT)</t>
-        </is>
+    <row r="321" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A321" t="s">
+        <v>325</v>
       </c>
       <c r="B321">
         <v>2025</v>
@@ -7428,11 +8008,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="322">
-      <c r="A322" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação no Serviço de Guinchamento</t>
-        </is>
+    <row r="322" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A322" t="s">
+        <v>326</v>
       </c>
       <c r="B322">
         <v>2025</v>
@@ -7450,11 +8028,9 @@
         <v>32</v>
       </c>
     </row>
-    <row r="323">
-      <c r="A323" t="inlineStr">
-        <is>
-          <t>Fomento e Difusão do Forró</t>
-        </is>
+    <row r="323" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A323" t="s">
+        <v>327</v>
       </c>
       <c r="B323">
         <v>2025</v>
@@ -7472,11 +8048,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="324">
-      <c r="A324" t="inlineStr">
-        <is>
-          <t>Ações e Atividades Culturais da Biblioteca Mario de Andrade</t>
-        </is>
+    <row r="324" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A324" t="s">
+        <v>328</v>
       </c>
       <c r="B324">
         <v>2025</v>
@@ -7494,11 +8068,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="325">
-      <c r="A325" t="inlineStr">
-        <is>
-          <t>Ações e Atividades Culturais do Departamento do Patrimônio Histórico</t>
-        </is>
+    <row r="325" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A325" t="s">
+        <v>329</v>
       </c>
       <c r="B325">
         <v>2025</v>
@@ -7516,11 +8088,9 @@
         <v>32</v>
       </c>
     </row>
-    <row r="326">
-      <c r="A326" t="inlineStr">
-        <is>
-          <t>Circuito Cultural de São Paulo</t>
-        </is>
+    <row r="326" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A326" t="s">
+        <v>330</v>
       </c>
       <c r="B326">
         <v>2025</v>
@@ -7538,11 +8108,9 @@
         <v>22</v>
       </c>
     </row>
-    <row r="327">
-      <c r="A327" t="inlineStr">
-        <is>
-          <t>Ampliação, Reforma e Requalificação de Posto do Corpo de Bombeiros</t>
-        </is>
+    <row r="327" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A327" t="s">
+        <v>331</v>
       </c>
       <c r="B327">
         <v>2025</v>
@@ -7560,11 +8128,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="328">
-      <c r="A328" t="inlineStr">
-        <is>
-          <t>Publicação de Editais e Outras Publicações Legais e de Interesse do Município</t>
-        </is>
+    <row r="328" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A328" t="s">
+        <v>332</v>
       </c>
       <c r="B328">
         <v>2025</v>
@@ -7582,11 +8148,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="329">
-      <c r="A329" t="inlineStr">
-        <is>
-          <t>Fomento e Difusão do Reggae e da Cultura Rastafari</t>
-        </is>
+    <row r="329" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A329" t="s">
+        <v>333</v>
       </c>
       <c r="B329">
         <v>2025</v>
@@ -7604,11 +8168,9 @@
         <v>21</v>
       </c>
     </row>
-    <row r="330">
-      <c r="A330" t="inlineStr">
-        <is>
-          <t>Ampliação, Reforma e Requalificação de Unidades de Conservação</t>
-        </is>
+    <row r="330" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A330" t="s">
+        <v>334</v>
       </c>
       <c r="B330">
         <v>2025</v>
@@ -7626,11 +8188,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="331">
-      <c r="A331" t="inlineStr">
-        <is>
-          <t>Fomento e Difusão do Funk</t>
-        </is>
+    <row r="331" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A331" t="s">
+        <v>335</v>
       </c>
       <c r="B331">
         <v>2025</v>
@@ -7648,11 +8208,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="332">
-      <c r="A332" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação do Centro Público de Economia Solidária e Direitos Humanos</t>
-        </is>
+    <row r="332" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A332" t="s">
+        <v>336</v>
       </c>
       <c r="B332">
         <v>2025</v>
@@ -7670,11 +8228,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="333">
-      <c r="A333" t="inlineStr">
-        <is>
-          <t>Educação Paulistana Pode Mais - BID</t>
-        </is>
+    <row r="333" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A333" t="s">
+        <v>337</v>
       </c>
       <c r="B333">
         <v>2025</v>
@@ -7686,17 +8242,15 @@
         <v>494508.13</v>
       </c>
       <c r="E333">
-        <v>0.6610336607911477</v>
+        <v>0.66103366079114767</v>
       </c>
       <c r="F333">
         <v>2</v>
       </c>
     </row>
-    <row r="334">
-      <c r="A334" t="inlineStr">
-        <is>
-          <t>Política Municipal de Desenvolvimento Econômico</t>
-        </is>
+    <row r="334" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A334" t="s">
+        <v>338</v>
       </c>
       <c r="B334">
         <v>2025</v>
@@ -7714,20 +8268,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="335">
-      <c r="A335" t="inlineStr">
-        <is>
-          <t>BID II - Ampliação, Reforma e Requalificação de Equipamentos de Assistência Hospitalar</t>
-        </is>
+    <row r="335" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A335" t="s">
+        <v>339</v>
       </c>
       <c r="B335">
         <v>2025</v>
       </c>
       <c r="C335">
-        <v>718382.4400000001</v>
+        <v>718382.44000000006</v>
       </c>
       <c r="D335">
-        <v>718382.4400000001</v>
+        <v>718382.44000000006</v>
       </c>
       <c r="E335">
         <v>1</v>
@@ -7736,17 +8288,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="336">
-      <c r="A336" t="inlineStr">
-        <is>
-          <t>Restituição de Receitas Descontinuadas</t>
-        </is>
+    <row r="336" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A336" t="s">
+        <v>340</v>
       </c>
       <c r="B336">
         <v>2025</v>
       </c>
       <c r="C336">
-        <v>659534.8100000001</v>
+        <v>659534.81000000006</v>
       </c>
       <c r="D336">
         <v>0</v>
@@ -7758,11 +8308,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="337">
-      <c r="A337" t="inlineStr">
-        <is>
-          <t>Plano Municipal do Livro, Leitura, Literatura e Biblioteca (PMLLLB)</t>
-        </is>
+    <row r="337" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A337" t="s">
+        <v>341</v>
       </c>
       <c r="B337">
         <v>2025</v>
@@ -7780,11 +8328,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="338">
-      <c r="A338" t="inlineStr">
-        <is>
-          <t>Implantação de Corredores de Ônibus Novos</t>
-        </is>
+    <row r="338" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A338" t="s">
+        <v>342</v>
       </c>
       <c r="B338">
         <v>2025</v>
@@ -7802,11 +8348,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="339">
-      <c r="A339" t="inlineStr">
-        <is>
-          <t>Território Hip Hop (Vocacional Hip Hop)</t>
-        </is>
+    <row r="339" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A339" t="s">
+        <v>343</v>
       </c>
       <c r="B339">
         <v>2025</v>
@@ -7824,11 +8368,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="340">
-      <c r="A340" t="inlineStr">
-        <is>
-          <t>Centro de Referência da Dança</t>
-        </is>
+    <row r="340" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A340" t="s">
+        <v>344</v>
       </c>
       <c r="B340">
         <v>2025</v>
@@ -7846,11 +8388,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="341">
-      <c r="A341" t="inlineStr">
-        <is>
-          <t>Gestão do Patrimônio Imobiliário Municipal</t>
-        </is>
+    <row r="341" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A341" t="s">
+        <v>345</v>
       </c>
       <c r="B341">
         <v>2025</v>
@@ -7862,18 +8402,15 @@
         <v>420054.78</v>
       </c>
       <c r="E341">
-        <v>0.8148003457328933</v>
+        <v>0.81480034573289328</v>
       </c>
       <c r="F341">
         <v>1</v>
       </c>
     </row>
-    <row r="342">
-      <c r="A342" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Avança Saúde SP - Ampliação, Reforma e Requalificação de Equipamentos de Saúde_x000D__x000D_
-</t>
-        </is>
+    <row r="342" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A342" t="s">
+        <v>346</v>
       </c>
       <c r="B342">
         <v>2025</v>
@@ -7891,11 +8428,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="343">
-      <c r="A343" t="inlineStr">
-        <is>
-          <t>Políticas, Programas e Ações para Imigrantes e Promoção ao Trabalho Decente</t>
-        </is>
+    <row r="343" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A343" t="s">
+        <v>347</v>
       </c>
       <c r="B343">
         <v>2025</v>
@@ -7913,11 +8448,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="344">
-      <c r="A344" t="inlineStr">
-        <is>
-          <t>Centro de Memória do Circo</t>
-        </is>
+    <row r="344" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A344" t="s">
+        <v>348</v>
       </c>
       <c r="B344">
         <v>2025</v>
@@ -7935,11 +8468,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="345">
-      <c r="A345" t="inlineStr">
-        <is>
-          <t>Oficina nos Equipamentos Culturais</t>
-        </is>
+    <row r="345" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A345" t="s">
+        <v>349</v>
       </c>
       <c r="B345">
         <v>2025</v>
@@ -7957,11 +8488,9 @@
         <v>26</v>
       </c>
     </row>
-    <row r="346">
-      <c r="A346" t="inlineStr">
-        <is>
-          <t>Construção e Implantação de Equipamentos de Saúde Animal</t>
-        </is>
+    <row r="346" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A346" t="s">
+        <v>350</v>
       </c>
       <c r="B346">
         <v>2025</v>
@@ -7979,11 +8508,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="347">
-      <c r="A347" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação Semafórica</t>
-        </is>
+    <row r="347" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A347" t="s">
+        <v>351</v>
       </c>
       <c r="B347">
         <v>2025</v>
@@ -8001,11 +8528,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="348">
-      <c r="A348" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Espaços Lúdicos e Educativos</t>
-        </is>
+    <row r="348" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A348" t="s">
+        <v>352</v>
       </c>
       <c r="B348">
         <v>2025</v>
@@ -8023,11 +8548,9 @@
         <v>28</v>
       </c>
     </row>
-    <row r="349">
-      <c r="A349" t="inlineStr">
-        <is>
-          <t>Políticas, Programas e Ações para Promoção da Igualdade Racial</t>
-        </is>
+    <row r="349" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A349" t="s">
+        <v>353</v>
       </c>
       <c r="B349">
         <v>2025</v>
@@ -8045,11 +8568,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="350">
-      <c r="A350" t="inlineStr">
-        <is>
-          <t>Pesquisa de Satisfação do Cidadão em Relação aos Serviços, Políticas e Programas</t>
-        </is>
+    <row r="350" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A350" t="s">
+        <v>354</v>
       </c>
       <c r="B350">
         <v>2025</v>
@@ -8067,11 +8588,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="351">
-      <c r="A351" t="inlineStr">
-        <is>
-          <t>Pagamentos de Serviços Ambientais</t>
-        </is>
+    <row r="351" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A351" t="s">
+        <v>355</v>
       </c>
       <c r="B351">
         <v>2025</v>
@@ -8089,11 +8608,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="352">
-      <c r="A352" t="inlineStr">
-        <is>
-          <t>Programação de Atividades Culturais do Departamento dos Museus Municipais</t>
-        </is>
+    <row r="352" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A352" t="s">
+        <v>356</v>
       </c>
       <c r="B352">
         <v>2025</v>
@@ -8111,33 +8628,29 @@
         <v>2</v>
       </c>
     </row>
-    <row r="353">
-      <c r="A353" t="inlineStr">
-        <is>
-          <t>Manutenção de Prédios Administrativos</t>
-        </is>
+    <row r="353" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A353" t="s">
+        <v>357</v>
       </c>
       <c r="B353">
         <v>2025</v>
       </c>
       <c r="C353">
-        <v>301223.41</v>
+        <v>301223.40999999997</v>
       </c>
       <c r="D353">
         <v>287609.56</v>
       </c>
       <c r="E353">
-        <v>0.9548048075015151</v>
+        <v>0.95480480750151508</v>
       </c>
       <c r="F353">
         <v>4</v>
       </c>
     </row>
-    <row r="354">
-      <c r="A354" t="inlineStr">
-        <is>
-          <t>Instalação de Polo Criativo na Chácara do Jockey</t>
-        </is>
+    <row r="354" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A354" t="s">
+        <v>358</v>
       </c>
       <c r="B354">
         <v>2025</v>
@@ -8155,11 +8668,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="355">
-      <c r="A355" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação da Supervisão Geral das Juntas do Serviço Militar</t>
-        </is>
+    <row r="355" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A355" t="s">
+        <v>359</v>
       </c>
       <c r="B355">
         <v>2025</v>
@@ -8177,11 +8688,9 @@
         <v>32</v>
       </c>
     </row>
-    <row r="356">
-      <c r="A356" t="inlineStr">
-        <is>
-          <t>Auxílio Destinado a Assistência Odontológica a Agentes Públicos - Lei nº 17.841/2022</t>
-        </is>
+    <row r="356" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A356" t="s">
+        <v>360</v>
       </c>
       <c r="B356">
         <v>2025</v>
@@ -8199,11 +8708,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="357">
-      <c r="A357" t="inlineStr">
-        <is>
-          <t>FUMCAD - Multas Revertidas ao Fundo</t>
-        </is>
+    <row r="357" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A357" t="s">
+        <v>361</v>
       </c>
       <c r="B357">
         <v>2025</v>
@@ -8221,20 +8728,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="358">
-      <c r="A358" t="inlineStr">
-        <is>
-          <t>Conservação e Valorização de Acervos da Biblioteca Mário de Andrade</t>
-        </is>
+    <row r="358" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A358" t="s">
+        <v>362</v>
       </c>
       <c r="B358">
         <v>2025</v>
       </c>
       <c r="C358">
-        <v>156014.95</v>
+        <v>156014.95000000001</v>
       </c>
       <c r="D358">
-        <v>156014.95</v>
+        <v>156014.95000000001</v>
       </c>
       <c r="E358">
         <v>1</v>
@@ -8243,20 +8748,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="359">
-      <c r="A359" t="inlineStr">
-        <is>
-          <t>Políticas, Programas e Ações para Povos Indígenas</t>
-        </is>
+    <row r="359" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A359" t="s">
+        <v>363</v>
       </c>
       <c r="B359">
         <v>2025</v>
       </c>
       <c r="C359">
-        <v>140811.8</v>
+        <v>140811.79999999999</v>
       </c>
       <c r="D359">
-        <v>140811.8</v>
+        <v>140811.79999999999</v>
       </c>
       <c r="E359">
         <v>1</v>
@@ -8265,11 +8768,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="360">
-      <c r="A360" t="inlineStr">
-        <is>
-          <t>Ações de Monitoramento de Mudanças Climáticas</t>
-        </is>
+    <row r="360" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A360" t="s">
+        <v>364</v>
       </c>
       <c r="B360">
         <v>2025</v>
@@ -8287,11 +8788,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="361">
-      <c r="A361" t="inlineStr">
-        <is>
-          <t>Implantação de Projetos de Redesenho Urbano para Segurança Viária</t>
-        </is>
+    <row r="361" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A361" t="s">
+        <v>365</v>
       </c>
       <c r="B361">
         <v>2025</v>
@@ -8309,11 +8808,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="362">
-      <c r="A362" t="inlineStr">
-        <is>
-          <t>Políticas, Programas e Ações para Pessoas Egressas do Sistema Prisional</t>
-        </is>
+    <row r="362" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A362" t="s">
+        <v>366</v>
       </c>
       <c r="B362">
         <v>2025</v>
@@ -8331,11 +8828,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="363">
-      <c r="A363" t="inlineStr">
-        <is>
-          <t>Promoção da Transparência, do Acesso à Informação e do Controle Social</t>
-        </is>
+    <row r="363" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A363" t="s">
+        <v>367</v>
       </c>
       <c r="B363">
         <v>2025</v>
@@ -8353,11 +8848,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="364">
-      <c r="A364" t="inlineStr">
-        <is>
-          <t>Conservação e Valorização de Acervos do Departamento dos Museus Municipais</t>
-        </is>
+    <row r="364" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A364" t="s">
+        <v>368</v>
       </c>
       <c r="B364">
         <v>2025</v>
@@ -8375,11 +8868,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="365">
-      <c r="A365" t="inlineStr">
-        <is>
-          <t>Ações e Atividades Culturais do Arquivo Histórico Municipal</t>
-        </is>
+    <row r="365" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A365" t="s">
+        <v>369</v>
       </c>
       <c r="B365">
         <v>2025</v>
@@ -8397,11 +8888,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="366">
-      <c r="A366" t="inlineStr">
-        <is>
-          <t>Programa de Promoção da Imagem de São Paulo no Exterior</t>
-        </is>
+    <row r="366" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A366" t="s">
+        <v>370</v>
       </c>
       <c r="B366">
         <v>2025</v>
@@ -8419,11 +8908,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="367">
-      <c r="A367" t="inlineStr">
-        <is>
-          <t>Ações do Programa Agentes de Governo Aberto</t>
-        </is>
+    <row r="367" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A367" t="s">
+        <v>371</v>
       </c>
       <c r="B367">
         <v>2025</v>
@@ -8432,7 +8919,7 @@
         <v>59683.09</v>
       </c>
       <c r="D367">
-        <v>18531.01</v>
+        <v>18531.009999999998</v>
       </c>
       <c r="E367">
         <v>0.3104901237519706</v>
@@ -8441,11 +8928,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="368">
-      <c r="A368" t="inlineStr">
-        <is>
-          <t>Projetos e Ações de Apoio Habitacional</t>
-        </is>
+    <row r="368" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A368" t="s">
+        <v>372</v>
       </c>
       <c r="B368">
         <v>2025</v>
@@ -8463,11 +8948,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="369">
-      <c r="A369" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação do Herbário Municipal</t>
-        </is>
+    <row r="369" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A369" t="s">
+        <v>373</v>
       </c>
       <c r="B369">
         <v>2025</v>
@@ -8485,11 +8968,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="370">
-      <c r="A370" t="inlineStr">
-        <is>
-          <t>Corredor Aricanduva - Fortalecimento Institucional - 3.3</t>
-        </is>
+    <row r="370" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A370" t="s">
+        <v>374</v>
       </c>
       <c r="B370">
         <v>2025</v>
@@ -8507,11 +8988,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="371">
-      <c r="A371" t="inlineStr">
-        <is>
-          <t>Corredor Aricanduva - Controles Internos - 3.2</t>
-        </is>
+    <row r="371" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A371" t="s">
+        <v>375</v>
       </c>
       <c r="B371">
         <v>2025</v>
@@ -8529,11 +9008,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="372">
-      <c r="A372" t="inlineStr">
-        <is>
-          <t>Corredor Aricanduva - Acompanhamento Ambiental e Social - 1.5</t>
-        </is>
+    <row r="372" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A372" t="s">
+        <v>376</v>
       </c>
       <c r="B372">
         <v>2025</v>
@@ -8551,11 +9028,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="373">
-      <c r="A373" t="inlineStr">
-        <is>
-          <t>Comunicação e Orientação na Valorização e Cuidado na Primeira Infância</t>
-        </is>
+    <row r="373" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A373" t="s">
+        <v>377</v>
       </c>
       <c r="B373">
         <v>2025</v>
@@ -8573,11 +9048,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="374">
-      <c r="A374" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação do Programa de Pós-Graduação</t>
-        </is>
+    <row r="374" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A374" t="s">
+        <v>378</v>
       </c>
       <c r="B374">
         <v>2025</v>
@@ -8595,11 +9068,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="375">
-      <c r="A375" t="inlineStr">
-        <is>
-          <t>Fiscalização, Monitoramento e Controle Ambiental</t>
-        </is>
+    <row r="375" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A375" t="s">
+        <v>379</v>
       </c>
       <c r="B375">
         <v>2025</v>
@@ -8617,11 +9088,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="376">
-      <c r="A376" t="inlineStr">
-        <is>
-          <t>Ampliação, Reforma e Requalificação de Edificação da Câmara Municipal de São Paulo</t>
-        </is>
+    <row r="376" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A376" t="s">
+        <v>380</v>
       </c>
       <c r="B376">
         <v>2025</v>
@@ -8636,11 +9105,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="377">
-      <c r="A377" t="inlineStr">
-        <is>
-          <t>Ampliação, Reforma e Requalificação de Edificação do Tribunal de Contas do Município</t>
-        </is>
+    <row r="377" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A377" t="s">
+        <v>381</v>
       </c>
       <c r="B377">
         <v>2025</v>
@@ -8655,11 +9122,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="378">
-      <c r="A378" t="inlineStr">
-        <is>
-          <t>Ações de Vigilância Socioassistencial</t>
-        </is>
+    <row r="378" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A378" t="s">
+        <v>382</v>
       </c>
       <c r="B378">
         <v>2025</v>
@@ -8674,11 +9139,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="379">
-      <c r="A379" t="inlineStr">
-        <is>
-          <t>Benefícios Eventuais</t>
-        </is>
+    <row r="379" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A379" t="s">
+        <v>383</v>
       </c>
       <c r="B379">
         <v>2025</v>
@@ -8693,11 +9156,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="380">
-      <c r="A380" t="inlineStr">
-        <is>
-          <t>Construção de Edificações da Câmara Municipal de São Paulo</t>
-        </is>
+    <row r="380" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A380" t="s">
+        <v>384</v>
       </c>
       <c r="B380">
         <v>2025</v>
@@ -8712,11 +9173,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="381">
-      <c r="A381" t="inlineStr">
-        <is>
-          <t>Contraprestação de Parceria Público-Privada (PPP) - Iluminação Pública</t>
-        </is>
+    <row r="381" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A381" t="s">
+        <v>385</v>
       </c>
       <c r="B381">
         <v>2025</v>
@@ -8731,11 +9190,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="382">
-      <c r="A382" t="inlineStr">
-        <is>
-          <t>Câmara Municipal - Comunicação</t>
-        </is>
+    <row r="382" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A382" t="s">
+        <v>386</v>
       </c>
       <c r="B382">
         <v>2025</v>
@@ -8750,11 +9207,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="383">
-      <c r="A383" t="inlineStr">
-        <is>
-          <t>Encargos Referentes a Pagamentos de Manutenção de Conta Corrente</t>
-        </is>
+    <row r="383" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A383" t="s">
+        <v>387</v>
       </c>
       <c r="B383">
         <v>2025</v>
@@ -8769,11 +9224,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="384">
-      <c r="A384" t="inlineStr">
-        <is>
-          <t>Escola de Gestão e Contas Públicas</t>
-        </is>
+    <row r="384" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A384" t="s">
+        <v>388</v>
       </c>
       <c r="B384">
         <v>2025</v>
@@ -8788,11 +9241,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="385">
-      <c r="A385" t="inlineStr">
-        <is>
-          <t>Escola do Parlamento</t>
-        </is>
+    <row r="385" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A385" t="s">
+        <v>389</v>
       </c>
       <c r="B385">
         <v>2025</v>
@@ -8807,11 +9258,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="386">
-      <c r="A386" t="inlineStr">
-        <is>
-          <t>Expansão e Aperfeiçoamento das Atividades da CMSP</t>
-        </is>
+    <row r="386" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A386" t="s">
+        <v>390</v>
       </c>
       <c r="B386">
         <v>2025</v>
@@ -8826,11 +9275,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="387">
-      <c r="A387" t="inlineStr">
-        <is>
-          <t>Expansão e Aperfeiçoamento das Atividades do TCM</t>
-        </is>
+    <row r="387" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A387" t="s">
+        <v>391</v>
       </c>
       <c r="B387">
         <v>2025</v>
@@ -8845,11 +9292,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="388">
-      <c r="A388" t="inlineStr">
-        <is>
-          <t>Inserção das Famílias no Cadastro Único</t>
-        </is>
+    <row r="388" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A388" t="s">
+        <v>392</v>
       </c>
       <c r="B388">
         <v>2025</v>
@@ -8864,11 +9309,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="389">
-      <c r="A389" t="inlineStr">
-        <is>
-          <t>Manutenção e Operação de Edificação da Câmara Municipal de São Paulo</t>
-        </is>
+    <row r="389" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A389" t="s">
+        <v>393</v>
       </c>
       <c r="B389">
         <v>2025</v>
@@ -8883,11 +9326,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="390">
-      <c r="A390" t="inlineStr">
-        <is>
-          <t>Modernização Semafórica</t>
-        </is>
+    <row r="390" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A390" t="s">
+        <v>394</v>
       </c>
       <c r="B390">
         <v>2025</v>
@@ -8902,11 +9343,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="391">
-      <c r="A391" t="inlineStr">
-        <is>
-          <t>Plano de Contingência para Situações de Altas Temperaturas - Decreto nº 62.760/2023</t>
-        </is>
+    <row r="391" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A391" t="s">
+        <v>395</v>
       </c>
       <c r="B391">
         <v>2025</v>
@@ -8921,11 +9360,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="392">
-      <c r="A392" t="inlineStr">
-        <is>
-          <t>Programa Reencontro</t>
-        </is>
+    <row r="392" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A392" t="s">
+        <v>396</v>
       </c>
       <c r="B392">
         <v>2025</v>
@@ -8940,11 +9377,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="393">
-      <c r="A393" t="inlineStr">
-        <is>
-          <t>Programa de Garantia de Renda Familiar Mínima</t>
-        </is>
+    <row r="393" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A393" t="s">
+        <v>397</v>
       </c>
       <c r="B393">
         <v>2025</v>
@@ -8959,11 +9394,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="394">
-      <c r="A394" t="inlineStr">
-        <is>
-          <t>Realização de Conferências Municipais Temáticas</t>
-        </is>
+    <row r="394" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A394" t="s">
+        <v>398</v>
       </c>
       <c r="B394">
         <v>2025</v>
@@ -8978,11 +9411,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="395">
-      <c r="A395" t="inlineStr">
-        <is>
-          <t>Servidores Comissionados no Hospital Serv. Públco Municipal - HSPM</t>
-        </is>
+    <row r="395" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A395" t="s">
+        <v>399</v>
       </c>
       <c r="B395">
         <v>2025</v>
@@ -8997,11 +9428,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="396">
-      <c r="A396" t="inlineStr">
-        <is>
-          <t>Tarifa de Arrecadação de Multas</t>
-        </is>
+    <row r="396" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A396" t="s">
+        <v>400</v>
       </c>
       <c r="B396">
         <v>2025</v>
